--- a/GENERATED/StructureDefinition-PacienteLP.xlsx
+++ b/GENERATED/StructureDefinition-PacienteLP.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AO$79</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AO$106</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2981" uniqueCount="515">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3983" uniqueCount="595">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-01-10T16:59:21-03:00</t>
+    <t>2023-01-11T16:48:21-03:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -416,7 +416,7 @@
     <t>Patient.extension</t>
   </si>
   <si>
-    <t>4</t>
+    <t>7</t>
   </si>
   <si>
     <t xml:space="preserve">Extension
@@ -490,6 +490,42 @@
   <si>
     <t xml:space="preserve">Extension {http://minsal.cl/listaespera/StructureDefinition/PertenecienteEtnia}
 </t>
+  </si>
+  <si>
+    <t>Patient.extension:Etnia</t>
+  </si>
+  <si>
+    <t>Etnia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {http://minsal.cl/listaespera/StructureDefinition/Etnia}
+</t>
+  </si>
+  <si>
+    <t>Etnia a la cual pertenece</t>
+  </si>
+  <si>
+    <t>Patient.extension:Etniatexto</t>
+  </si>
+  <si>
+    <t>Etniatexto</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {http://minsal.cl/listaespera/StructureDefinition/Etniatexto}
+</t>
+  </si>
+  <si>
+    <t>Patient.extension:Afrodescendiente</t>
+  </si>
+  <si>
+    <t>Afrodescendiente</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {http://minsal.cl/listaespera/StructureDefinition/Afrodescendiente}
+</t>
+  </si>
+  <si>
+    <t>paciente pertenece a un Pueblo Afrodescendiente chileno</t>
   </si>
   <si>
     <t>Patient.modifierExtension</t>
@@ -1047,6 +1083,9 @@
     <t>Patient.telecom</t>
   </si>
   <si>
+    <t>3</t>
+  </si>
+  <si>
     <t xml:space="preserve">ContactPoint
 </t>
   </si>
@@ -1063,6 +1102,9 @@
     <t>People have (primary) ways to contact them in some way such as phone, email.</t>
   </si>
   <si>
+    <t>Slice creado para almacenar diferentes contactos</t>
+  </si>
+  <si>
     <t>telecom</t>
   </si>
   <si>
@@ -1070,6 +1112,209 @@
   </si>
   <si>
     <t>PID-13, PID-14, PID-40</t>
+  </si>
+  <si>
+    <t>Patient.telecom:contacto1</t>
+  </si>
+  <si>
+    <t>contacto1</t>
+  </si>
+  <si>
+    <t>Patient.telecom:contacto1.id</t>
+  </si>
+  <si>
+    <t>Patient.telecom.id</t>
+  </si>
+  <si>
+    <t>Patient.telecom:contacto1.extension</t>
+  </si>
+  <si>
+    <t>Patient.telecom.extension</t>
+  </si>
+  <si>
+    <t>Patient.telecom:contacto1.system</t>
+  </si>
+  <si>
+    <t>Patient.telecom.system</t>
+  </si>
+  <si>
+    <t>phone | fax | email | pager | url | sms | other</t>
+  </si>
+  <si>
+    <t>Telecommunications form for contact point - what communications system is required to make use of the contact.</t>
+  </si>
+  <si>
+    <t>hone</t>
+  </si>
+  <si>
+    <t>Telecommunications form for contact point.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/contact-point-system|4.0.1</t>
+  </si>
+  <si>
+    <t>ContactPoint.system</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cpt-2
+</t>
+  </si>
+  <si>
+    <t>./scheme</t>
+  </si>
+  <si>
+    <t>XTN.3</t>
+  </si>
+  <si>
+    <t>Patient.telecom:contacto1.value</t>
+  </si>
+  <si>
+    <t>Patient.telecom.value</t>
+  </si>
+  <si>
+    <t>The actual contact point details</t>
+  </si>
+  <si>
+    <t>The actual contact point details, in a form that is meaningful to the designated communication system (i.e. phone number or email address).</t>
+  </si>
+  <si>
+    <t>Additional text data such as phone extension numbers, or notes about use of the contact are sometimes included in the value.</t>
+  </si>
+  <si>
+    <t>Need to support legacy numbers that are not in a tightly controlled format.</t>
+  </si>
+  <si>
+    <t>ContactPoint.value</t>
+  </si>
+  <si>
+    <t>./url</t>
+  </si>
+  <si>
+    <t>XTN.1 (or XTN.12)</t>
+  </si>
+  <si>
+    <t>Patient.telecom:contacto1.use</t>
+  </si>
+  <si>
+    <t>Patient.telecom.use</t>
+  </si>
+  <si>
+    <t>home | work | temp | old | mobile - purpose of this contact point</t>
+  </si>
+  <si>
+    <t>Identifies the purpose for the contact point.</t>
+  </si>
+  <si>
+    <t>Applications can assume that a contact is current unless it explicitly says that it is temporary or old.</t>
+  </si>
+  <si>
+    <t>Need to track the way a person uses this contact, so a user can choose which is appropriate for their purpose.</t>
+  </si>
+  <si>
+    <t>Use of contact point.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/contact-point-use|4.0.1</t>
+  </si>
+  <si>
+    <t>ContactPoint.use</t>
+  </si>
+  <si>
+    <t>XTN.2 - but often indicated by field</t>
+  </si>
+  <si>
+    <t>Patient.telecom:contacto1.rank</t>
+  </si>
+  <si>
+    <t>Patient.telecom.rank</t>
+  </si>
+  <si>
+    <t xml:space="preserve">positiveInt
+</t>
+  </si>
+  <si>
+    <t>Specify preferred order of use (1 = highest)</t>
+  </si>
+  <si>
+    <t>Specifies a preferred order in which to use a set of contacts. ContactPoints with lower rank values are more preferred than those with higher rank values.</t>
+  </si>
+  <si>
+    <t>Note that rank does not necessarily follow the order in which the contacts are represented in the instance.</t>
+  </si>
+  <si>
+    <t>ContactPoint.rank</t>
+  </si>
+  <si>
+    <t>Patient.telecom:contacto1.period</t>
+  </si>
+  <si>
+    <t>Patient.telecom.period</t>
+  </si>
+  <si>
+    <t>Time period when the contact point was/is in use</t>
+  </si>
+  <si>
+    <t>Time period when the contact point was/is in use.</t>
+  </si>
+  <si>
+    <t>ContactPoint.period</t>
+  </si>
+  <si>
+    <t>Patient.telecom:contacto2</t>
+  </si>
+  <si>
+    <t>contacto2</t>
+  </si>
+  <si>
+    <t>Patient.telecom:contacto2.id</t>
+  </si>
+  <si>
+    <t>Patient.telecom:contacto2.extension</t>
+  </si>
+  <si>
+    <t>Patient.telecom:contacto2.system</t>
+  </si>
+  <si>
+    <t>Patient.telecom:contacto2.value</t>
+  </si>
+  <si>
+    <t>Patient.telecom:contacto2.use</t>
+  </si>
+  <si>
+    <t>Patient.telecom:contacto2.rank</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>Patient.telecom:contacto2.period</t>
+  </si>
+  <si>
+    <t>Patient.telecom:contacto3</t>
+  </si>
+  <si>
+    <t>contacto3</t>
+  </si>
+  <si>
+    <t>Patient.telecom:contacto3.id</t>
+  </si>
+  <si>
+    <t>Patient.telecom:contacto3.extension</t>
+  </si>
+  <si>
+    <t>Patient.telecom:contacto3.system</t>
+  </si>
+  <si>
+    <t>Patient.telecom:contacto3.value</t>
+  </si>
+  <si>
+    <t>Patient.telecom:contacto3.use</t>
+  </si>
+  <si>
+    <t>Patient.telecom:contacto3.rank</t>
+  </si>
+  <si>
+    <t>Patient.telecom:contacto3.period</t>
   </si>
   <si>
     <t>Patient.gender</t>
@@ -1923,7 +2168,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AO79"/>
+  <dimension ref="A1:AO106"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="45.84375" customWidth="true" bestFit="true"/>
@@ -3494,43 +3739,41 @@
         <v>152</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>152</v>
-      </c>
-      <c r="C14" s="2"/>
+        <v>128</v>
+      </c>
+      <c r="C14" t="s" s="2">
+        <v>153</v>
+      </c>
       <c r="D14" t="s" s="2">
-        <v>153</v>
+        <v>77</v>
       </c>
       <c r="E14" s="2"/>
       <c r="F14" t="s" s="2">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="G14" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="H14" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="I14" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="J14" t="s" s="2">
         <v>77</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>130</v>
+        <v>154</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="M14" t="s" s="2">
         <v>155</v>
       </c>
-      <c r="N14" t="s" s="2">
-        <v>156</v>
-      </c>
-      <c r="O14" t="s" s="2">
-        <v>157</v>
-      </c>
+      <c r="N14" s="2"/>
+      <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
         <v>77</v>
       </c>
@@ -3578,7 +3821,7 @@
         <v>77</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>158</v>
+        <v>135</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>75</v>
@@ -3587,13 +3830,13 @@
         <v>76</v>
       </c>
       <c r="AI14" t="s" s="2">
-        <v>77</v>
+        <v>142</v>
       </c>
       <c r="AJ14" t="s" s="2">
         <v>136</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>127</v>
+        <v>77</v>
       </c>
       <c r="AL14" t="s" s="2">
         <v>77</v>
@@ -3610,12 +3853,14 @@
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>159</v>
-      </c>
-      <c r="C15" s="2"/>
+        <v>128</v>
+      </c>
+      <c r="C15" t="s" s="2">
+        <v>157</v>
+      </c>
       <c r="D15" t="s" s="2">
         <v>77</v>
       </c>
@@ -3624,30 +3869,28 @@
         <v>84</v>
       </c>
       <c r="G15" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="H15" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="I15" t="s" s="2">
         <v>77</v>
       </c>
       <c r="J15" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="N15" s="2"/>
-      <c r="O15" t="s" s="2">
-        <v>163</v>
-      </c>
+      <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
         <v>77</v>
       </c>
@@ -3683,19 +3926,19 @@
         <v>77</v>
       </c>
       <c r="AB15" t="s" s="2">
-        <v>164</v>
+        <v>77</v>
       </c>
       <c r="AC15" t="s" s="2">
-        <v>165</v>
+        <v>77</v>
       </c>
       <c r="AD15" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE15" t="s" s="2">
-        <v>134</v>
+        <v>77</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>159</v>
+        <v>135</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>75</v>
@@ -3704,22 +3947,22 @@
         <v>76</v>
       </c>
       <c r="AI15" t="s" s="2">
-        <v>77</v>
+        <v>142</v>
       </c>
       <c r="AJ15" t="s" s="2">
-        <v>96</v>
+        <v>136</v>
       </c>
       <c r="AK15" t="s" s="2">
-        <v>166</v>
+        <v>77</v>
       </c>
       <c r="AL15" t="s" s="2">
-        <v>167</v>
+        <v>77</v>
       </c>
       <c r="AM15" t="s" s="2">
-        <v>168</v>
+        <v>77</v>
       </c>
       <c r="AN15" t="s" s="2">
-        <v>169</v>
+        <v>77</v>
       </c>
       <c r="AO15" t="s" s="2">
         <v>77</v>
@@ -3727,13 +3970,13 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>170</v>
+        <v>159</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>159</v>
+        <v>128</v>
       </c>
       <c r="C16" t="s" s="2">
-        <v>171</v>
+        <v>160</v>
       </c>
       <c r="D16" t="s" s="2">
         <v>77</v>
@@ -3752,21 +3995,19 @@
         <v>77</v>
       </c>
       <c r="J16" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="K16" t="s" s="2">
+        <v>161</v>
+      </c>
+      <c r="L16" t="s" s="2">
         <v>160</v>
-      </c>
-      <c r="L16" t="s" s="2">
-        <v>161</v>
       </c>
       <c r="M16" t="s" s="2">
         <v>162</v>
       </c>
       <c r="N16" s="2"/>
-      <c r="O16" t="s" s="2">
-        <v>163</v>
-      </c>
+      <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
         <v>77</v>
       </c>
@@ -3814,7 +4055,7 @@
         <v>77</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>159</v>
+        <v>135</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>75</v>
@@ -3823,22 +4064,22 @@
         <v>76</v>
       </c>
       <c r="AI16" t="s" s="2">
-        <v>77</v>
+        <v>142</v>
       </c>
       <c r="AJ16" t="s" s="2">
-        <v>96</v>
+        <v>136</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>166</v>
+        <v>77</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>167</v>
+        <v>77</v>
       </c>
       <c r="AM16" t="s" s="2">
-        <v>168</v>
+        <v>77</v>
       </c>
       <c r="AN16" t="s" s="2">
-        <v>169</v>
+        <v>77</v>
       </c>
       <c r="AO16" t="s" s="2">
         <v>77</v>
@@ -3846,42 +4087,46 @@
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>172</v>
+        <v>163</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>173</v>
+        <v>163</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
-        <v>77</v>
+        <v>164</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
         <v>75</v>
       </c>
       <c r="G17" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="H17" t="s" s="2">
         <v>77</v>
       </c>
       <c r="I17" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="J17" t="s" s="2">
         <v>77</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>174</v>
+        <v>130</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>175</v>
+        <v>165</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>176</v>
-      </c>
-      <c r="N17" s="2"/>
-      <c r="O17" s="2"/>
+        <v>166</v>
+      </c>
+      <c r="N17" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="O17" t="s" s="2">
+        <v>168</v>
+      </c>
       <c r="P17" t="s" s="2">
         <v>77</v>
       </c>
@@ -3929,22 +4174,22 @@
         <v>77</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>177</v>
+        <v>169</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH17" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="AI17" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ17" t="s" s="2">
-        <v>77</v>
+        <v>136</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>178</v>
+        <v>127</v>
       </c>
       <c r="AL17" t="s" s="2">
         <v>77</v>
@@ -3961,18 +4206,18 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>179</v>
+        <v>170</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
-        <v>153</v>
+        <v>77</v>
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="G18" t="s" s="2">
         <v>76</v>
@@ -3984,21 +4229,21 @@
         <v>77</v>
       </c>
       <c r="J18" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>130</v>
+        <v>171</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>181</v>
+        <v>172</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>182</v>
-      </c>
-      <c r="N18" t="s" s="2">
-        <v>156</v>
-      </c>
-      <c r="O18" s="2"/>
+        <v>173</v>
+      </c>
+      <c r="N18" s="2"/>
+      <c r="O18" t="s" s="2">
+        <v>174</v>
+      </c>
       <c r="P18" t="s" s="2">
         <v>77</v>
       </c>
@@ -4034,10 +4279,10 @@
         <v>77</v>
       </c>
       <c r="AB18" t="s" s="2">
-        <v>133</v>
+        <v>175</v>
       </c>
       <c r="AC18" t="s" s="2">
-        <v>183</v>
+        <v>176</v>
       </c>
       <c r="AD18" t="s" s="2">
         <v>77</v>
@@ -4046,7 +4291,7 @@
         <v>134</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>184</v>
+        <v>170</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>75</v>
@@ -4058,19 +4303,19 @@
         <v>77</v>
       </c>
       <c r="AJ18" t="s" s="2">
-        <v>136</v>
+        <v>96</v>
       </c>
       <c r="AK18" t="s" s="2">
+        <v>177</v>
+      </c>
+      <c r="AL18" t="s" s="2">
         <v>178</v>
       </c>
-      <c r="AL18" t="s" s="2">
-        <v>77</v>
-      </c>
       <c r="AM18" t="s" s="2">
-        <v>77</v>
+        <v>179</v>
       </c>
       <c r="AN18" t="s" s="2">
-        <v>77</v>
+        <v>180</v>
       </c>
       <c r="AO18" t="s" s="2">
         <v>77</v>
@@ -4078,45 +4323,45 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>186</v>
-      </c>
-      <c r="C19" s="2"/>
+        <v>170</v>
+      </c>
+      <c r="C19" t="s" s="2">
+        <v>182</v>
+      </c>
       <c r="D19" t="s" s="2">
         <v>77</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="G19" t="s" s="2">
         <v>84</v>
       </c>
       <c r="H19" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="I19" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="J19" t="s" s="2">
         <v>85</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>104</v>
+        <v>171</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>187</v>
+        <v>172</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>188</v>
-      </c>
-      <c r="N19" t="s" s="2">
-        <v>189</v>
-      </c>
+        <v>173</v>
+      </c>
+      <c r="N19" s="2"/>
       <c r="O19" t="s" s="2">
-        <v>190</v>
+        <v>174</v>
       </c>
       <c r="P19" t="s" s="2">
         <v>77</v>
@@ -4141,13 +4386,13 @@
         <v>77</v>
       </c>
       <c r="X19" t="s" s="2">
-        <v>191</v>
+        <v>77</v>
       </c>
       <c r="Y19" t="s" s="2">
-        <v>192</v>
+        <v>77</v>
       </c>
       <c r="Z19" t="s" s="2">
-        <v>193</v>
+        <v>77</v>
       </c>
       <c r="AA19" t="s" s="2">
         <v>77</v>
@@ -4165,13 +4410,13 @@
         <v>77</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>194</v>
+        <v>170</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH19" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="AI19" t="s" s="2">
         <v>77</v>
@@ -4180,16 +4425,16 @@
         <v>96</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>195</v>
+        <v>177</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>77</v>
+        <v>178</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>77</v>
+        <v>179</v>
       </c>
       <c r="AN19" t="s" s="2">
-        <v>127</v>
+        <v>180</v>
       </c>
       <c r="AO19" t="s" s="2">
         <v>77</v>
@@ -4197,10 +4442,10 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>196</v>
+        <v>183</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>197</v>
+        <v>184</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -4208,35 +4453,31 @@
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
-        <v>84</v>
+        <v>75</v>
       </c>
       <c r="G20" t="s" s="2">
         <v>84</v>
       </c>
       <c r="H20" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="I20" t="s" s="2">
         <v>77</v>
       </c>
       <c r="J20" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>198</v>
+        <v>185</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>199</v>
+        <v>186</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>200</v>
-      </c>
-      <c r="N20" t="s" s="2">
-        <v>201</v>
-      </c>
-      <c r="O20" t="s" s="2">
-        <v>202</v>
-      </c>
+        <v>187</v>
+      </c>
+      <c r="N20" s="2"/>
+      <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
         <v>77</v>
       </c>
@@ -4260,13 +4501,13 @@
         <v>77</v>
       </c>
       <c r="X20" t="s" s="2">
-        <v>203</v>
+        <v>77</v>
       </c>
       <c r="Y20" t="s" s="2">
-        <v>204</v>
+        <v>77</v>
       </c>
       <c r="Z20" t="s" s="2">
-        <v>205</v>
+        <v>77</v>
       </c>
       <c r="AA20" t="s" s="2">
         <v>77</v>
@@ -4284,7 +4525,7 @@
         <v>77</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>206</v>
+        <v>188</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>75</v>
@@ -4296,10 +4537,10 @@
         <v>77</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>96</v>
+        <v>77</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>195</v>
+        <v>189</v>
       </c>
       <c r="AL20" t="s" s="2">
         <v>77</v>
@@ -4308,7 +4549,7 @@
         <v>77</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>207</v>
+        <v>77</v>
       </c>
       <c r="AO20" t="s" s="2">
         <v>77</v>
@@ -4316,21 +4557,21 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>208</v>
+        <v>190</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>209</v>
+        <v>191</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
-        <v>77</v>
+        <v>164</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
         <v>75</v>
       </c>
       <c r="G21" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="H21" t="s" s="2">
         <v>77</v>
@@ -4339,23 +4580,21 @@
         <v>77</v>
       </c>
       <c r="J21" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>98</v>
+        <v>130</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>210</v>
+        <v>192</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>211</v>
+        <v>193</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>212</v>
-      </c>
-      <c r="O21" t="s" s="2">
-        <v>213</v>
-      </c>
+        <v>167</v>
+      </c>
+      <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
         <v>77</v>
       </c>
@@ -4367,7 +4606,7 @@
         <v>77</v>
       </c>
       <c r="T21" t="s" s="2">
-        <v>214</v>
+        <v>77</v>
       </c>
       <c r="U21" t="s" s="2">
         <v>77</v>
@@ -4391,34 +4630,34 @@
         <v>77</v>
       </c>
       <c r="AB21" t="s" s="2">
-        <v>77</v>
+        <v>133</v>
       </c>
       <c r="AC21" t="s" s="2">
-        <v>77</v>
+        <v>194</v>
       </c>
       <c r="AD21" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE21" t="s" s="2">
-        <v>77</v>
+        <v>134</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>215</v>
+        <v>195</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH21" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="AI21" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>96</v>
+        <v>136</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>216</v>
+        <v>189</v>
       </c>
       <c r="AL21" t="s" s="2">
         <v>77</v>
@@ -4427,7 +4666,7 @@
         <v>77</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>217</v>
+        <v>77</v>
       </c>
       <c r="AO21" t="s" s="2">
         <v>77</v>
@@ -4435,10 +4674,10 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>218</v>
+        <v>196</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>219</v>
+        <v>197</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4446,33 +4685,35 @@
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
-        <v>84</v>
+        <v>75</v>
       </c>
       <c r="G22" t="s" s="2">
         <v>84</v>
       </c>
       <c r="H22" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I22" t="s" s="2">
         <v>85</v>
-      </c>
-      <c r="I22" t="s" s="2">
-        <v>77</v>
       </c>
       <c r="J22" t="s" s="2">
         <v>85</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>174</v>
+        <v>104</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>220</v>
+        <v>198</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>221</v>
+        <v>199</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>222</v>
-      </c>
-      <c r="O22" s="2"/>
+        <v>200</v>
+      </c>
+      <c r="O22" t="s" s="2">
+        <v>201</v>
+      </c>
       <c r="P22" t="s" s="2">
         <v>77</v>
       </c>
@@ -4484,7 +4725,7 @@
         <v>77</v>
       </c>
       <c r="T22" t="s" s="2">
-        <v>223</v>
+        <v>77</v>
       </c>
       <c r="U22" t="s" s="2">
         <v>77</v>
@@ -4496,13 +4737,13 @@
         <v>77</v>
       </c>
       <c r="X22" t="s" s="2">
-        <v>77</v>
+        <v>202</v>
       </c>
       <c r="Y22" t="s" s="2">
-        <v>77</v>
+        <v>203</v>
       </c>
       <c r="Z22" t="s" s="2">
-        <v>77</v>
+        <v>204</v>
       </c>
       <c r="AA22" t="s" s="2">
         <v>77</v>
@@ -4520,7 +4761,7 @@
         <v>77</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>224</v>
+        <v>205</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>75</v>
@@ -4535,7 +4776,7 @@
         <v>96</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>225</v>
+        <v>206</v>
       </c>
       <c r="AL22" t="s" s="2">
         <v>77</v>
@@ -4544,7 +4785,7 @@
         <v>77</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>226</v>
+        <v>127</v>
       </c>
       <c r="AO22" t="s" s="2">
         <v>77</v>
@@ -4552,10 +4793,10 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>227</v>
+        <v>207</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>228</v>
+        <v>208</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4563,13 +4804,13 @@
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="G23" t="s" s="2">
         <v>84</v>
       </c>
       <c r="H23" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="I23" t="s" s="2">
         <v>77</v>
@@ -4578,16 +4819,20 @@
         <v>85</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>229</v>
+        <v>209</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>230</v>
+        <v>210</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>231</v>
-      </c>
-      <c r="N23" s="2"/>
-      <c r="O23" s="2"/>
+        <v>211</v>
+      </c>
+      <c r="N23" t="s" s="2">
+        <v>212</v>
+      </c>
+      <c r="O23" t="s" s="2">
+        <v>213</v>
+      </c>
       <c r="P23" t="s" s="2">
         <v>77</v>
       </c>
@@ -4611,13 +4856,13 @@
         <v>77</v>
       </c>
       <c r="X23" t="s" s="2">
-        <v>77</v>
+        <v>214</v>
       </c>
       <c r="Y23" t="s" s="2">
-        <v>77</v>
+        <v>215</v>
       </c>
       <c r="Z23" t="s" s="2">
-        <v>77</v>
+        <v>216</v>
       </c>
       <c r="AA23" t="s" s="2">
         <v>77</v>
@@ -4635,7 +4880,7 @@
         <v>77</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>232</v>
+        <v>217</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>75</v>
@@ -4650,7 +4895,7 @@
         <v>96</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>233</v>
+        <v>206</v>
       </c>
       <c r="AL23" t="s" s="2">
         <v>77</v>
@@ -4659,7 +4904,7 @@
         <v>77</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>234</v>
+        <v>218</v>
       </c>
       <c r="AO23" t="s" s="2">
         <v>77</v>
@@ -4667,10 +4912,10 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>235</v>
+        <v>219</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>236</v>
+        <v>220</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4693,18 +4938,20 @@
         <v>85</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>237</v>
+        <v>98</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>238</v>
+        <v>221</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>239</v>
+        <v>222</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>240</v>
-      </c>
-      <c r="O24" s="2"/>
+        <v>223</v>
+      </c>
+      <c r="O24" t="s" s="2">
+        <v>224</v>
+      </c>
       <c r="P24" t="s" s="2">
         <v>77</v>
       </c>
@@ -4716,7 +4963,7 @@
         <v>77</v>
       </c>
       <c r="T24" t="s" s="2">
-        <v>77</v>
+        <v>225</v>
       </c>
       <c r="U24" t="s" s="2">
         <v>77</v>
@@ -4752,7 +4999,7 @@
         <v>77</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>241</v>
+        <v>226</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>75</v>
@@ -4767,7 +5014,7 @@
         <v>96</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>242</v>
+        <v>227</v>
       </c>
       <c r="AL24" t="s" s="2">
         <v>77</v>
@@ -4776,7 +5023,7 @@
         <v>77</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>243</v>
+        <v>228</v>
       </c>
       <c r="AO24" t="s" s="2">
         <v>77</v>
@@ -4784,20 +5031,18 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>244</v>
+        <v>229</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>159</v>
-      </c>
-      <c r="C25" t="s" s="2">
-        <v>245</v>
-      </c>
+        <v>230</v>
+      </c>
+      <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
         <v>77</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="G25" t="s" s="2">
         <v>84</v>
@@ -4812,18 +5057,18 @@
         <v>85</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>160</v>
+        <v>185</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>161</v>
+        <v>231</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="N25" s="2"/>
-      <c r="O25" t="s" s="2">
-        <v>163</v>
-      </c>
+        <v>232</v>
+      </c>
+      <c r="N25" t="s" s="2">
+        <v>233</v>
+      </c>
+      <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
         <v>77</v>
       </c>
@@ -4835,7 +5080,7 @@
         <v>77</v>
       </c>
       <c r="T25" t="s" s="2">
-        <v>77</v>
+        <v>234</v>
       </c>
       <c r="U25" t="s" s="2">
         <v>77</v>
@@ -4871,13 +5116,13 @@
         <v>77</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>159</v>
+        <v>235</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH25" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="AI25" t="s" s="2">
         <v>77</v>
@@ -4886,16 +5131,16 @@
         <v>96</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>166</v>
+        <v>236</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>167</v>
+        <v>77</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>168</v>
+        <v>77</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>169</v>
+        <v>237</v>
       </c>
       <c r="AO25" t="s" s="2">
         <v>77</v>
@@ -4903,10 +5148,10 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>246</v>
+        <v>238</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>173</v>
+        <v>239</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4926,16 +5171,16 @@
         <v>77</v>
       </c>
       <c r="J26" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>174</v>
+        <v>240</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>175</v>
+        <v>241</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>176</v>
+        <v>242</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
@@ -4986,7 +5231,7 @@
         <v>77</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>177</v>
+        <v>243</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>75</v>
@@ -4998,10 +5243,10 @@
         <v>77</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>77</v>
+        <v>96</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>178</v>
+        <v>244</v>
       </c>
       <c r="AL26" t="s" s="2">
         <v>77</v>
@@ -5010,7 +5255,7 @@
         <v>77</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>77</v>
+        <v>245</v>
       </c>
       <c r="AO26" t="s" s="2">
         <v>77</v>
@@ -5018,21 +5263,21 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
+        <v>246</v>
+      </c>
+      <c r="B27" t="s" s="2">
         <v>247</v>
-      </c>
-      <c r="B27" t="s" s="2">
-        <v>180</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
-        <v>153</v>
+        <v>77</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
         <v>75</v>
       </c>
       <c r="G27" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="H27" t="s" s="2">
         <v>77</v>
@@ -5041,19 +5286,19 @@
         <v>77</v>
       </c>
       <c r="J27" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>130</v>
+        <v>248</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>181</v>
+        <v>249</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>182</v>
+        <v>250</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>156</v>
+        <v>251</v>
       </c>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
@@ -5091,34 +5336,34 @@
         <v>77</v>
       </c>
       <c r="AB27" t="s" s="2">
-        <v>133</v>
+        <v>77</v>
       </c>
       <c r="AC27" t="s" s="2">
-        <v>183</v>
+        <v>77</v>
       </c>
       <c r="AD27" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE27" t="s" s="2">
-        <v>134</v>
+        <v>77</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>184</v>
+        <v>252</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH27" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="AI27" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>136</v>
+        <v>96</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>178</v>
+        <v>253</v>
       </c>
       <c r="AL27" t="s" s="2">
         <v>77</v>
@@ -5127,7 +5372,7 @@
         <v>77</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>77</v>
+        <v>254</v>
       </c>
       <c r="AO27" t="s" s="2">
         <v>77</v>
@@ -5135,12 +5380,14 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>248</v>
+        <v>255</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>186</v>
-      </c>
-      <c r="C28" s="2"/>
+        <v>170</v>
+      </c>
+      <c r="C28" t="s" s="2">
+        <v>256</v>
+      </c>
       <c r="D28" t="s" s="2">
         <v>77</v>
       </c>
@@ -5152,28 +5399,26 @@
         <v>84</v>
       </c>
       <c r="H28" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="I28" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="J28" t="s" s="2">
         <v>85</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>104</v>
+        <v>171</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>187</v>
+        <v>172</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>188</v>
-      </c>
-      <c r="N28" t="s" s="2">
-        <v>189</v>
-      </c>
+        <v>173</v>
+      </c>
+      <c r="N28" s="2"/>
       <c r="O28" t="s" s="2">
-        <v>190</v>
+        <v>174</v>
       </c>
       <c r="P28" t="s" s="2">
         <v>77</v>
@@ -5198,13 +5443,13 @@
         <v>77</v>
       </c>
       <c r="X28" t="s" s="2">
-        <v>191</v>
+        <v>77</v>
       </c>
       <c r="Y28" t="s" s="2">
-        <v>192</v>
+        <v>77</v>
       </c>
       <c r="Z28" t="s" s="2">
-        <v>193</v>
+        <v>77</v>
       </c>
       <c r="AA28" t="s" s="2">
         <v>77</v>
@@ -5222,13 +5467,13 @@
         <v>77</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>194</v>
+        <v>170</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH28" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="AI28" t="s" s="2">
         <v>77</v>
@@ -5237,16 +5482,16 @@
         <v>96</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>195</v>
+        <v>177</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>77</v>
+        <v>178</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>77</v>
+        <v>179</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>127</v>
+        <v>180</v>
       </c>
       <c r="AO28" t="s" s="2">
         <v>77</v>
@@ -5254,10 +5499,10 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>249</v>
+        <v>257</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>197</v>
+        <v>184</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5265,35 +5510,31 @@
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
-        <v>84</v>
+        <v>75</v>
       </c>
       <c r="G29" t="s" s="2">
         <v>84</v>
       </c>
       <c r="H29" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="I29" t="s" s="2">
         <v>77</v>
       </c>
       <c r="J29" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>198</v>
+        <v>185</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>199</v>
+        <v>186</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>200</v>
-      </c>
-      <c r="N29" t="s" s="2">
-        <v>201</v>
-      </c>
-      <c r="O29" t="s" s="2">
-        <v>202</v>
-      </c>
+        <v>187</v>
+      </c>
+      <c r="N29" s="2"/>
+      <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
         <v>77</v>
       </c>
@@ -5317,13 +5558,13 @@
         <v>77</v>
       </c>
       <c r="X29" t="s" s="2">
-        <v>203</v>
+        <v>77</v>
       </c>
       <c r="Y29" t="s" s="2">
-        <v>204</v>
+        <v>77</v>
       </c>
       <c r="Z29" t="s" s="2">
-        <v>205</v>
+        <v>77</v>
       </c>
       <c r="AA29" t="s" s="2">
         <v>77</v>
@@ -5341,7 +5582,7 @@
         <v>77</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>206</v>
+        <v>188</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>75</v>
@@ -5353,10 +5594,10 @@
         <v>77</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>96</v>
+        <v>77</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>195</v>
+        <v>189</v>
       </c>
       <c r="AL29" t="s" s="2">
         <v>77</v>
@@ -5365,7 +5606,7 @@
         <v>77</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>207</v>
+        <v>77</v>
       </c>
       <c r="AO29" t="s" s="2">
         <v>77</v>
@@ -5373,21 +5614,21 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>250</v>
+        <v>258</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>209</v>
+        <v>191</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
-        <v>77</v>
+        <v>164</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
         <v>75</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="H30" t="s" s="2">
         <v>77</v>
@@ -5396,23 +5637,21 @@
         <v>77</v>
       </c>
       <c r="J30" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>98</v>
+        <v>130</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>210</v>
+        <v>192</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>211</v>
+        <v>193</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>212</v>
-      </c>
-      <c r="O30" t="s" s="2">
-        <v>213</v>
-      </c>
+        <v>167</v>
+      </c>
+      <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
         <v>77</v>
       </c>
@@ -5424,7 +5663,7 @@
         <v>77</v>
       </c>
       <c r="T30" t="s" s="2">
-        <v>214</v>
+        <v>77</v>
       </c>
       <c r="U30" t="s" s="2">
         <v>77</v>
@@ -5448,34 +5687,34 @@
         <v>77</v>
       </c>
       <c r="AB30" t="s" s="2">
-        <v>77</v>
+        <v>133</v>
       </c>
       <c r="AC30" t="s" s="2">
-        <v>77</v>
+        <v>194</v>
       </c>
       <c r="AD30" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE30" t="s" s="2">
-        <v>77</v>
+        <v>134</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>215</v>
+        <v>195</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="AI30" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>96</v>
+        <v>136</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>216</v>
+        <v>189</v>
       </c>
       <c r="AL30" t="s" s="2">
         <v>77</v>
@@ -5484,7 +5723,7 @@
         <v>77</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>217</v>
+        <v>77</v>
       </c>
       <c r="AO30" t="s" s="2">
         <v>77</v>
@@ -5492,10 +5731,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>251</v>
+        <v>259</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>219</v>
+        <v>197</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5503,33 +5742,35 @@
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
-        <v>84</v>
+        <v>75</v>
       </c>
       <c r="G31" t="s" s="2">
         <v>84</v>
       </c>
       <c r="H31" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I31" t="s" s="2">
         <v>85</v>
-      </c>
-      <c r="I31" t="s" s="2">
-        <v>77</v>
       </c>
       <c r="J31" t="s" s="2">
         <v>85</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>174</v>
+        <v>104</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>220</v>
+        <v>198</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>221</v>
+        <v>199</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>222</v>
-      </c>
-      <c r="O31" s="2"/>
+        <v>200</v>
+      </c>
+      <c r="O31" t="s" s="2">
+        <v>201</v>
+      </c>
       <c r="P31" t="s" s="2">
         <v>77</v>
       </c>
@@ -5541,7 +5782,7 @@
         <v>77</v>
       </c>
       <c r="T31" t="s" s="2">
-        <v>223</v>
+        <v>77</v>
       </c>
       <c r="U31" t="s" s="2">
         <v>77</v>
@@ -5553,13 +5794,13 @@
         <v>77</v>
       </c>
       <c r="X31" t="s" s="2">
-        <v>77</v>
+        <v>202</v>
       </c>
       <c r="Y31" t="s" s="2">
-        <v>77</v>
+        <v>203</v>
       </c>
       <c r="Z31" t="s" s="2">
-        <v>77</v>
+        <v>204</v>
       </c>
       <c r="AA31" t="s" s="2">
         <v>77</v>
@@ -5577,7 +5818,7 @@
         <v>77</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>224</v>
+        <v>205</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>75</v>
@@ -5592,7 +5833,7 @@
         <v>96</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>225</v>
+        <v>206</v>
       </c>
       <c r="AL31" t="s" s="2">
         <v>77</v>
@@ -5601,7 +5842,7 @@
         <v>77</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>226</v>
+        <v>127</v>
       </c>
       <c r="AO31" t="s" s="2">
         <v>77</v>
@@ -5609,10 +5850,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>252</v>
+        <v>260</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>228</v>
+        <v>208</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5620,13 +5861,13 @@
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="G32" t="s" s="2">
         <v>84</v>
       </c>
       <c r="H32" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="I32" t="s" s="2">
         <v>77</v>
@@ -5635,16 +5876,20 @@
         <v>85</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>229</v>
+        <v>209</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>230</v>
+        <v>210</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>231</v>
-      </c>
-      <c r="N32" s="2"/>
-      <c r="O32" s="2"/>
+        <v>211</v>
+      </c>
+      <c r="N32" t="s" s="2">
+        <v>212</v>
+      </c>
+      <c r="O32" t="s" s="2">
+        <v>213</v>
+      </c>
       <c r="P32" t="s" s="2">
         <v>77</v>
       </c>
@@ -5668,13 +5913,13 @@
         <v>77</v>
       </c>
       <c r="X32" t="s" s="2">
-        <v>77</v>
+        <v>214</v>
       </c>
       <c r="Y32" t="s" s="2">
-        <v>77</v>
+        <v>215</v>
       </c>
       <c r="Z32" t="s" s="2">
-        <v>77</v>
+        <v>216</v>
       </c>
       <c r="AA32" t="s" s="2">
         <v>77</v>
@@ -5692,7 +5937,7 @@
         <v>77</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>232</v>
+        <v>217</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>75</v>
@@ -5707,7 +5952,7 @@
         <v>96</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>233</v>
+        <v>206</v>
       </c>
       <c r="AL32" t="s" s="2">
         <v>77</v>
@@ -5716,7 +5961,7 @@
         <v>77</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>234</v>
+        <v>218</v>
       </c>
       <c r="AO32" t="s" s="2">
         <v>77</v>
@@ -5724,10 +5969,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>253</v>
+        <v>261</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>236</v>
+        <v>220</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5750,18 +5995,20 @@
         <v>85</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>237</v>
+        <v>98</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>238</v>
+        <v>221</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>239</v>
+        <v>222</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>240</v>
-      </c>
-      <c r="O33" s="2"/>
+        <v>223</v>
+      </c>
+      <c r="O33" t="s" s="2">
+        <v>224</v>
+      </c>
       <c r="P33" t="s" s="2">
         <v>77</v>
       </c>
@@ -5773,7 +6020,7 @@
         <v>77</v>
       </c>
       <c r="T33" t="s" s="2">
-        <v>77</v>
+        <v>225</v>
       </c>
       <c r="U33" t="s" s="2">
         <v>77</v>
@@ -5809,7 +6056,7 @@
         <v>77</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>241</v>
+        <v>226</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>75</v>
@@ -5824,7 +6071,7 @@
         <v>96</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>242</v>
+        <v>227</v>
       </c>
       <c r="AL33" t="s" s="2">
         <v>77</v>
@@ -5833,7 +6080,7 @@
         <v>77</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>243</v>
+        <v>228</v>
       </c>
       <c r="AO33" t="s" s="2">
         <v>77</v>
@@ -5841,10 +6088,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>254</v>
+        <v>262</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>254</v>
+        <v>230</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5852,41 +6099,37 @@
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="G34" t="s" s="2">
         <v>84</v>
       </c>
       <c r="H34" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="I34" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="J34" t="s" s="2">
         <v>85</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>255</v>
+        <v>185</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>256</v>
+        <v>231</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>257</v>
+        <v>232</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>258</v>
-      </c>
-      <c r="O34" t="s" s="2">
-        <v>259</v>
-      </c>
+        <v>233</v>
+      </c>
+      <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
         <v>77</v>
       </c>
-      <c r="Q34" t="s" s="2">
-        <v>260</v>
-      </c>
+      <c r="Q34" s="2"/>
       <c r="R34" t="s" s="2">
         <v>77</v>
       </c>
@@ -5894,7 +6137,7 @@
         <v>77</v>
       </c>
       <c r="T34" t="s" s="2">
-        <v>77</v>
+        <v>234</v>
       </c>
       <c r="U34" t="s" s="2">
         <v>77</v>
@@ -5930,7 +6173,7 @@
         <v>77</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>254</v>
+        <v>235</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>75</v>
@@ -5945,16 +6188,16 @@
         <v>96</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>261</v>
+        <v>236</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>178</v>
+        <v>77</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>262</v>
+        <v>77</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>77</v>
+        <v>237</v>
       </c>
       <c r="AO34" t="s" s="2">
         <v>77</v>
@@ -5965,7 +6208,7 @@
         <v>263</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>263</v>
+        <v>239</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5973,13 +6216,13 @@
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
-        <v>84</v>
+        <v>75</v>
       </c>
       <c r="G35" t="s" s="2">
         <v>84</v>
       </c>
       <c r="H35" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="I35" t="s" s="2">
         <v>77</v>
@@ -5988,20 +6231,16 @@
         <v>85</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>264</v>
+        <v>240</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>265</v>
+        <v>241</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>266</v>
-      </c>
-      <c r="N35" t="s" s="2">
-        <v>267</v>
-      </c>
-      <c r="O35" t="s" s="2">
-        <v>268</v>
-      </c>
+        <v>242</v>
+      </c>
+      <c r="N35" s="2"/>
+      <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
         <v>77</v>
       </c>
@@ -6037,25 +6276,25 @@
         <v>77</v>
       </c>
       <c r="AB35" t="s" s="2">
-        <v>164</v>
+        <v>77</v>
       </c>
       <c r="AC35" t="s" s="2">
-        <v>269</v>
+        <v>77</v>
       </c>
       <c r="AD35" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE35" t="s" s="2">
-        <v>134</v>
+        <v>77</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>263</v>
+        <v>243</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH35" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="AI35" t="s" s="2">
         <v>77</v>
@@ -6064,16 +6303,16 @@
         <v>96</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>270</v>
+        <v>244</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>271</v>
+        <v>77</v>
       </c>
       <c r="AM35" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>272</v>
+        <v>245</v>
       </c>
       <c r="AO35" t="s" s="2">
         <v>77</v>
@@ -6081,10 +6320,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>273</v>
+        <v>264</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>273</v>
+        <v>247</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6104,18 +6343,20 @@
         <v>77</v>
       </c>
       <c r="J36" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>174</v>
+        <v>248</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>175</v>
+        <v>249</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>176</v>
-      </c>
-      <c r="N36" s="2"/>
+        <v>250</v>
+      </c>
+      <c r="N36" t="s" s="2">
+        <v>251</v>
+      </c>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
         <v>77</v>
@@ -6164,7 +6405,7 @@
         <v>77</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>177</v>
+        <v>252</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>75</v>
@@ -6176,10 +6417,10 @@
         <v>77</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>77</v>
+        <v>96</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>178</v>
+        <v>253</v>
       </c>
       <c r="AL36" t="s" s="2">
         <v>77</v>
@@ -6188,7 +6429,7 @@
         <v>77</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>77</v>
+        <v>254</v>
       </c>
       <c r="AO36" t="s" s="2">
         <v>77</v>
@@ -6196,48 +6437,52 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>274</v>
+        <v>265</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>274</v>
+        <v>265</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
-        <v>153</v>
+        <v>77</v>
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
         <v>75</v>
       </c>
       <c r="G37" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="H37" t="s" s="2">
         <v>77</v>
       </c>
       <c r="I37" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="J37" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>130</v>
+        <v>266</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>181</v>
+        <v>267</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>182</v>
+        <v>268</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>156</v>
-      </c>
-      <c r="O37" s="2"/>
+        <v>269</v>
+      </c>
+      <c r="O37" t="s" s="2">
+        <v>270</v>
+      </c>
       <c r="P37" t="s" s="2">
         <v>77</v>
       </c>
-      <c r="Q37" s="2"/>
+      <c r="Q37" t="s" s="2">
+        <v>271</v>
+      </c>
       <c r="R37" t="s" s="2">
         <v>77</v>
       </c>
@@ -6269,40 +6514,40 @@
         <v>77</v>
       </c>
       <c r="AB37" t="s" s="2">
-        <v>133</v>
+        <v>77</v>
       </c>
       <c r="AC37" t="s" s="2">
-        <v>183</v>
+        <v>77</v>
       </c>
       <c r="AD37" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE37" t="s" s="2">
-        <v>134</v>
+        <v>77</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>184</v>
+        <v>265</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH37" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="AI37" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>136</v>
+        <v>96</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>178</v>
+        <v>272</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>77</v>
+        <v>189</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>77</v>
+        <v>273</v>
       </c>
       <c r="AN37" t="s" s="2">
         <v>77</v>
@@ -6313,10 +6558,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6324,22 +6569,22 @@
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="G38" t="s" s="2">
         <v>84</v>
       </c>
       <c r="H38" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="I38" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="J38" t="s" s="2">
         <v>85</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>104</v>
+        <v>275</v>
       </c>
       <c r="L38" t="s" s="2">
         <v>276</v>
@@ -6361,52 +6606,52 @@
         <v>77</v>
       </c>
       <c r="S38" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T38" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U38" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V38" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W38" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X38" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y38" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z38" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA38" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB38" t="s" s="2">
+        <v>175</v>
+      </c>
+      <c r="AC38" t="s" s="2">
         <v>280</v>
       </c>
-      <c r="T38" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U38" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V38" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W38" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X38" t="s" s="2">
-        <v>191</v>
-      </c>
-      <c r="Y38" t="s" s="2">
-        <v>281</v>
-      </c>
-      <c r="Z38" t="s" s="2">
-        <v>282</v>
-      </c>
-      <c r="AA38" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB38" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC38" t="s" s="2">
-        <v>77</v>
-      </c>
       <c r="AD38" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE38" t="s" s="2">
-        <v>77</v>
+        <v>134</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>283</v>
+        <v>274</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH38" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="AI38" t="s" s="2">
         <v>77</v>
@@ -6415,16 +6660,16 @@
         <v>96</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>77</v>
+        <v>282</v>
       </c>
       <c r="AM38" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="AO38" t="s" s="2">
         <v>77</v>
@@ -6432,10 +6677,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6443,35 +6688,31 @@
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
-        <v>84</v>
+        <v>75</v>
       </c>
       <c r="G39" t="s" s="2">
         <v>84</v>
       </c>
       <c r="H39" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="I39" t="s" s="2">
         <v>77</v>
       </c>
       <c r="J39" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>174</v>
+        <v>185</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>287</v>
+        <v>186</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>288</v>
-      </c>
-      <c r="N39" t="s" s="2">
-        <v>289</v>
-      </c>
-      <c r="O39" t="s" s="2">
-        <v>290</v>
-      </c>
+        <v>187</v>
+      </c>
+      <c r="N39" s="2"/>
+      <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
         <v>77</v>
       </c>
@@ -6519,7 +6760,7 @@
         <v>77</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>291</v>
+        <v>188</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>75</v>
@@ -6531,10 +6772,10 @@
         <v>77</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>96</v>
+        <v>77</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>292</v>
+        <v>189</v>
       </c>
       <c r="AL39" t="s" s="2">
         <v>77</v>
@@ -6543,7 +6784,7 @@
         <v>77</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>293</v>
+        <v>77</v>
       </c>
       <c r="AO39" t="s" s="2">
         <v>77</v>
@@ -6551,21 +6792,21 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>294</v>
+        <v>285</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>294</v>
+        <v>285</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>295</v>
+        <v>164</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
         <v>75</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="H40" t="s" s="2">
         <v>77</v>
@@ -6574,19 +6815,19 @@
         <v>77</v>
       </c>
       <c r="J40" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>174</v>
+        <v>130</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>296</v>
+        <v>192</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>297</v>
+        <v>193</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>298</v>
+        <v>167</v>
       </c>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
@@ -6624,34 +6865,34 @@
         <v>77</v>
       </c>
       <c r="AB40" t="s" s="2">
-        <v>77</v>
+        <v>133</v>
       </c>
       <c r="AC40" t="s" s="2">
-        <v>77</v>
+        <v>194</v>
       </c>
       <c r="AD40" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE40" t="s" s="2">
-        <v>77</v>
+        <v>134</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>299</v>
+        <v>195</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH40" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="AI40" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>96</v>
+        <v>136</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>300</v>
+        <v>189</v>
       </c>
       <c r="AL40" t="s" s="2">
         <v>77</v>
@@ -6660,7 +6901,7 @@
         <v>77</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>301</v>
+        <v>77</v>
       </c>
       <c r="AO40" t="s" s="2">
         <v>77</v>
@@ -6668,44 +6909,46 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>302</v>
+        <v>286</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>302</v>
+        <v>286</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
-        <v>303</v>
+        <v>77</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
-        <v>84</v>
+        <v>75</v>
       </c>
       <c r="G41" t="s" s="2">
         <v>84</v>
       </c>
       <c r="H41" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I41" t="s" s="2">
         <v>85</v>
-      </c>
-      <c r="I41" t="s" s="2">
-        <v>77</v>
       </c>
       <c r="J41" t="s" s="2">
         <v>85</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>174</v>
+        <v>104</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>304</v>
+        <v>287</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>305</v>
+        <v>288</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>306</v>
-      </c>
-      <c r="O41" s="2"/>
+        <v>289</v>
+      </c>
+      <c r="O41" t="s" s="2">
+        <v>290</v>
+      </c>
       <c r="P41" t="s" s="2">
         <v>77</v>
       </c>
@@ -6714,7 +6957,7 @@
         <v>77</v>
       </c>
       <c r="S41" t="s" s="2">
-        <v>77</v>
+        <v>291</v>
       </c>
       <c r="T41" t="s" s="2">
         <v>77</v>
@@ -6729,13 +6972,13 @@
         <v>77</v>
       </c>
       <c r="X41" t="s" s="2">
-        <v>77</v>
+        <v>202</v>
       </c>
       <c r="Y41" t="s" s="2">
-        <v>77</v>
+        <v>292</v>
       </c>
       <c r="Z41" t="s" s="2">
-        <v>77</v>
+        <v>293</v>
       </c>
       <c r="AA41" t="s" s="2">
         <v>77</v>
@@ -6753,13 +6996,13 @@
         <v>77</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>307</v>
+        <v>294</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH41" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="AI41" t="s" s="2">
         <v>77</v>
@@ -6768,7 +7011,7 @@
         <v>96</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>308</v>
+        <v>295</v>
       </c>
       <c r="AL41" t="s" s="2">
         <v>77</v>
@@ -6777,7 +7020,7 @@
         <v>77</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>309</v>
+        <v>296</v>
       </c>
       <c r="AO41" t="s" s="2">
         <v>77</v>
@@ -6785,10 +7028,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>310</v>
+        <v>297</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>310</v>
+        <v>297</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6796,13 +7039,13 @@
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="H42" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="I42" t="s" s="2">
         <v>77</v>
@@ -6811,16 +7054,20 @@
         <v>85</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>174</v>
+        <v>185</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>311</v>
+        <v>298</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>312</v>
-      </c>
-      <c r="N42" s="2"/>
-      <c r="O42" s="2"/>
+        <v>299</v>
+      </c>
+      <c r="N42" t="s" s="2">
+        <v>300</v>
+      </c>
+      <c r="O42" t="s" s="2">
+        <v>301</v>
+      </c>
       <c r="P42" t="s" s="2">
         <v>77</v>
       </c>
@@ -6868,13 +7115,13 @@
         <v>77</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>313</v>
+        <v>302</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH42" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="AI42" t="s" s="2">
         <v>77</v>
@@ -6883,7 +7130,7 @@
         <v>96</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>314</v>
+        <v>303</v>
       </c>
       <c r="AL42" t="s" s="2">
         <v>77</v>
@@ -6892,7 +7139,7 @@
         <v>77</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>315</v>
+        <v>304</v>
       </c>
       <c r="AO42" t="s" s="2">
         <v>77</v>
@@ -6900,21 +7147,21 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>316</v>
+        <v>305</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>316</v>
+        <v>305</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>77</v>
+        <v>306</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
         <v>75</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="H43" t="s" s="2">
         <v>77</v>
@@ -6926,15 +7173,17 @@
         <v>85</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>174</v>
+        <v>185</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>317</v>
+        <v>307</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>318</v>
-      </c>
-      <c r="N43" s="2"/>
+        <v>308</v>
+      </c>
+      <c r="N43" t="s" s="2">
+        <v>309</v>
+      </c>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
         <v>77</v>
@@ -6983,13 +7232,13 @@
         <v>77</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>319</v>
+        <v>310</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH43" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="AI43" t="s" s="2">
         <v>77</v>
@@ -6998,7 +7247,7 @@
         <v>96</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>320</v>
+        <v>311</v>
       </c>
       <c r="AL43" t="s" s="2">
         <v>77</v>
@@ -7007,7 +7256,7 @@
         <v>77</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>321</v>
+        <v>312</v>
       </c>
       <c r="AO43" t="s" s="2">
         <v>77</v>
@@ -7015,24 +7264,24 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>322</v>
+        <v>313</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>322</v>
+        <v>313</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>77</v>
+        <v>314</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="G44" t="s" s="2">
         <v>84</v>
       </c>
       <c r="H44" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="I44" t="s" s="2">
         <v>77</v>
@@ -7041,18 +7290,18 @@
         <v>85</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>229</v>
+        <v>185</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>323</v>
+        <v>315</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>324</v>
-      </c>
-      <c r="N44" s="2"/>
-      <c r="O44" t="s" s="2">
-        <v>325</v>
-      </c>
+        <v>316</v>
+      </c>
+      <c r="N44" t="s" s="2">
+        <v>317</v>
+      </c>
+      <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
         <v>77</v>
       </c>
@@ -7100,13 +7349,13 @@
         <v>77</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>326</v>
+        <v>318</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH44" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="AI44" t="s" s="2">
         <v>77</v>
@@ -7115,7 +7364,7 @@
         <v>96</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>327</v>
+        <v>319</v>
       </c>
       <c r="AL44" t="s" s="2">
         <v>77</v>
@@ -7124,7 +7373,7 @@
         <v>77</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>328</v>
+        <v>320</v>
       </c>
       <c r="AO44" t="s" s="2">
         <v>77</v>
@@ -7132,26 +7381,24 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>329</v>
+        <v>321</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>263</v>
-      </c>
-      <c r="C45" t="s" s="2">
-        <v>171</v>
-      </c>
+        <v>321</v>
+      </c>
+      <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
         <v>77</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
-        <v>84</v>
+        <v>75</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="H45" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="I45" t="s" s="2">
         <v>77</v>
@@ -7160,20 +7407,16 @@
         <v>85</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>264</v>
+        <v>185</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>265</v>
+        <v>322</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>266</v>
-      </c>
-      <c r="N45" t="s" s="2">
-        <v>267</v>
-      </c>
-      <c r="O45" t="s" s="2">
-        <v>268</v>
-      </c>
+        <v>323</v>
+      </c>
+      <c r="N45" s="2"/>
+      <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
         <v>77</v>
       </c>
@@ -7221,7 +7464,7 @@
         <v>77</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>263</v>
+        <v>324</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>75</v>
@@ -7236,16 +7479,16 @@
         <v>96</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>270</v>
+        <v>325</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>271</v>
+        <v>77</v>
       </c>
       <c r="AM45" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>272</v>
+        <v>326</v>
       </c>
       <c r="AO45" t="s" s="2">
         <v>77</v>
@@ -7253,14 +7496,12 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>263</v>
-      </c>
-      <c r="C46" t="s" s="2">
-        <v>245</v>
-      </c>
+        <v>327</v>
+      </c>
+      <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
         <v>77</v>
       </c>
@@ -7269,10 +7510,10 @@
         <v>75</v>
       </c>
       <c r="G46" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="H46" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="I46" t="s" s="2">
         <v>77</v>
@@ -7281,20 +7522,16 @@
         <v>85</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>264</v>
+        <v>185</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>265</v>
+        <v>328</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>266</v>
-      </c>
-      <c r="N46" t="s" s="2">
-        <v>267</v>
-      </c>
-      <c r="O46" t="s" s="2">
-        <v>268</v>
-      </c>
+        <v>329</v>
+      </c>
+      <c r="N46" s="2"/>
+      <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
         <v>77</v>
       </c>
@@ -7342,7 +7579,7 @@
         <v>77</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>263</v>
+        <v>330</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>75</v>
@@ -7357,16 +7594,16 @@
         <v>96</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>270</v>
+        <v>331</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>271</v>
+        <v>77</v>
       </c>
       <c r="AM46" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>272</v>
+        <v>332</v>
       </c>
       <c r="AO46" t="s" s="2">
         <v>77</v>
@@ -7374,10 +7611,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7388,7 +7625,7 @@
         <v>75</v>
       </c>
       <c r="G47" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="H47" t="s" s="2">
         <v>77</v>
@@ -7400,17 +7637,15 @@
         <v>85</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>332</v>
+        <v>240</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>334</v>
-      </c>
-      <c r="N47" t="s" s="2">
         <v>335</v>
       </c>
+      <c r="N47" s="2"/>
       <c r="O47" t="s" s="2">
         <v>336</v>
       </c>
@@ -7461,13 +7696,13 @@
         <v>77</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>331</v>
+        <v>337</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH47" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="AI47" t="s" s="2">
         <v>77</v>
@@ -7476,10 +7711,10 @@
         <v>96</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>338</v>
+        <v>77</v>
       </c>
       <c r="AM47" t="s" s="2">
         <v>77</v>
@@ -7496,21 +7731,23 @@
         <v>340</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>340</v>
-      </c>
-      <c r="C48" s="2"/>
+        <v>274</v>
+      </c>
+      <c r="C48" t="s" s="2">
+        <v>182</v>
+      </c>
       <c r="D48" t="s" s="2">
         <v>77</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="G48" t="s" s="2">
         <v>84</v>
       </c>
       <c r="H48" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="I48" t="s" s="2">
         <v>77</v>
@@ -7519,19 +7756,19 @@
         <v>85</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>104</v>
+        <v>275</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>341</v>
+        <v>276</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>342</v>
+        <v>277</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>343</v>
+        <v>278</v>
       </c>
       <c r="O48" t="s" s="2">
-        <v>344</v>
+        <v>279</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>77</v>
@@ -7556,13 +7793,13 @@
         <v>77</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>191</v>
+        <v>77</v>
       </c>
       <c r="Y48" t="s" s="2">
-        <v>345</v>
+        <v>77</v>
       </c>
       <c r="Z48" t="s" s="2">
-        <v>346</v>
+        <v>77</v>
       </c>
       <c r="AA48" t="s" s="2">
         <v>77</v>
@@ -7580,13 +7817,13 @@
         <v>77</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>340</v>
+        <v>274</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH48" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="AI48" t="s" s="2">
         <v>77</v>
@@ -7595,16 +7832,16 @@
         <v>96</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>347</v>
+        <v>281</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>348</v>
+        <v>282</v>
       </c>
       <c r="AM48" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>349</v>
+        <v>283</v>
       </c>
       <c r="AO48" t="s" s="2">
         <v>77</v>
@@ -7612,18 +7849,20 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>350</v>
+        <v>341</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>350</v>
-      </c>
-      <c r="C49" s="2"/>
+        <v>274</v>
+      </c>
+      <c r="C49" t="s" s="2">
+        <v>256</v>
+      </c>
       <c r="D49" t="s" s="2">
         <v>77</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
-        <v>84</v>
+        <v>75</v>
       </c>
       <c r="G49" t="s" s="2">
         <v>84</v>
@@ -7638,19 +7877,19 @@
         <v>85</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>351</v>
+        <v>275</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>352</v>
+        <v>276</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>353</v>
+        <v>277</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>354</v>
+        <v>278</v>
       </c>
       <c r="O49" t="s" s="2">
-        <v>355</v>
+        <v>279</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>77</v>
@@ -7699,13 +7938,13 @@
         <v>77</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>350</v>
+        <v>274</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH49" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="AI49" t="s" s="2">
         <v>77</v>
@@ -7714,27 +7953,27 @@
         <v>96</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>356</v>
+        <v>281</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>357</v>
+        <v>282</v>
       </c>
       <c r="AM49" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>358</v>
+        <v>283</v>
       </c>
       <c r="AO49" t="s" s="2">
-        <v>359</v>
+        <v>77</v>
       </c>
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>360</v>
+        <v>342</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>360</v>
+        <v>342</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7742,34 +7981,34 @@
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
-        <v>75</v>
+        <v>343</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="H50" t="s" s="2">
         <v>77</v>
       </c>
       <c r="I50" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="J50" t="s" s="2">
         <v>85</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>361</v>
+        <v>344</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>362</v>
+        <v>345</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>363</v>
+        <v>346</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>364</v>
+        <v>347</v>
       </c>
       <c r="O50" t="s" s="2">
-        <v>365</v>
+        <v>348</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>77</v>
@@ -7806,25 +8045,25 @@
         <v>77</v>
       </c>
       <c r="AB50" t="s" s="2">
-        <v>77</v>
+        <v>175</v>
       </c>
       <c r="AC50" t="s" s="2">
-        <v>77</v>
+        <v>349</v>
       </c>
       <c r="AD50" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE50" t="s" s="2">
-        <v>77</v>
+        <v>134</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>360</v>
+        <v>342</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH50" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="AI50" t="s" s="2">
         <v>77</v>
@@ -7833,16 +8072,16 @@
         <v>96</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>366</v>
+        <v>350</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>178</v>
+        <v>351</v>
       </c>
       <c r="AM50" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>367</v>
+        <v>352</v>
       </c>
       <c r="AO50" t="s" s="2">
         <v>77</v>
@@ -7850,24 +8089,26 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>368</v>
+        <v>353</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>368</v>
-      </c>
-      <c r="C51" s="2"/>
+        <v>342</v>
+      </c>
+      <c r="C51" t="s" s="2">
+        <v>354</v>
+      </c>
       <c r="D51" t="s" s="2">
         <v>77</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="G51" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="H51" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="I51" t="s" s="2">
         <v>77</v>
@@ -7876,19 +8117,19 @@
         <v>85</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>369</v>
+        <v>344</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>370</v>
+        <v>345</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>371</v>
+        <v>346</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>372</v>
+        <v>347</v>
       </c>
       <c r="O51" t="s" s="2">
-        <v>373</v>
+        <v>348</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>77</v>
@@ -7937,7 +8178,7 @@
         <v>77</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>368</v>
+        <v>342</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>75</v>
@@ -7952,16 +8193,16 @@
         <v>96</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>374</v>
+        <v>350</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>375</v>
+        <v>351</v>
       </c>
       <c r="AM51" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>376</v>
+        <v>352</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>77</v>
@@ -7969,10 +8210,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>377</v>
+        <v>355</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>377</v>
+        <v>356</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7995,18 +8236,16 @@
         <v>77</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>198</v>
+        <v>185</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>378</v>
+        <v>186</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>379</v>
+        <v>187</v>
       </c>
       <c r="N52" s="2"/>
-      <c r="O52" t="s" s="2">
-        <v>380</v>
-      </c>
+      <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
         <v>77</v>
       </c>
@@ -8030,13 +8269,13 @@
         <v>77</v>
       </c>
       <c r="X52" t="s" s="2">
-        <v>203</v>
+        <v>77</v>
       </c>
       <c r="Y52" t="s" s="2">
-        <v>381</v>
+        <v>77</v>
       </c>
       <c r="Z52" t="s" s="2">
-        <v>382</v>
+        <v>77</v>
       </c>
       <c r="AA52" t="s" s="2">
         <v>77</v>
@@ -8054,7 +8293,7 @@
         <v>77</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>377</v>
+        <v>188</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>75</v>
@@ -8066,19 +8305,19 @@
         <v>77</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>96</v>
+        <v>77</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>383</v>
+        <v>189</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>384</v>
+        <v>77</v>
       </c>
       <c r="AM52" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>385</v>
+        <v>77</v>
       </c>
       <c r="AO52" t="s" s="2">
         <v>77</v>
@@ -8086,21 +8325,21 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>386</v>
+        <v>357</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>386</v>
+        <v>358</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
-        <v>77</v>
+        <v>164</v>
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
         <v>75</v>
       </c>
       <c r="G53" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="H53" t="s" s="2">
         <v>77</v>
@@ -8112,20 +8351,18 @@
         <v>77</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>387</v>
+        <v>130</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>388</v>
+        <v>192</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>389</v>
+        <v>193</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>390</v>
-      </c>
-      <c r="O53" t="s" s="2">
-        <v>391</v>
-      </c>
+        <v>167</v>
+      </c>
+      <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
         <v>77</v>
       </c>
@@ -8161,43 +8398,43 @@
         <v>77</v>
       </c>
       <c r="AB53" t="s" s="2">
-        <v>77</v>
+        <v>133</v>
       </c>
       <c r="AC53" t="s" s="2">
-        <v>77</v>
+        <v>194</v>
       </c>
       <c r="AD53" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE53" t="s" s="2">
-        <v>77</v>
+        <v>134</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>386</v>
+        <v>195</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH53" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="AI53" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>96</v>
+        <v>136</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>392</v>
+        <v>189</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>178</v>
+        <v>77</v>
       </c>
       <c r="AM53" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>393</v>
+        <v>77</v>
       </c>
       <c r="AO53" t="s" s="2">
         <v>77</v>
@@ -8205,10 +8442,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>394</v>
+        <v>359</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>394</v>
+        <v>360</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8219,7 +8456,7 @@
         <v>75</v>
       </c>
       <c r="G54" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="H54" t="s" s="2">
         <v>77</v>
@@ -8228,23 +8465,19 @@
         <v>77</v>
       </c>
       <c r="J54" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>395</v>
+        <v>104</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>396</v>
+        <v>361</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>397</v>
-      </c>
-      <c r="N54" t="s" s="2">
-        <v>398</v>
-      </c>
-      <c r="O54" t="s" s="2">
-        <v>399</v>
-      </c>
+        <v>362</v>
+      </c>
+      <c r="N54" s="2"/>
+      <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
         <v>77</v>
       </c>
@@ -8253,7 +8486,7 @@
         <v>77</v>
       </c>
       <c r="S54" t="s" s="2">
-        <v>77</v>
+        <v>363</v>
       </c>
       <c r="T54" t="s" s="2">
         <v>77</v>
@@ -8268,13 +8501,13 @@
         <v>77</v>
       </c>
       <c r="X54" t="s" s="2">
-        <v>77</v>
+        <v>202</v>
       </c>
       <c r="Y54" t="s" s="2">
-        <v>77</v>
+        <v>364</v>
       </c>
       <c r="Z54" t="s" s="2">
-        <v>77</v>
+        <v>365</v>
       </c>
       <c r="AA54" t="s" s="2">
         <v>77</v>
@@ -8292,31 +8525,31 @@
         <v>77</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>394</v>
+        <v>366</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH54" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="AI54" t="s" s="2">
-        <v>77</v>
+        <v>367</v>
       </c>
       <c r="AJ54" t="s" s="2">
         <v>96</v>
       </c>
       <c r="AK54" t="s" s="2">
-        <v>400</v>
+        <v>368</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>178</v>
+        <v>77</v>
       </c>
       <c r="AM54" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>401</v>
+        <v>369</v>
       </c>
       <c r="AO54" t="s" s="2">
         <v>77</v>
@@ -8324,10 +8557,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>402</v>
+        <v>370</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>402</v>
+        <v>371</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8338,7 +8571,7 @@
         <v>75</v>
       </c>
       <c r="G55" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="H55" t="s" s="2">
         <v>77</v>
@@ -8347,22 +8580,22 @@
         <v>77</v>
       </c>
       <c r="J55" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>403</v>
+        <v>185</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>404</v>
+        <v>372</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>405</v>
+        <v>373</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>406</v>
+        <v>374</v>
       </c>
       <c r="O55" t="s" s="2">
-        <v>407</v>
+        <v>375</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>77</v>
@@ -8411,31 +8644,31 @@
         <v>77</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>402</v>
+        <v>376</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH55" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="AI55" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>408</v>
+        <v>96</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>409</v>
+        <v>377</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>178</v>
+        <v>77</v>
       </c>
       <c r="AM55" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>77</v>
+        <v>378</v>
       </c>
       <c r="AO55" t="s" s="2">
         <v>77</v>
@@ -8443,10 +8676,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>410</v>
+        <v>379</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>410</v>
+        <v>380</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8463,22 +8696,26 @@
         <v>77</v>
       </c>
       <c r="I56" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="J56" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>174</v>
+        <v>104</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>175</v>
+        <v>381</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>176</v>
-      </c>
-      <c r="N56" s="2"/>
-      <c r="O56" s="2"/>
+        <v>382</v>
+      </c>
+      <c r="N56" t="s" s="2">
+        <v>383</v>
+      </c>
+      <c r="O56" t="s" s="2">
+        <v>384</v>
+      </c>
       <c r="P56" t="s" s="2">
         <v>77</v>
       </c>
@@ -8502,13 +8739,13 @@
         <v>77</v>
       </c>
       <c r="X56" t="s" s="2">
-        <v>77</v>
+        <v>202</v>
       </c>
       <c r="Y56" t="s" s="2">
-        <v>77</v>
+        <v>385</v>
       </c>
       <c r="Z56" t="s" s="2">
-        <v>77</v>
+        <v>386</v>
       </c>
       <c r="AA56" t="s" s="2">
         <v>77</v>
@@ -8526,7 +8763,7 @@
         <v>77</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>177</v>
+        <v>387</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>75</v>
@@ -8538,10 +8775,10 @@
         <v>77</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>77</v>
+        <v>96</v>
       </c>
       <c r="AK56" t="s" s="2">
-        <v>178</v>
+        <v>295</v>
       </c>
       <c r="AL56" t="s" s="2">
         <v>77</v>
@@ -8550,7 +8787,7 @@
         <v>77</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>77</v>
+        <v>388</v>
       </c>
       <c r="AO56" t="s" s="2">
         <v>77</v>
@@ -8558,21 +8795,21 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>411</v>
+        <v>389</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>411</v>
+        <v>390</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
-        <v>153</v>
+        <v>77</v>
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
         <v>75</v>
       </c>
       <c r="G57" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="H57" t="s" s="2">
         <v>77</v>
@@ -8581,19 +8818,19 @@
         <v>77</v>
       </c>
       <c r="J57" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>130</v>
+        <v>391</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>181</v>
+        <v>392</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>182</v>
+        <v>393</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>156</v>
+        <v>394</v>
       </c>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
@@ -8604,7 +8841,7 @@
         <v>77</v>
       </c>
       <c r="S57" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="T57" t="s" s="2">
         <v>77</v>
@@ -8643,22 +8880,22 @@
         <v>77</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>184</v>
+        <v>395</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH57" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="AI57" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>136</v>
+        <v>96</v>
       </c>
       <c r="AK57" t="s" s="2">
-        <v>178</v>
+        <v>189</v>
       </c>
       <c r="AL57" t="s" s="2">
         <v>77</v>
@@ -8667,7 +8904,7 @@
         <v>77</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>77</v>
+        <v>189</v>
       </c>
       <c r="AO57" t="s" s="2">
         <v>77</v>
@@ -8675,46 +8912,42 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>412</v>
+        <v>396</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>412</v>
+        <v>397</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
-        <v>413</v>
+        <v>77</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
         <v>75</v>
       </c>
       <c r="G58" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="H58" t="s" s="2">
         <v>77</v>
       </c>
       <c r="I58" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="J58" t="s" s="2">
         <v>85</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>130</v>
+        <v>240</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>414</v>
+        <v>398</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>415</v>
-      </c>
-      <c r="N58" t="s" s="2">
-        <v>156</v>
-      </c>
-      <c r="O58" t="s" s="2">
-        <v>157</v>
-      </c>
+        <v>399</v>
+      </c>
+      <c r="N58" s="2"/>
+      <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
         <v>77</v>
       </c>
@@ -8762,31 +8995,31 @@
         <v>77</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>416</v>
+        <v>400</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH58" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="AI58" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>136</v>
+        <v>96</v>
       </c>
       <c r="AK58" t="s" s="2">
+        <v>338</v>
+      </c>
+      <c r="AL58" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM58" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN58" t="s" s="2">
         <v>127</v>
-      </c>
-      <c r="AL58" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AM58" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN58" t="s" s="2">
-        <v>77</v>
       </c>
       <c r="AO58" t="s" s="2">
         <v>77</v>
@@ -8794,43 +9027,47 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>417</v>
+        <v>401</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>417</v>
-      </c>
-      <c r="C59" s="2"/>
+        <v>342</v>
+      </c>
+      <c r="C59" t="s" s="2">
+        <v>402</v>
+      </c>
       <c r="D59" t="s" s="2">
         <v>77</v>
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="G59" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="H59" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="I59" t="s" s="2">
         <v>77</v>
       </c>
       <c r="J59" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>198</v>
+        <v>344</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>418</v>
+        <v>345</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>419</v>
-      </c>
-      <c r="N59" s="2"/>
+        <v>346</v>
+      </c>
+      <c r="N59" t="s" s="2">
+        <v>347</v>
+      </c>
       <c r="O59" t="s" s="2">
-        <v>420</v>
+        <v>348</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>77</v>
@@ -8855,13 +9092,13 @@
         <v>77</v>
       </c>
       <c r="X59" t="s" s="2">
-        <v>203</v>
+        <v>77</v>
       </c>
       <c r="Y59" t="s" s="2">
-        <v>421</v>
+        <v>77</v>
       </c>
       <c r="Z59" t="s" s="2">
-        <v>422</v>
+        <v>77</v>
       </c>
       <c r="AA59" t="s" s="2">
         <v>77</v>
@@ -8879,7 +9116,7 @@
         <v>77</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>417</v>
+        <v>342</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>75</v>
@@ -8894,16 +9131,16 @@
         <v>96</v>
       </c>
       <c r="AK59" t="s" s="2">
-        <v>423</v>
+        <v>350</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>178</v>
+        <v>351</v>
       </c>
       <c r="AM59" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>424</v>
+        <v>352</v>
       </c>
       <c r="AO59" t="s" s="2">
         <v>77</v>
@@ -8911,10 +9148,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>425</v>
+        <v>403</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>425</v>
+        <v>356</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -8937,18 +9174,16 @@
         <v>77</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>264</v>
+        <v>185</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>426</v>
+        <v>186</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>427</v>
+        <v>187</v>
       </c>
       <c r="N60" s="2"/>
-      <c r="O60" t="s" s="2">
-        <v>428</v>
-      </c>
+      <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
         <v>77</v>
       </c>
@@ -8996,7 +9231,7 @@
         <v>77</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>425</v>
+        <v>188</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>75</v>
@@ -9008,19 +9243,19 @@
         <v>77</v>
       </c>
       <c r="AJ60" t="s" s="2">
-        <v>96</v>
+        <v>77</v>
       </c>
       <c r="AK60" t="s" s="2">
-        <v>270</v>
+        <v>189</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>178</v>
+        <v>77</v>
       </c>
       <c r="AM60" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>429</v>
+        <v>77</v>
       </c>
       <c r="AO60" t="s" s="2">
         <v>77</v>
@@ -9028,14 +9263,14 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>430</v>
+        <v>404</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>430</v>
+        <v>358</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
-        <v>77</v>
+        <v>164</v>
       </c>
       <c r="E61" s="2"/>
       <c r="F61" t="s" s="2">
@@ -9054,20 +9289,18 @@
         <v>77</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>332</v>
+        <v>130</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>431</v>
+        <v>192</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>432</v>
+        <v>193</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>433</v>
-      </c>
-      <c r="O61" t="s" s="2">
-        <v>336</v>
-      </c>
+        <v>167</v>
+      </c>
+      <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
         <v>77</v>
       </c>
@@ -9103,19 +9336,19 @@
         <v>77</v>
       </c>
       <c r="AB61" t="s" s="2">
-        <v>77</v>
+        <v>133</v>
       </c>
       <c r="AC61" t="s" s="2">
-        <v>77</v>
+        <v>194</v>
       </c>
       <c r="AD61" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE61" t="s" s="2">
-        <v>77</v>
+        <v>134</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>430</v>
+        <v>195</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>75</v>
@@ -9127,19 +9360,19 @@
         <v>77</v>
       </c>
       <c r="AJ61" t="s" s="2">
-        <v>96</v>
+        <v>136</v>
       </c>
       <c r="AK61" t="s" s="2">
-        <v>337</v>
+        <v>189</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>178</v>
+        <v>77</v>
       </c>
       <c r="AM61" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>434</v>
+        <v>77</v>
       </c>
       <c r="AO61" t="s" s="2">
         <v>77</v>
@@ -9147,10 +9380,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>435</v>
+        <v>405</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>435</v>
+        <v>360</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9170,21 +9403,19 @@
         <v>77</v>
       </c>
       <c r="J62" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>369</v>
+        <v>104</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>436</v>
+        <v>361</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>437</v>
+        <v>362</v>
       </c>
       <c r="N62" s="2"/>
-      <c r="O62" t="s" s="2">
-        <v>438</v>
-      </c>
+      <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
         <v>77</v>
       </c>
@@ -9208,13 +9439,13 @@
         <v>77</v>
       </c>
       <c r="X62" t="s" s="2">
-        <v>77</v>
+        <v>202</v>
       </c>
       <c r="Y62" t="s" s="2">
-        <v>77</v>
+        <v>364</v>
       </c>
       <c r="Z62" t="s" s="2">
-        <v>77</v>
+        <v>365</v>
       </c>
       <c r="AA62" t="s" s="2">
         <v>77</v>
@@ -9232,7 +9463,7 @@
         <v>77</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>435</v>
+        <v>366</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>75</v>
@@ -9241,22 +9472,22 @@
         <v>84</v>
       </c>
       <c r="AI62" t="s" s="2">
-        <v>77</v>
+        <v>367</v>
       </c>
       <c r="AJ62" t="s" s="2">
         <v>96</v>
       </c>
       <c r="AK62" t="s" s="2">
-        <v>374</v>
+        <v>368</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>178</v>
+        <v>77</v>
       </c>
       <c r="AM62" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>439</v>
+        <v>369</v>
       </c>
       <c r="AO62" t="s" s="2">
         <v>77</v>
@@ -9264,10 +9495,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>440</v>
+        <v>406</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>440</v>
+        <v>371</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9287,20 +9518,22 @@
         <v>77</v>
       </c>
       <c r="J63" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>104</v>
+        <v>185</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>341</v>
+        <v>372</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>441</v>
-      </c>
-      <c r="N63" s="2"/>
+        <v>373</v>
+      </c>
+      <c r="N63" t="s" s="2">
+        <v>374</v>
+      </c>
       <c r="O63" t="s" s="2">
-        <v>442</v>
+        <v>375</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>77</v>
@@ -9325,13 +9558,13 @@
         <v>77</v>
       </c>
       <c r="X63" t="s" s="2">
-        <v>191</v>
+        <v>77</v>
       </c>
       <c r="Y63" t="s" s="2">
-        <v>345</v>
+        <v>77</v>
       </c>
       <c r="Z63" t="s" s="2">
-        <v>346</v>
+        <v>77</v>
       </c>
       <c r="AA63" t="s" s="2">
         <v>77</v>
@@ -9349,7 +9582,7 @@
         <v>77</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>440</v>
+        <v>376</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>75</v>
@@ -9364,16 +9597,16 @@
         <v>96</v>
       </c>
       <c r="AK63" t="s" s="2">
-        <v>347</v>
+        <v>377</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>178</v>
+        <v>77</v>
       </c>
       <c r="AM63" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>443</v>
+        <v>378</v>
       </c>
       <c r="AO63" t="s" s="2">
         <v>77</v>
@@ -9381,10 +9614,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>444</v>
+        <v>407</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>444</v>
+        <v>380</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9401,23 +9634,25 @@
         <v>77</v>
       </c>
       <c r="I64" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="J64" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>237</v>
+        <v>104</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>445</v>
+        <v>381</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>446</v>
-      </c>
-      <c r="N64" s="2"/>
+        <v>382</v>
+      </c>
+      <c r="N64" t="s" s="2">
+        <v>383</v>
+      </c>
       <c r="O64" t="s" s="2">
-        <v>447</v>
+        <v>384</v>
       </c>
       <c r="P64" t="s" s="2">
         <v>77</v>
@@ -9442,13 +9677,13 @@
         <v>77</v>
       </c>
       <c r="X64" t="s" s="2">
-        <v>77</v>
+        <v>202</v>
       </c>
       <c r="Y64" t="s" s="2">
-        <v>77</v>
+        <v>385</v>
       </c>
       <c r="Z64" t="s" s="2">
-        <v>77</v>
+        <v>386</v>
       </c>
       <c r="AA64" t="s" s="2">
         <v>77</v>
@@ -9466,7 +9701,7 @@
         <v>77</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>444</v>
+        <v>387</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>75</v>
@@ -9475,22 +9710,22 @@
         <v>84</v>
       </c>
       <c r="AI64" t="s" s="2">
-        <v>448</v>
+        <v>77</v>
       </c>
       <c r="AJ64" t="s" s="2">
         <v>96</v>
       </c>
       <c r="AK64" t="s" s="2">
-        <v>449</v>
+        <v>295</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>178</v>
+        <v>77</v>
       </c>
       <c r="AM64" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>450</v>
+        <v>388</v>
       </c>
       <c r="AO64" t="s" s="2">
         <v>77</v>
@@ -9498,10 +9733,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>451</v>
+        <v>408</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>451</v>
+        <v>390</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9521,18 +9756,20 @@
         <v>77</v>
       </c>
       <c r="J65" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>229</v>
+        <v>391</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>452</v>
+        <v>392</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>453</v>
-      </c>
-      <c r="N65" s="2"/>
+        <v>393</v>
+      </c>
+      <c r="N65" t="s" s="2">
+        <v>394</v>
+      </c>
       <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
         <v>77</v>
@@ -9542,7 +9779,7 @@
         <v>77</v>
       </c>
       <c r="S65" t="s" s="2">
-        <v>77</v>
+        <v>409</v>
       </c>
       <c r="T65" t="s" s="2">
         <v>77</v>
@@ -9581,7 +9818,7 @@
         <v>77</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>451</v>
+        <v>395</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>75</v>
@@ -9596,16 +9833,16 @@
         <v>96</v>
       </c>
       <c r="AK65" t="s" s="2">
-        <v>454</v>
+        <v>189</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>178</v>
+        <v>77</v>
       </c>
       <c r="AM65" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>77</v>
+        <v>189</v>
       </c>
       <c r="AO65" t="s" s="2">
         <v>77</v>
@@ -9613,10 +9850,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>455</v>
+        <v>410</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>455</v>
+        <v>397</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9627,7 +9864,7 @@
         <v>75</v>
       </c>
       <c r="G66" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="H66" t="s" s="2">
         <v>77</v>
@@ -9636,23 +9873,19 @@
         <v>77</v>
       </c>
       <c r="J66" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>403</v>
+        <v>240</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>456</v>
+        <v>398</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>457</v>
-      </c>
-      <c r="N66" t="s" s="2">
-        <v>458</v>
-      </c>
-      <c r="O66" t="s" s="2">
-        <v>459</v>
-      </c>
+        <v>399</v>
+      </c>
+      <c r="N66" s="2"/>
+      <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
         <v>77</v>
       </c>
@@ -9700,13 +9933,13 @@
         <v>77</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>455</v>
+        <v>400</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH66" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="AI66" t="s" s="2">
         <v>77</v>
@@ -9715,16 +9948,16 @@
         <v>96</v>
       </c>
       <c r="AK66" t="s" s="2">
-        <v>460</v>
+        <v>338</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>461</v>
+        <v>77</v>
       </c>
       <c r="AM66" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>77</v>
+        <v>127</v>
       </c>
       <c r="AO66" t="s" s="2">
         <v>77</v>
@@ -9732,42 +9965,48 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>462</v>
+        <v>411</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>462</v>
-      </c>
-      <c r="C67" s="2"/>
+        <v>342</v>
+      </c>
+      <c r="C67" t="s" s="2">
+        <v>412</v>
+      </c>
       <c r="D67" t="s" s="2">
         <v>77</v>
       </c>
       <c r="E67" s="2"/>
       <c r="F67" t="s" s="2">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="G67" t="s" s="2">
         <v>84</v>
       </c>
       <c r="H67" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="I67" t="s" s="2">
         <v>77</v>
       </c>
       <c r="J67" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>174</v>
+        <v>344</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>175</v>
+        <v>345</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>176</v>
-      </c>
-      <c r="N67" s="2"/>
-      <c r="O67" s="2"/>
+        <v>346</v>
+      </c>
+      <c r="N67" t="s" s="2">
+        <v>347</v>
+      </c>
+      <c r="O67" t="s" s="2">
+        <v>348</v>
+      </c>
       <c r="P67" t="s" s="2">
         <v>77</v>
       </c>
@@ -9815,31 +10054,31 @@
         <v>77</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>177</v>
+        <v>342</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH67" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="AI67" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ67" t="s" s="2">
-        <v>77</v>
+        <v>96</v>
       </c>
       <c r="AK67" t="s" s="2">
-        <v>178</v>
+        <v>350</v>
       </c>
       <c r="AL67" t="s" s="2">
-        <v>77</v>
+        <v>351</v>
       </c>
       <c r="AM67" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN67" t="s" s="2">
-        <v>77</v>
+        <v>352</v>
       </c>
       <c r="AO67" t="s" s="2">
         <v>77</v>
@@ -9847,21 +10086,21 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>463</v>
+        <v>413</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>463</v>
+        <v>356</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
-        <v>153</v>
+        <v>77</v>
       </c>
       <c r="E68" s="2"/>
       <c r="F68" t="s" s="2">
         <v>75</v>
       </c>
       <c r="G68" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="H68" t="s" s="2">
         <v>77</v>
@@ -9873,17 +10112,15 @@
         <v>77</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>130</v>
+        <v>185</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>182</v>
-      </c>
-      <c r="N68" t="s" s="2">
-        <v>156</v>
-      </c>
+        <v>187</v>
+      </c>
+      <c r="N68" s="2"/>
       <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
         <v>77</v>
@@ -9932,22 +10169,22 @@
         <v>77</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH68" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="AI68" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ68" t="s" s="2">
-        <v>136</v>
+        <v>77</v>
       </c>
       <c r="AK68" t="s" s="2">
-        <v>178</v>
+        <v>189</v>
       </c>
       <c r="AL68" t="s" s="2">
         <v>77</v>
@@ -9964,14 +10201,14 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>464</v>
+        <v>414</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>464</v>
+        <v>358</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
-        <v>413</v>
+        <v>164</v>
       </c>
       <c r="E69" s="2"/>
       <c r="F69" t="s" s="2">
@@ -9984,26 +10221,24 @@
         <v>77</v>
       </c>
       <c r="I69" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="J69" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="K69" t="s" s="2">
         <v>130</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>414</v>
+        <v>192</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>415</v>
+        <v>193</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>156</v>
-      </c>
-      <c r="O69" t="s" s="2">
-        <v>157</v>
-      </c>
+        <v>167</v>
+      </c>
+      <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
         <v>77</v>
       </c>
@@ -10039,19 +10274,19 @@
         <v>77</v>
       </c>
       <c r="AB69" t="s" s="2">
-        <v>77</v>
+        <v>133</v>
       </c>
       <c r="AC69" t="s" s="2">
-        <v>77</v>
+        <v>194</v>
       </c>
       <c r="AD69" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE69" t="s" s="2">
-        <v>77</v>
+        <v>134</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>416</v>
+        <v>195</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>75</v>
@@ -10066,7 +10301,7 @@
         <v>136</v>
       </c>
       <c r="AK69" t="s" s="2">
-        <v>127</v>
+        <v>189</v>
       </c>
       <c r="AL69" t="s" s="2">
         <v>77</v>
@@ -10083,10 +10318,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>465</v>
+        <v>415</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>465</v>
+        <v>360</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10094,7 +10329,7 @@
       </c>
       <c r="E70" s="2"/>
       <c r="F70" t="s" s="2">
-        <v>84</v>
+        <v>75</v>
       </c>
       <c r="G70" t="s" s="2">
         <v>84</v>
@@ -10106,23 +10341,19 @@
         <v>77</v>
       </c>
       <c r="J70" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>198</v>
+        <v>104</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>466</v>
+        <v>361</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>467</v>
-      </c>
-      <c r="N70" t="s" s="2">
-        <v>468</v>
-      </c>
-      <c r="O70" t="s" s="2">
-        <v>469</v>
-      </c>
+        <v>362</v>
+      </c>
+      <c r="N70" s="2"/>
+      <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
         <v>77</v>
       </c>
@@ -10146,13 +10377,13 @@
         <v>77</v>
       </c>
       <c r="X70" t="s" s="2">
-        <v>108</v>
+        <v>202</v>
       </c>
       <c r="Y70" t="s" s="2">
-        <v>109</v>
+        <v>364</v>
       </c>
       <c r="Z70" t="s" s="2">
-        <v>110</v>
+        <v>365</v>
       </c>
       <c r="AA70" t="s" s="2">
         <v>77</v>
@@ -10170,31 +10401,31 @@
         <v>77</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>465</v>
+        <v>366</v>
       </c>
       <c r="AG70" t="s" s="2">
-        <v>84</v>
+        <v>75</v>
       </c>
       <c r="AH70" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AI70" t="s" s="2">
-        <v>77</v>
+        <v>367</v>
       </c>
       <c r="AJ70" t="s" s="2">
         <v>96</v>
       </c>
       <c r="AK70" t="s" s="2">
-        <v>470</v>
+        <v>368</v>
       </c>
       <c r="AL70" t="s" s="2">
-        <v>471</v>
+        <v>77</v>
       </c>
       <c r="AM70" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN70" t="s" s="2">
-        <v>472</v>
+        <v>369</v>
       </c>
       <c r="AO70" t="s" s="2">
         <v>77</v>
@@ -10202,10 +10433,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>473</v>
+        <v>416</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>473</v>
+        <v>371</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10225,22 +10456,22 @@
         <v>77</v>
       </c>
       <c r="J71" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>255</v>
+        <v>185</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>474</v>
+        <v>372</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>475</v>
+        <v>373</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>476</v>
+        <v>374</v>
       </c>
       <c r="O71" t="s" s="2">
-        <v>477</v>
+        <v>375</v>
       </c>
       <c r="P71" t="s" s="2">
         <v>77</v>
@@ -10289,7 +10520,7 @@
         <v>77</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>473</v>
+        <v>376</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>75</v>
@@ -10304,16 +10535,16 @@
         <v>96</v>
       </c>
       <c r="AK71" t="s" s="2">
-        <v>478</v>
+        <v>377</v>
       </c>
       <c r="AL71" t="s" s="2">
-        <v>479</v>
+        <v>77</v>
       </c>
       <c r="AM71" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>480</v>
+        <v>378</v>
       </c>
       <c r="AO71" t="s" s="2">
         <v>77</v>
@@ -10321,44 +10552,46 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>481</v>
+        <v>417</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>481</v>
+        <v>380</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
-        <v>482</v>
+        <v>77</v>
       </c>
       <c r="E72" s="2"/>
       <c r="F72" t="s" s="2">
         <v>75</v>
       </c>
       <c r="G72" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="H72" t="s" s="2">
         <v>77</v>
       </c>
       <c r="I72" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="J72" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>483</v>
+        <v>104</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>484</v>
+        <v>381</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>485</v>
+        <v>382</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>486</v>
-      </c>
-      <c r="O72" s="2"/>
+        <v>383</v>
+      </c>
+      <c r="O72" t="s" s="2">
+        <v>384</v>
+      </c>
       <c r="P72" t="s" s="2">
         <v>77</v>
       </c>
@@ -10382,13 +10615,13 @@
         <v>77</v>
       </c>
       <c r="X72" t="s" s="2">
-        <v>77</v>
+        <v>202</v>
       </c>
       <c r="Y72" t="s" s="2">
-        <v>77</v>
+        <v>385</v>
       </c>
       <c r="Z72" t="s" s="2">
-        <v>77</v>
+        <v>386</v>
       </c>
       <c r="AA72" t="s" s="2">
         <v>77</v>
@@ -10406,13 +10639,13 @@
         <v>77</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>481</v>
+        <v>387</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH72" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="AI72" t="s" s="2">
         <v>77</v>
@@ -10421,16 +10654,16 @@
         <v>96</v>
       </c>
       <c r="AK72" t="s" s="2">
-        <v>487</v>
+        <v>295</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>178</v>
+        <v>77</v>
       </c>
       <c r="AM72" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN72" t="s" s="2">
-        <v>488</v>
+        <v>388</v>
       </c>
       <c r="AO72" t="s" s="2">
         <v>77</v>
@@ -10438,10 +10671,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>489</v>
+        <v>418</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>489</v>
+        <v>390</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10464,20 +10697,18 @@
         <v>85</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>237</v>
+        <v>391</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>490</v>
+        <v>392</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>491</v>
+        <v>393</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>492</v>
-      </c>
-      <c r="O73" t="s" s="2">
-        <v>493</v>
-      </c>
+        <v>394</v>
+      </c>
+      <c r="O73" s="2"/>
       <c r="P73" t="s" s="2">
         <v>77</v>
       </c>
@@ -10486,7 +10717,7 @@
         <v>77</v>
       </c>
       <c r="S73" t="s" s="2">
-        <v>77</v>
+        <v>343</v>
       </c>
       <c r="T73" t="s" s="2">
         <v>77</v>
@@ -10525,7 +10756,7 @@
         <v>77</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>489</v>
+        <v>395</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>75</v>
@@ -10540,16 +10771,16 @@
         <v>96</v>
       </c>
       <c r="AK73" t="s" s="2">
-        <v>449</v>
+        <v>189</v>
       </c>
       <c r="AL73" t="s" s="2">
-        <v>494</v>
+        <v>77</v>
       </c>
       <c r="AM73" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN73" t="s" s="2">
-        <v>77</v>
+        <v>189</v>
       </c>
       <c r="AO73" t="s" s="2">
         <v>77</v>
@@ -10557,10 +10788,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>495</v>
+        <v>419</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>495</v>
+        <v>397</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -10571,32 +10802,28 @@
         <v>75</v>
       </c>
       <c r="G74" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="H74" t="s" s="2">
         <v>77</v>
       </c>
       <c r="I74" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="J74" t="s" s="2">
         <v>85</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>403</v>
+        <v>240</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>496</v>
+        <v>398</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>497</v>
-      </c>
-      <c r="N74" t="s" s="2">
-        <v>498</v>
-      </c>
-      <c r="O74" t="s" s="2">
-        <v>499</v>
-      </c>
+        <v>399</v>
+      </c>
+      <c r="N74" s="2"/>
+      <c r="O74" s="2"/>
       <c r="P74" t="s" s="2">
         <v>77</v>
       </c>
@@ -10644,13 +10871,13 @@
         <v>77</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>495</v>
+        <v>400</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH74" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="AI74" t="s" s="2">
         <v>77</v>
@@ -10659,16 +10886,16 @@
         <v>96</v>
       </c>
       <c r="AK74" t="s" s="2">
-        <v>500</v>
+        <v>338</v>
       </c>
       <c r="AL74" t="s" s="2">
-        <v>178</v>
+        <v>77</v>
       </c>
       <c r="AM74" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN74" t="s" s="2">
-        <v>77</v>
+        <v>127</v>
       </c>
       <c r="AO74" t="s" s="2">
         <v>77</v>
@@ -10676,10 +10903,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>501</v>
+        <v>420</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>501</v>
+        <v>420</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -10699,19 +10926,23 @@
         <v>77</v>
       </c>
       <c r="J75" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>174</v>
+        <v>104</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>175</v>
+        <v>421</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>176</v>
-      </c>
-      <c r="N75" s="2"/>
-      <c r="O75" s="2"/>
+        <v>422</v>
+      </c>
+      <c r="N75" t="s" s="2">
+        <v>423</v>
+      </c>
+      <c r="O75" t="s" s="2">
+        <v>424</v>
+      </c>
       <c r="P75" t="s" s="2">
         <v>77</v>
       </c>
@@ -10735,13 +10966,13 @@
         <v>77</v>
       </c>
       <c r="X75" t="s" s="2">
-        <v>77</v>
+        <v>202</v>
       </c>
       <c r="Y75" t="s" s="2">
-        <v>77</v>
+        <v>425</v>
       </c>
       <c r="Z75" t="s" s="2">
-        <v>77</v>
+        <v>426</v>
       </c>
       <c r="AA75" t="s" s="2">
         <v>77</v>
@@ -10759,7 +10990,7 @@
         <v>77</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>177</v>
+        <v>420</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>75</v>
@@ -10771,19 +11002,19 @@
         <v>77</v>
       </c>
       <c r="AJ75" t="s" s="2">
-        <v>77</v>
+        <v>96</v>
       </c>
       <c r="AK75" t="s" s="2">
-        <v>178</v>
+        <v>427</v>
       </c>
       <c r="AL75" t="s" s="2">
-        <v>77</v>
+        <v>428</v>
       </c>
       <c r="AM75" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN75" t="s" s="2">
-        <v>77</v>
+        <v>429</v>
       </c>
       <c r="AO75" t="s" s="2">
         <v>77</v>
@@ -10791,44 +11022,46 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>502</v>
+        <v>430</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>502</v>
+        <v>430</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
-        <v>153</v>
+        <v>77</v>
       </c>
       <c r="E76" s="2"/>
       <c r="F76" t="s" s="2">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="G76" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="H76" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="I76" t="s" s="2">
         <v>77</v>
       </c>
       <c r="J76" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>130</v>
+        <v>431</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>181</v>
+        <v>432</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>182</v>
+        <v>433</v>
       </c>
       <c r="N76" t="s" s="2">
-        <v>156</v>
-      </c>
-      <c r="O76" s="2"/>
+        <v>434</v>
+      </c>
+      <c r="O76" t="s" s="2">
+        <v>435</v>
+      </c>
       <c r="P76" t="s" s="2">
         <v>77</v>
       </c>
@@ -10876,53 +11109,53 @@
         <v>77</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>184</v>
+        <v>430</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH76" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="AI76" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ76" t="s" s="2">
-        <v>136</v>
+        <v>96</v>
       </c>
       <c r="AK76" t="s" s="2">
-        <v>178</v>
+        <v>436</v>
       </c>
       <c r="AL76" t="s" s="2">
-        <v>77</v>
+        <v>437</v>
       </c>
       <c r="AM76" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN76" t="s" s="2">
-        <v>77</v>
+        <v>438</v>
       </c>
       <c r="AO76" t="s" s="2">
-        <v>77</v>
+        <v>439</v>
       </c>
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>503</v>
+        <v>440</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>503</v>
+        <v>440</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
-        <v>413</v>
+        <v>77</v>
       </c>
       <c r="E77" s="2"/>
       <c r="F77" t="s" s="2">
         <v>75</v>
       </c>
       <c r="G77" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="H77" t="s" s="2">
         <v>77</v>
@@ -10934,19 +11167,19 @@
         <v>85</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>130</v>
+        <v>441</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>414</v>
+        <v>442</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>415</v>
+        <v>443</v>
       </c>
       <c r="N77" t="s" s="2">
-        <v>156</v>
+        <v>444</v>
       </c>
       <c r="O77" t="s" s="2">
-        <v>157</v>
+        <v>445</v>
       </c>
       <c r="P77" t="s" s="2">
         <v>77</v>
@@ -10995,31 +11228,31 @@
         <v>77</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>416</v>
+        <v>440</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH77" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="AI77" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ77" t="s" s="2">
-        <v>136</v>
+        <v>96</v>
       </c>
       <c r="AK77" t="s" s="2">
-        <v>127</v>
+        <v>446</v>
       </c>
       <c r="AL77" t="s" s="2">
-        <v>77</v>
+        <v>189</v>
       </c>
       <c r="AM77" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN77" t="s" s="2">
-        <v>77</v>
+        <v>447</v>
       </c>
       <c r="AO77" t="s" s="2">
         <v>77</v>
@@ -11027,10 +11260,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>504</v>
+        <v>448</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>504</v>
+        <v>448</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11038,10 +11271,10 @@
       </c>
       <c r="E78" s="2"/>
       <c r="F78" t="s" s="2">
-        <v>84</v>
+        <v>75</v>
       </c>
       <c r="G78" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="H78" t="s" s="2">
         <v>77</v>
@@ -11053,18 +11286,20 @@
         <v>85</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>505</v>
+        <v>449</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>506</v>
+        <v>450</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>507</v>
+        <v>451</v>
       </c>
       <c r="N78" t="s" s="2">
-        <v>508</v>
-      </c>
-      <c r="O78" s="2"/>
+        <v>452</v>
+      </c>
+      <c r="O78" t="s" s="2">
+        <v>453</v>
+      </c>
       <c r="P78" t="s" s="2">
         <v>77</v>
       </c>
@@ -11112,13 +11347,13 @@
         <v>77</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>504</v>
+        <v>448</v>
       </c>
       <c r="AG78" t="s" s="2">
-        <v>84</v>
+        <v>75</v>
       </c>
       <c r="AH78" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="AI78" t="s" s="2">
         <v>77</v>
@@ -11127,16 +11362,16 @@
         <v>96</v>
       </c>
       <c r="AK78" t="s" s="2">
-        <v>166</v>
+        <v>454</v>
       </c>
       <c r="AL78" t="s" s="2">
-        <v>178</v>
+        <v>455</v>
       </c>
       <c r="AM78" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN78" t="s" s="2">
-        <v>509</v>
+        <v>456</v>
       </c>
       <c r="AO78" t="s" s="2">
         <v>77</v>
@@ -11144,10 +11379,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>510</v>
+        <v>457</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>510</v>
+        <v>457</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11155,7 +11390,7 @@
       </c>
       <c r="E79" s="2"/>
       <c r="F79" t="s" s="2">
-        <v>84</v>
+        <v>75</v>
       </c>
       <c r="G79" t="s" s="2">
         <v>84</v>
@@ -11167,19 +11402,21 @@
         <v>77</v>
       </c>
       <c r="J79" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>104</v>
+        <v>209</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>511</v>
+        <v>458</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>512</v>
+        <v>459</v>
       </c>
       <c r="N79" s="2"/>
-      <c r="O79" s="2"/>
+      <c r="O79" t="s" s="2">
+        <v>460</v>
+      </c>
       <c r="P79" t="s" s="2">
         <v>77</v>
       </c>
@@ -11203,13 +11440,13 @@
         <v>77</v>
       </c>
       <c r="X79" t="s" s="2">
-        <v>191</v>
+        <v>214</v>
       </c>
       <c r="Y79" t="s" s="2">
-        <v>512</v>
+        <v>461</v>
       </c>
       <c r="Z79" t="s" s="2">
-        <v>513</v>
+        <v>462</v>
       </c>
       <c r="AA79" t="s" s="2">
         <v>77</v>
@@ -11227,10 +11464,10 @@
         <v>77</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>510</v>
+        <v>457</v>
       </c>
       <c r="AG79" t="s" s="2">
-        <v>84</v>
+        <v>75</v>
       </c>
       <c r="AH79" t="s" s="2">
         <v>84</v>
@@ -11242,23 +11479,3196 @@
         <v>96</v>
       </c>
       <c r="AK79" t="s" s="2">
+        <v>463</v>
+      </c>
+      <c r="AL79" t="s" s="2">
+        <v>464</v>
+      </c>
+      <c r="AM79" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN79" t="s" s="2">
+        <v>465</v>
+      </c>
+      <c r="AO79" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="80" hidden="true">
+      <c r="A80" t="s" s="2">
+        <v>466</v>
+      </c>
+      <c r="B80" t="s" s="2">
+        <v>466</v>
+      </c>
+      <c r="C80" s="2"/>
+      <c r="D80" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E80" s="2"/>
+      <c r="F80" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G80" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="H80" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I80" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J80" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K80" t="s" s="2">
+        <v>467</v>
+      </c>
+      <c r="L80" t="s" s="2">
+        <v>468</v>
+      </c>
+      <c r="M80" t="s" s="2">
+        <v>469</v>
+      </c>
+      <c r="N80" t="s" s="2">
+        <v>470</v>
+      </c>
+      <c r="O80" t="s" s="2">
+        <v>471</v>
+      </c>
+      <c r="P80" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q80" s="2"/>
+      <c r="R80" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S80" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T80" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U80" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V80" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W80" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X80" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y80" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z80" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA80" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB80" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC80" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD80" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE80" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF80" t="s" s="2">
+        <v>466</v>
+      </c>
+      <c r="AG80" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH80" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI80" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ80" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="AK80" t="s" s="2">
+        <v>472</v>
+      </c>
+      <c r="AL80" t="s" s="2">
+        <v>189</v>
+      </c>
+      <c r="AM80" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN80" t="s" s="2">
+        <v>473</v>
+      </c>
+      <c r="AO80" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="81" hidden="true">
+      <c r="A81" t="s" s="2">
+        <v>474</v>
+      </c>
+      <c r="B81" t="s" s="2">
+        <v>474</v>
+      </c>
+      <c r="C81" s="2"/>
+      <c r="D81" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E81" s="2"/>
+      <c r="F81" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G81" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H81" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I81" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J81" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K81" t="s" s="2">
+        <v>475</v>
+      </c>
+      <c r="L81" t="s" s="2">
+        <v>476</v>
+      </c>
+      <c r="M81" t="s" s="2">
+        <v>477</v>
+      </c>
+      <c r="N81" t="s" s="2">
+        <v>478</v>
+      </c>
+      <c r="O81" t="s" s="2">
+        <v>479</v>
+      </c>
+      <c r="P81" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q81" s="2"/>
+      <c r="R81" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S81" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T81" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U81" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V81" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W81" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X81" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y81" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z81" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA81" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB81" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC81" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD81" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE81" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF81" t="s" s="2">
+        <v>474</v>
+      </c>
+      <c r="AG81" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH81" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI81" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ81" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="AK81" t="s" s="2">
+        <v>480</v>
+      </c>
+      <c r="AL81" t="s" s="2">
+        <v>189</v>
+      </c>
+      <c r="AM81" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN81" t="s" s="2">
+        <v>481</v>
+      </c>
+      <c r="AO81" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="82" hidden="true">
+      <c r="A82" t="s" s="2">
+        <v>482</v>
+      </c>
+      <c r="B82" t="s" s="2">
+        <v>482</v>
+      </c>
+      <c r="C82" s="2"/>
+      <c r="D82" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E82" s="2"/>
+      <c r="F82" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G82" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H82" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I82" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J82" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K82" t="s" s="2">
+        <v>483</v>
+      </c>
+      <c r="L82" t="s" s="2">
+        <v>484</v>
+      </c>
+      <c r="M82" t="s" s="2">
+        <v>485</v>
+      </c>
+      <c r="N82" t="s" s="2">
+        <v>486</v>
+      </c>
+      <c r="O82" t="s" s="2">
+        <v>487</v>
+      </c>
+      <c r="P82" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q82" s="2"/>
+      <c r="R82" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S82" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T82" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U82" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V82" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W82" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X82" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y82" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z82" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA82" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB82" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC82" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD82" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE82" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF82" t="s" s="2">
+        <v>482</v>
+      </c>
+      <c r="AG82" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH82" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI82" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ82" t="s" s="2">
+        <v>488</v>
+      </c>
+      <c r="AK82" t="s" s="2">
+        <v>489</v>
+      </c>
+      <c r="AL82" t="s" s="2">
+        <v>189</v>
+      </c>
+      <c r="AM82" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN82" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AO82" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="83" hidden="true">
+      <c r="A83" t="s" s="2">
+        <v>490</v>
+      </c>
+      <c r="B83" t="s" s="2">
+        <v>490</v>
+      </c>
+      <c r="C83" s="2"/>
+      <c r="D83" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E83" s="2"/>
+      <c r="F83" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G83" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="H83" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I83" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J83" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K83" t="s" s="2">
+        <v>185</v>
+      </c>
+      <c r="L83" t="s" s="2">
+        <v>186</v>
+      </c>
+      <c r="M83" t="s" s="2">
+        <v>187</v>
+      </c>
+      <c r="N83" s="2"/>
+      <c r="O83" s="2"/>
+      <c r="P83" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q83" s="2"/>
+      <c r="R83" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S83" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T83" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U83" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V83" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W83" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X83" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y83" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z83" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA83" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB83" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC83" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD83" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE83" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF83" t="s" s="2">
+        <v>188</v>
+      </c>
+      <c r="AG83" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH83" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI83" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ83" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AK83" t="s" s="2">
+        <v>189</v>
+      </c>
+      <c r="AL83" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM83" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN83" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AO83" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="84" hidden="true">
+      <c r="A84" t="s" s="2">
+        <v>491</v>
+      </c>
+      <c r="B84" t="s" s="2">
+        <v>491</v>
+      </c>
+      <c r="C84" s="2"/>
+      <c r="D84" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="E84" s="2"/>
+      <c r="F84" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G84" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H84" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I84" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J84" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K84" t="s" s="2">
+        <v>130</v>
+      </c>
+      <c r="L84" t="s" s="2">
+        <v>192</v>
+      </c>
+      <c r="M84" t="s" s="2">
+        <v>193</v>
+      </c>
+      <c r="N84" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="O84" s="2"/>
+      <c r="P84" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q84" s="2"/>
+      <c r="R84" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S84" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T84" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U84" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V84" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W84" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X84" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y84" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z84" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA84" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB84" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC84" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD84" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE84" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF84" t="s" s="2">
+        <v>195</v>
+      </c>
+      <c r="AG84" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH84" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI84" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ84" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="AK84" t="s" s="2">
+        <v>189</v>
+      </c>
+      <c r="AL84" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM84" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN84" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AO84" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="85" hidden="true">
+      <c r="A85" t="s" s="2">
+        <v>492</v>
+      </c>
+      <c r="B85" t="s" s="2">
+        <v>492</v>
+      </c>
+      <c r="C85" s="2"/>
+      <c r="D85" t="s" s="2">
+        <v>493</v>
+      </c>
+      <c r="E85" s="2"/>
+      <c r="F85" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G85" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H85" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I85" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="J85" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="K85" t="s" s="2">
+        <v>130</v>
+      </c>
+      <c r="L85" t="s" s="2">
+        <v>494</v>
+      </c>
+      <c r="M85" t="s" s="2">
+        <v>495</v>
+      </c>
+      <c r="N85" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="O85" t="s" s="2">
+        <v>168</v>
+      </c>
+      <c r="P85" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q85" s="2"/>
+      <c r="R85" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S85" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T85" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U85" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V85" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W85" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X85" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y85" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z85" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA85" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB85" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC85" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD85" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE85" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF85" t="s" s="2">
+        <v>496</v>
+      </c>
+      <c r="AG85" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH85" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI85" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ85" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="AK85" t="s" s="2">
+        <v>127</v>
+      </c>
+      <c r="AL85" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM85" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN85" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AO85" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="86" hidden="true">
+      <c r="A86" t="s" s="2">
+        <v>497</v>
+      </c>
+      <c r="B86" t="s" s="2">
+        <v>497</v>
+      </c>
+      <c r="C86" s="2"/>
+      <c r="D86" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E86" s="2"/>
+      <c r="F86" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G86" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H86" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I86" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J86" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K86" t="s" s="2">
+        <v>209</v>
+      </c>
+      <c r="L86" t="s" s="2">
+        <v>498</v>
+      </c>
+      <c r="M86" t="s" s="2">
+        <v>499</v>
+      </c>
+      <c r="N86" s="2"/>
+      <c r="O86" t="s" s="2">
+        <v>500</v>
+      </c>
+      <c r="P86" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q86" s="2"/>
+      <c r="R86" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S86" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T86" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U86" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V86" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W86" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X86" t="s" s="2">
+        <v>214</v>
+      </c>
+      <c r="Y86" t="s" s="2">
+        <v>501</v>
+      </c>
+      <c r="Z86" t="s" s="2">
+        <v>502</v>
+      </c>
+      <c r="AA86" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB86" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC86" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD86" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE86" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF86" t="s" s="2">
+        <v>497</v>
+      </c>
+      <c r="AG86" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH86" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI86" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ86" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="AK86" t="s" s="2">
+        <v>503</v>
+      </c>
+      <c r="AL86" t="s" s="2">
+        <v>189</v>
+      </c>
+      <c r="AM86" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN86" t="s" s="2">
+        <v>504</v>
+      </c>
+      <c r="AO86" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="87" hidden="true">
+      <c r="A87" t="s" s="2">
+        <v>505</v>
+      </c>
+      <c r="B87" t="s" s="2">
+        <v>505</v>
+      </c>
+      <c r="C87" s="2"/>
+      <c r="D87" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E87" s="2"/>
+      <c r="F87" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G87" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="H87" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I87" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J87" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K87" t="s" s="2">
+        <v>275</v>
+      </c>
+      <c r="L87" t="s" s="2">
+        <v>506</v>
+      </c>
+      <c r="M87" t="s" s="2">
+        <v>507</v>
+      </c>
+      <c r="N87" s="2"/>
+      <c r="O87" t="s" s="2">
+        <v>508</v>
+      </c>
+      <c r="P87" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q87" s="2"/>
+      <c r="R87" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S87" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T87" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U87" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V87" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W87" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X87" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y87" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z87" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA87" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB87" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC87" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD87" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE87" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF87" t="s" s="2">
+        <v>505</v>
+      </c>
+      <c r="AG87" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH87" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI87" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ87" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="AK87" t="s" s="2">
+        <v>281</v>
+      </c>
+      <c r="AL87" t="s" s="2">
+        <v>189</v>
+      </c>
+      <c r="AM87" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN87" t="s" s="2">
+        <v>509</v>
+      </c>
+      <c r="AO87" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="88" hidden="true">
+      <c r="A88" t="s" s="2">
+        <v>510</v>
+      </c>
+      <c r="B88" t="s" s="2">
+        <v>510</v>
+      </c>
+      <c r="C88" s="2"/>
+      <c r="D88" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E88" s="2"/>
+      <c r="F88" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G88" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H88" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I88" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J88" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K88" t="s" s="2">
+        <v>344</v>
+      </c>
+      <c r="L88" t="s" s="2">
+        <v>511</v>
+      </c>
+      <c r="M88" t="s" s="2">
+        <v>512</v>
+      </c>
+      <c r="N88" t="s" s="2">
+        <v>513</v>
+      </c>
+      <c r="O88" t="s" s="2">
+        <v>348</v>
+      </c>
+      <c r="P88" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q88" s="2"/>
+      <c r="R88" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S88" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T88" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U88" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V88" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W88" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X88" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y88" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z88" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA88" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB88" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC88" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD88" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE88" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF88" t="s" s="2">
+        <v>510</v>
+      </c>
+      <c r="AG88" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH88" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI88" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ88" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="AK88" t="s" s="2">
+        <v>350</v>
+      </c>
+      <c r="AL88" t="s" s="2">
+        <v>189</v>
+      </c>
+      <c r="AM88" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN88" t="s" s="2">
         <v>514</v>
       </c>
-      <c r="AL79" t="s" s="2">
-        <v>178</v>
-      </c>
-      <c r="AM79" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN79" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AO79" t="s" s="2">
+      <c r="AO88" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="89" hidden="true">
+      <c r="A89" t="s" s="2">
+        <v>515</v>
+      </c>
+      <c r="B89" t="s" s="2">
+        <v>515</v>
+      </c>
+      <c r="C89" s="2"/>
+      <c r="D89" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E89" s="2"/>
+      <c r="F89" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G89" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="H89" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I89" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J89" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K89" t="s" s="2">
+        <v>449</v>
+      </c>
+      <c r="L89" t="s" s="2">
+        <v>516</v>
+      </c>
+      <c r="M89" t="s" s="2">
+        <v>517</v>
+      </c>
+      <c r="N89" s="2"/>
+      <c r="O89" t="s" s="2">
+        <v>518</v>
+      </c>
+      <c r="P89" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q89" s="2"/>
+      <c r="R89" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S89" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T89" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U89" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V89" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W89" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X89" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y89" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z89" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA89" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB89" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC89" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD89" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE89" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF89" t="s" s="2">
+        <v>515</v>
+      </c>
+      <c r="AG89" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH89" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI89" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ89" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="AK89" t="s" s="2">
+        <v>454</v>
+      </c>
+      <c r="AL89" t="s" s="2">
+        <v>189</v>
+      </c>
+      <c r="AM89" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN89" t="s" s="2">
+        <v>519</v>
+      </c>
+      <c r="AO89" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="90" hidden="true">
+      <c r="A90" t="s" s="2">
+        <v>520</v>
+      </c>
+      <c r="B90" t="s" s="2">
+        <v>520</v>
+      </c>
+      <c r="C90" s="2"/>
+      <c r="D90" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E90" s="2"/>
+      <c r="F90" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G90" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="H90" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I90" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J90" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K90" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="L90" t="s" s="2">
+        <v>421</v>
+      </c>
+      <c r="M90" t="s" s="2">
+        <v>521</v>
+      </c>
+      <c r="N90" s="2"/>
+      <c r="O90" t="s" s="2">
+        <v>522</v>
+      </c>
+      <c r="P90" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q90" s="2"/>
+      <c r="R90" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S90" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T90" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U90" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V90" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W90" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X90" t="s" s="2">
+        <v>202</v>
+      </c>
+      <c r="Y90" t="s" s="2">
+        <v>425</v>
+      </c>
+      <c r="Z90" t="s" s="2">
+        <v>426</v>
+      </c>
+      <c r="AA90" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB90" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC90" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD90" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE90" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF90" t="s" s="2">
+        <v>520</v>
+      </c>
+      <c r="AG90" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH90" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI90" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ90" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="AK90" t="s" s="2">
+        <v>427</v>
+      </c>
+      <c r="AL90" t="s" s="2">
+        <v>189</v>
+      </c>
+      <c r="AM90" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN90" t="s" s="2">
+        <v>523</v>
+      </c>
+      <c r="AO90" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="91" hidden="true">
+      <c r="A91" t="s" s="2">
+        <v>524</v>
+      </c>
+      <c r="B91" t="s" s="2">
+        <v>524</v>
+      </c>
+      <c r="C91" s="2"/>
+      <c r="D91" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E91" s="2"/>
+      <c r="F91" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G91" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="H91" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I91" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J91" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K91" t="s" s="2">
+        <v>248</v>
+      </c>
+      <c r="L91" t="s" s="2">
+        <v>525</v>
+      </c>
+      <c r="M91" t="s" s="2">
+        <v>526</v>
+      </c>
+      <c r="N91" s="2"/>
+      <c r="O91" t="s" s="2">
+        <v>527</v>
+      </c>
+      <c r="P91" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q91" s="2"/>
+      <c r="R91" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S91" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T91" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U91" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V91" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W91" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X91" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y91" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z91" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA91" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB91" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC91" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD91" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE91" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF91" t="s" s="2">
+        <v>524</v>
+      </c>
+      <c r="AG91" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH91" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI91" t="s" s="2">
+        <v>528</v>
+      </c>
+      <c r="AJ91" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="AK91" t="s" s="2">
+        <v>529</v>
+      </c>
+      <c r="AL91" t="s" s="2">
+        <v>189</v>
+      </c>
+      <c r="AM91" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN91" t="s" s="2">
+        <v>530</v>
+      </c>
+      <c r="AO91" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="92" hidden="true">
+      <c r="A92" t="s" s="2">
+        <v>531</v>
+      </c>
+      <c r="B92" t="s" s="2">
+        <v>531</v>
+      </c>
+      <c r="C92" s="2"/>
+      <c r="D92" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E92" s="2"/>
+      <c r="F92" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G92" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="H92" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I92" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J92" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K92" t="s" s="2">
+        <v>240</v>
+      </c>
+      <c r="L92" t="s" s="2">
+        <v>532</v>
+      </c>
+      <c r="M92" t="s" s="2">
+        <v>533</v>
+      </c>
+      <c r="N92" s="2"/>
+      <c r="O92" s="2"/>
+      <c r="P92" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q92" s="2"/>
+      <c r="R92" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S92" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T92" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U92" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V92" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W92" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X92" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y92" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z92" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA92" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB92" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC92" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD92" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE92" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF92" t="s" s="2">
+        <v>531</v>
+      </c>
+      <c r="AG92" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH92" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI92" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ92" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="AK92" t="s" s="2">
+        <v>534</v>
+      </c>
+      <c r="AL92" t="s" s="2">
+        <v>189</v>
+      </c>
+      <c r="AM92" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN92" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AO92" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="93" hidden="true">
+      <c r="A93" t="s" s="2">
+        <v>535</v>
+      </c>
+      <c r="B93" t="s" s="2">
+        <v>535</v>
+      </c>
+      <c r="C93" s="2"/>
+      <c r="D93" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E93" s="2"/>
+      <c r="F93" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G93" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H93" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I93" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J93" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K93" t="s" s="2">
+        <v>483</v>
+      </c>
+      <c r="L93" t="s" s="2">
+        <v>536</v>
+      </c>
+      <c r="M93" t="s" s="2">
+        <v>537</v>
+      </c>
+      <c r="N93" t="s" s="2">
+        <v>538</v>
+      </c>
+      <c r="O93" t="s" s="2">
+        <v>539</v>
+      </c>
+      <c r="P93" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q93" s="2"/>
+      <c r="R93" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S93" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T93" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U93" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V93" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W93" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X93" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y93" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z93" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA93" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB93" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC93" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD93" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE93" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF93" t="s" s="2">
+        <v>535</v>
+      </c>
+      <c r="AG93" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH93" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI93" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ93" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="AK93" t="s" s="2">
+        <v>540</v>
+      </c>
+      <c r="AL93" t="s" s="2">
+        <v>541</v>
+      </c>
+      <c r="AM93" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN93" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AO93" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="94" hidden="true">
+      <c r="A94" t="s" s="2">
+        <v>542</v>
+      </c>
+      <c r="B94" t="s" s="2">
+        <v>542</v>
+      </c>
+      <c r="C94" s="2"/>
+      <c r="D94" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E94" s="2"/>
+      <c r="F94" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G94" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="H94" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I94" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J94" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K94" t="s" s="2">
+        <v>185</v>
+      </c>
+      <c r="L94" t="s" s="2">
+        <v>186</v>
+      </c>
+      <c r="M94" t="s" s="2">
+        <v>187</v>
+      </c>
+      <c r="N94" s="2"/>
+      <c r="O94" s="2"/>
+      <c r="P94" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q94" s="2"/>
+      <c r="R94" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S94" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T94" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U94" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V94" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W94" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X94" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y94" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z94" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA94" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB94" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC94" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD94" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE94" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF94" t="s" s="2">
+        <v>188</v>
+      </c>
+      <c r="AG94" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH94" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI94" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ94" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AK94" t="s" s="2">
+        <v>189</v>
+      </c>
+      <c r="AL94" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM94" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN94" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AO94" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="95" hidden="true">
+      <c r="A95" t="s" s="2">
+        <v>543</v>
+      </c>
+      <c r="B95" t="s" s="2">
+        <v>543</v>
+      </c>
+      <c r="C95" s="2"/>
+      <c r="D95" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="E95" s="2"/>
+      <c r="F95" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G95" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H95" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I95" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J95" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K95" t="s" s="2">
+        <v>130</v>
+      </c>
+      <c r="L95" t="s" s="2">
+        <v>192</v>
+      </c>
+      <c r="M95" t="s" s="2">
+        <v>193</v>
+      </c>
+      <c r="N95" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="O95" s="2"/>
+      <c r="P95" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q95" s="2"/>
+      <c r="R95" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S95" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T95" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U95" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V95" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W95" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X95" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y95" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z95" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA95" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB95" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC95" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD95" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE95" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF95" t="s" s="2">
+        <v>195</v>
+      </c>
+      <c r="AG95" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH95" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI95" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ95" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="AK95" t="s" s="2">
+        <v>189</v>
+      </c>
+      <c r="AL95" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM95" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN95" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AO95" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="96" hidden="true">
+      <c r="A96" t="s" s="2">
+        <v>544</v>
+      </c>
+      <c r="B96" t="s" s="2">
+        <v>544</v>
+      </c>
+      <c r="C96" s="2"/>
+      <c r="D96" t="s" s="2">
+        <v>493</v>
+      </c>
+      <c r="E96" s="2"/>
+      <c r="F96" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G96" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H96" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I96" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="J96" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="K96" t="s" s="2">
+        <v>130</v>
+      </c>
+      <c r="L96" t="s" s="2">
+        <v>494</v>
+      </c>
+      <c r="M96" t="s" s="2">
+        <v>495</v>
+      </c>
+      <c r="N96" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="O96" t="s" s="2">
+        <v>168</v>
+      </c>
+      <c r="P96" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q96" s="2"/>
+      <c r="R96" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S96" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T96" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U96" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V96" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W96" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X96" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y96" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z96" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA96" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB96" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC96" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD96" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE96" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF96" t="s" s="2">
+        <v>496</v>
+      </c>
+      <c r="AG96" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH96" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI96" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ96" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="AK96" t="s" s="2">
+        <v>127</v>
+      </c>
+      <c r="AL96" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM96" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN96" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AO96" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="97" hidden="true">
+      <c r="A97" t="s" s="2">
+        <v>545</v>
+      </c>
+      <c r="B97" t="s" s="2">
+        <v>545</v>
+      </c>
+      <c r="C97" s="2"/>
+      <c r="D97" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E97" s="2"/>
+      <c r="F97" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="G97" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="H97" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I97" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J97" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K97" t="s" s="2">
+        <v>209</v>
+      </c>
+      <c r="L97" t="s" s="2">
+        <v>546</v>
+      </c>
+      <c r="M97" t="s" s="2">
+        <v>547</v>
+      </c>
+      <c r="N97" t="s" s="2">
+        <v>548</v>
+      </c>
+      <c r="O97" t="s" s="2">
+        <v>549</v>
+      </c>
+      <c r="P97" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q97" s="2"/>
+      <c r="R97" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S97" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T97" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U97" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V97" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W97" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X97" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="Y97" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="Z97" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="AA97" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB97" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC97" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD97" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE97" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF97" t="s" s="2">
+        <v>545</v>
+      </c>
+      <c r="AG97" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AH97" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI97" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ97" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="AK97" t="s" s="2">
+        <v>550</v>
+      </c>
+      <c r="AL97" t="s" s="2">
+        <v>551</v>
+      </c>
+      <c r="AM97" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN97" t="s" s="2">
+        <v>552</v>
+      </c>
+      <c r="AO97" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="98" hidden="true">
+      <c r="A98" t="s" s="2">
+        <v>553</v>
+      </c>
+      <c r="B98" t="s" s="2">
+        <v>553</v>
+      </c>
+      <c r="C98" s="2"/>
+      <c r="D98" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E98" s="2"/>
+      <c r="F98" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G98" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="H98" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I98" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J98" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K98" t="s" s="2">
+        <v>266</v>
+      </c>
+      <c r="L98" t="s" s="2">
+        <v>554</v>
+      </c>
+      <c r="M98" t="s" s="2">
+        <v>555</v>
+      </c>
+      <c r="N98" t="s" s="2">
+        <v>556</v>
+      </c>
+      <c r="O98" t="s" s="2">
+        <v>557</v>
+      </c>
+      <c r="P98" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q98" s="2"/>
+      <c r="R98" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S98" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T98" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U98" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V98" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W98" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X98" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y98" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z98" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA98" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB98" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC98" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD98" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE98" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF98" t="s" s="2">
+        <v>553</v>
+      </c>
+      <c r="AG98" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH98" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI98" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ98" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="AK98" t="s" s="2">
+        <v>558</v>
+      </c>
+      <c r="AL98" t="s" s="2">
+        <v>559</v>
+      </c>
+      <c r="AM98" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN98" t="s" s="2">
+        <v>560</v>
+      </c>
+      <c r="AO98" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="99" hidden="true">
+      <c r="A99" t="s" s="2">
+        <v>561</v>
+      </c>
+      <c r="B99" t="s" s="2">
+        <v>561</v>
+      </c>
+      <c r="C99" s="2"/>
+      <c r="D99" t="s" s="2">
+        <v>562</v>
+      </c>
+      <c r="E99" s="2"/>
+      <c r="F99" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G99" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H99" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I99" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J99" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K99" t="s" s="2">
+        <v>563</v>
+      </c>
+      <c r="L99" t="s" s="2">
+        <v>564</v>
+      </c>
+      <c r="M99" t="s" s="2">
+        <v>565</v>
+      </c>
+      <c r="N99" t="s" s="2">
+        <v>566</v>
+      </c>
+      <c r="O99" s="2"/>
+      <c r="P99" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q99" s="2"/>
+      <c r="R99" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S99" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T99" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U99" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V99" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W99" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X99" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y99" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z99" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA99" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB99" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC99" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD99" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE99" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF99" t="s" s="2">
+        <v>561</v>
+      </c>
+      <c r="AG99" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH99" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI99" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ99" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="AK99" t="s" s="2">
+        <v>567</v>
+      </c>
+      <c r="AL99" t="s" s="2">
+        <v>189</v>
+      </c>
+      <c r="AM99" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN99" t="s" s="2">
+        <v>568</v>
+      </c>
+      <c r="AO99" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="100" hidden="true">
+      <c r="A100" t="s" s="2">
+        <v>569</v>
+      </c>
+      <c r="B100" t="s" s="2">
+        <v>569</v>
+      </c>
+      <c r="C100" s="2"/>
+      <c r="D100" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E100" s="2"/>
+      <c r="F100" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G100" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="H100" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I100" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J100" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="K100" t="s" s="2">
+        <v>248</v>
+      </c>
+      <c r="L100" t="s" s="2">
+        <v>570</v>
+      </c>
+      <c r="M100" t="s" s="2">
+        <v>571</v>
+      </c>
+      <c r="N100" t="s" s="2">
+        <v>572</v>
+      </c>
+      <c r="O100" t="s" s="2">
+        <v>573</v>
+      </c>
+      <c r="P100" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q100" s="2"/>
+      <c r="R100" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S100" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T100" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U100" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V100" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W100" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X100" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y100" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z100" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA100" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB100" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC100" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD100" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE100" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF100" t="s" s="2">
+        <v>569</v>
+      </c>
+      <c r="AG100" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH100" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI100" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ100" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="AK100" t="s" s="2">
+        <v>529</v>
+      </c>
+      <c r="AL100" t="s" s="2">
+        <v>574</v>
+      </c>
+      <c r="AM100" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN100" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AO100" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="101" hidden="true">
+      <c r="A101" t="s" s="2">
+        <v>575</v>
+      </c>
+      <c r="B101" t="s" s="2">
+        <v>575</v>
+      </c>
+      <c r="C101" s="2"/>
+      <c r="D101" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E101" s="2"/>
+      <c r="F101" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G101" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H101" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I101" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="J101" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="K101" t="s" s="2">
+        <v>483</v>
+      </c>
+      <c r="L101" t="s" s="2">
+        <v>576</v>
+      </c>
+      <c r="M101" t="s" s="2">
+        <v>577</v>
+      </c>
+      <c r="N101" t="s" s="2">
+        <v>578</v>
+      </c>
+      <c r="O101" t="s" s="2">
+        <v>579</v>
+      </c>
+      <c r="P101" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q101" s="2"/>
+      <c r="R101" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S101" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T101" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U101" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V101" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W101" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X101" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y101" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z101" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA101" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB101" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC101" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD101" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE101" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF101" t="s" s="2">
+        <v>575</v>
+      </c>
+      <c r="AG101" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH101" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI101" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ101" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="AK101" t="s" s="2">
+        <v>580</v>
+      </c>
+      <c r="AL101" t="s" s="2">
+        <v>189</v>
+      </c>
+      <c r="AM101" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN101" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AO101" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="102" hidden="true">
+      <c r="A102" t="s" s="2">
+        <v>581</v>
+      </c>
+      <c r="B102" t="s" s="2">
+        <v>581</v>
+      </c>
+      <c r="C102" s="2"/>
+      <c r="D102" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E102" s="2"/>
+      <c r="F102" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G102" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="H102" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I102" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J102" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K102" t="s" s="2">
+        <v>185</v>
+      </c>
+      <c r="L102" t="s" s="2">
+        <v>186</v>
+      </c>
+      <c r="M102" t="s" s="2">
+        <v>187</v>
+      </c>
+      <c r="N102" s="2"/>
+      <c r="O102" s="2"/>
+      <c r="P102" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q102" s="2"/>
+      <c r="R102" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S102" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T102" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U102" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V102" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W102" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X102" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y102" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z102" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA102" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB102" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC102" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD102" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE102" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF102" t="s" s="2">
+        <v>188</v>
+      </c>
+      <c r="AG102" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH102" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI102" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ102" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AK102" t="s" s="2">
+        <v>189</v>
+      </c>
+      <c r="AL102" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM102" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN102" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AO102" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="103" hidden="true">
+      <c r="A103" t="s" s="2">
+        <v>582</v>
+      </c>
+      <c r="B103" t="s" s="2">
+        <v>582</v>
+      </c>
+      <c r="C103" s="2"/>
+      <c r="D103" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="E103" s="2"/>
+      <c r="F103" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G103" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H103" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I103" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J103" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K103" t="s" s="2">
+        <v>130</v>
+      </c>
+      <c r="L103" t="s" s="2">
+        <v>192</v>
+      </c>
+      <c r="M103" t="s" s="2">
+        <v>193</v>
+      </c>
+      <c r="N103" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="O103" s="2"/>
+      <c r="P103" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q103" s="2"/>
+      <c r="R103" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S103" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T103" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U103" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V103" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W103" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X103" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y103" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z103" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA103" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB103" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC103" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD103" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE103" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF103" t="s" s="2">
+        <v>195</v>
+      </c>
+      <c r="AG103" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH103" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI103" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ103" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="AK103" t="s" s="2">
+        <v>189</v>
+      </c>
+      <c r="AL103" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM103" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN103" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AO103" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="104" hidden="true">
+      <c r="A104" t="s" s="2">
+        <v>583</v>
+      </c>
+      <c r="B104" t="s" s="2">
+        <v>583</v>
+      </c>
+      <c r="C104" s="2"/>
+      <c r="D104" t="s" s="2">
+        <v>493</v>
+      </c>
+      <c r="E104" s="2"/>
+      <c r="F104" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G104" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H104" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I104" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="J104" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="K104" t="s" s="2">
+        <v>130</v>
+      </c>
+      <c r="L104" t="s" s="2">
+        <v>494</v>
+      </c>
+      <c r="M104" t="s" s="2">
+        <v>495</v>
+      </c>
+      <c r="N104" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="O104" t="s" s="2">
+        <v>168</v>
+      </c>
+      <c r="P104" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q104" s="2"/>
+      <c r="R104" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S104" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T104" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U104" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V104" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W104" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X104" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y104" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z104" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA104" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB104" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC104" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD104" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE104" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF104" t="s" s="2">
+        <v>496</v>
+      </c>
+      <c r="AG104" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH104" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI104" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ104" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="AK104" t="s" s="2">
+        <v>127</v>
+      </c>
+      <c r="AL104" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM104" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN104" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AO104" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="105" hidden="true">
+      <c r="A105" t="s" s="2">
+        <v>584</v>
+      </c>
+      <c r="B105" t="s" s="2">
+        <v>584</v>
+      </c>
+      <c r="C105" s="2"/>
+      <c r="D105" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E105" s="2"/>
+      <c r="F105" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="G105" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="H105" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I105" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J105" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="K105" t="s" s="2">
+        <v>585</v>
+      </c>
+      <c r="L105" t="s" s="2">
+        <v>586</v>
+      </c>
+      <c r="M105" t="s" s="2">
+        <v>587</v>
+      </c>
+      <c r="N105" t="s" s="2">
+        <v>588</v>
+      </c>
+      <c r="O105" s="2"/>
+      <c r="P105" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q105" s="2"/>
+      <c r="R105" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S105" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T105" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U105" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V105" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W105" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X105" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y105" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z105" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA105" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB105" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC105" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD105" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE105" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF105" t="s" s="2">
+        <v>584</v>
+      </c>
+      <c r="AG105" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AH105" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI105" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ105" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="AK105" t="s" s="2">
+        <v>177</v>
+      </c>
+      <c r="AL105" t="s" s="2">
+        <v>189</v>
+      </c>
+      <c r="AM105" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN105" t="s" s="2">
+        <v>589</v>
+      </c>
+      <c r="AO105" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="106" hidden="true">
+      <c r="A106" t="s" s="2">
+        <v>590</v>
+      </c>
+      <c r="B106" t="s" s="2">
+        <v>590</v>
+      </c>
+      <c r="C106" s="2"/>
+      <c r="D106" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E106" s="2"/>
+      <c r="F106" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="G106" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="H106" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I106" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J106" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="K106" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="L106" t="s" s="2">
+        <v>591</v>
+      </c>
+      <c r="M106" t="s" s="2">
+        <v>592</v>
+      </c>
+      <c r="N106" s="2"/>
+      <c r="O106" s="2"/>
+      <c r="P106" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q106" s="2"/>
+      <c r="R106" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S106" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T106" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U106" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V106" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W106" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X106" t="s" s="2">
+        <v>202</v>
+      </c>
+      <c r="Y106" t="s" s="2">
+        <v>592</v>
+      </c>
+      <c r="Z106" t="s" s="2">
+        <v>593</v>
+      </c>
+      <c r="AA106" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB106" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC106" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD106" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE106" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF106" t="s" s="2">
+        <v>590</v>
+      </c>
+      <c r="AG106" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AH106" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI106" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ106" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="AK106" t="s" s="2">
+        <v>594</v>
+      </c>
+      <c r="AL106" t="s" s="2">
+        <v>189</v>
+      </c>
+      <c r="AM106" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN106" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AO106" t="s" s="2">
         <v>77</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AO79">
+  <autoFilter ref="A1:AO106">
     <filterColumn colId="6">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -11268,7 +14678,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI78">
+  <conditionalFormatting sqref="A2:AI105">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/GENERATED/StructureDefinition-PacienteLP.xlsx
+++ b/GENERATED/StructureDefinition-PacienteLP.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AO$106</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AO$129</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3983" uniqueCount="595">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4828" uniqueCount="646">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-01-11T16:48:21-03:00</t>
+    <t>2023-01-11T19:25:19-03:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1074,10 +1074,162 @@
     <t>XPN.13 + XPN.14</t>
   </si>
   <si>
-    <t>Patient.name:identificacionPrincipal</t>
-  </si>
-  <si>
-    <t>Patient.name:otraIdentificacion</t>
+    <t>Patient.name:Nombres</t>
+  </si>
+  <si>
+    <t>Nombres</t>
+  </si>
+  <si>
+    <t>Patient.name:Nombres.id</t>
+  </si>
+  <si>
+    <t>Patient.name:Nombres.extension</t>
+  </si>
+  <si>
+    <t>Patient.name:Nombres.use</t>
+  </si>
+  <si>
+    <t>Uso del nombre del paciente</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Este es el uso que se le da al nombre del paciente considerando que puede ser nombre oficial, temporal, seudonimo, entre otros, Pero por motivos legales este uso es Oficial </t>
+  </si>
+  <si>
+    <t>Patient.name:Nombres.text</t>
+  </si>
+  <si>
+    <t>Patient.name:Nombres.family</t>
+  </si>
+  <si>
+    <t>Primer Apellido</t>
+  </si>
+  <si>
+    <t>Se debe ingresar el primer apellido, segun indica su identificacion personal</t>
+  </si>
+  <si>
+    <t>Patient.name:Nombres.family.id</t>
+  </si>
+  <si>
+    <t>Patient.name.family.id</t>
+  </si>
+  <si>
+    <t>xml:id (or equivalent in JSON)</t>
+  </si>
+  <si>
+    <t>unique id for the element within a resource (for internal references)</t>
+  </si>
+  <si>
+    <t>Patient.name:Nombres.family.extension</t>
+  </si>
+  <si>
+    <t>Patient.name.family.extension</t>
+  </si>
+  <si>
+    <t>Extensión para apellido paterno</t>
+  </si>
+  <si>
+    <t>Patient.name:Nombres.family.extension:mothers-family</t>
+  </si>
+  <si>
+    <t>mothers-family</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {humanname-mothers-family}
+</t>
+  </si>
+  <si>
+    <t>Portion of family name derived from mother</t>
+  </si>
+  <si>
+    <t>The portion of the family name that is derived from the person's mother.</t>
+  </si>
+  <si>
+    <t>Patient.name:Nombres.family.extension:fathers-family</t>
+  </si>
+  <si>
+    <t>fathers-family</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {humanname-fathers-family}
+</t>
+  </si>
+  <si>
+    <t>Portion of family name derived from father</t>
+  </si>
+  <si>
+    <t>The portion of the family name that is derived from the person's father.</t>
+  </si>
+  <si>
+    <t>Patient.name:Nombres.family.value</t>
+  </si>
+  <si>
+    <t>Patient.name.family.value</t>
+  </si>
+  <si>
+    <t>Primitive value for string</t>
+  </si>
+  <si>
+    <t>The actual value</t>
+  </si>
+  <si>
+    <t>1048576</t>
+  </si>
+  <si>
+    <t>string.value</t>
+  </si>
+  <si>
+    <t>Patient.name:Nombres.given</t>
+  </si>
+  <si>
+    <t>Patient.name:Nombres.prefix</t>
+  </si>
+  <si>
+    <t>Patient.name:Nombres.suffix</t>
+  </si>
+  <si>
+    <t>Patient.name:Nombres.period</t>
+  </si>
+  <si>
+    <t>Patient.name:NombresSocial</t>
+  </si>
+  <si>
+    <t>NombresSocial</t>
+  </si>
+  <si>
+    <t>Patient.name:NombresSocial.id</t>
+  </si>
+  <si>
+    <t>Patient.name:NombresSocial.extension</t>
+  </si>
+  <si>
+    <t>Patient.name:NombresSocial.use</t>
+  </si>
+  <si>
+    <t>nickname</t>
+  </si>
+  <si>
+    <t>Patient.name:NombresSocial.text</t>
+  </si>
+  <si>
+    <t>Patient.name:NombresSocial.family</t>
+  </si>
+  <si>
+    <t>Patient.name:NombresSocial.given</t>
+  </si>
+  <si>
+    <t>Nombre Social</t>
+  </si>
+  <si>
+    <t>Nombre Social del Paciente</t>
+  </si>
+  <si>
+    <t>Patient.name:NombresSocial.prefix</t>
+  </si>
+  <si>
+    <t>Patient.name:NombresSocial.suffix</t>
+  </si>
+  <si>
+    <t>Patient.name:NombresSocial.period</t>
   </si>
   <si>
     <t>Patient.telecom</t>
@@ -1144,7 +1296,7 @@
     <t>Telecommunications form for contact point - what communications system is required to make use of the contact.</t>
   </si>
   <si>
-    <t>hone</t>
+    <t>phone</t>
   </si>
   <si>
     <t>Telecommunications form for contact point.</t>
@@ -1209,6 +1361,9 @@
   </si>
   <si>
     <t>Need to track the way a person uses this contact, so a user can choose which is appropriate for their purpose.</t>
+  </si>
+  <si>
+    <t>mobile</t>
   </si>
   <si>
     <t>Use of contact point.</t>
@@ -2168,10 +2323,10 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AO106"/>
+  <dimension ref="A1:AO129"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="45.84375" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="51.4765625" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="38.84375" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="20.81640625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="38.81640625" customWidth="true" bestFit="true" hidden="true"/>
@@ -6572,10 +6727,10 @@
         <v>84</v>
       </c>
       <c r="G38" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="H38" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="I38" t="s" s="2">
         <v>77</v>
@@ -7039,13 +7194,13 @@
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
-        <v>84</v>
+        <v>75</v>
       </c>
       <c r="G42" t="s" s="2">
         <v>84</v>
       </c>
       <c r="H42" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="I42" t="s" s="2">
         <v>77</v>
@@ -7275,13 +7430,13 @@
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
-        <v>84</v>
+        <v>75</v>
       </c>
       <c r="G44" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="H44" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="I44" t="s" s="2">
         <v>77</v>
@@ -7734,7 +7889,7 @@
         <v>274</v>
       </c>
       <c r="C48" t="s" s="2">
-        <v>182</v>
+        <v>341</v>
       </c>
       <c r="D48" t="s" s="2">
         <v>77</v>
@@ -7849,14 +8004,12 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>274</v>
-      </c>
-      <c r="C49" t="s" s="2">
-        <v>256</v>
-      </c>
+        <v>284</v>
+      </c>
+      <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
         <v>77</v>
       </c>
@@ -7868,29 +8021,25 @@
         <v>84</v>
       </c>
       <c r="H49" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="I49" t="s" s="2">
         <v>77</v>
       </c>
       <c r="J49" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>275</v>
+        <v>185</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>276</v>
+        <v>186</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>277</v>
-      </c>
-      <c r="N49" t="s" s="2">
-        <v>278</v>
-      </c>
-      <c r="O49" t="s" s="2">
-        <v>279</v>
-      </c>
+        <v>187</v>
+      </c>
+      <c r="N49" s="2"/>
+      <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
         <v>77</v>
       </c>
@@ -7938,31 +8087,31 @@
         <v>77</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>274</v>
+        <v>188</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH49" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="AI49" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>96</v>
+        <v>77</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>281</v>
+        <v>189</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>282</v>
+        <v>77</v>
       </c>
       <c r="AM49" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>283</v>
+        <v>77</v>
       </c>
       <c r="AO49" t="s" s="2">
         <v>77</v>
@@ -7970,18 +8119,18 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>342</v>
+        <v>285</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
-        <v>77</v>
+        <v>164</v>
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
-        <v>343</v>
+        <v>75</v>
       </c>
       <c r="G50" t="s" s="2">
         <v>76</v>
@@ -7993,23 +8142,21 @@
         <v>77</v>
       </c>
       <c r="J50" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>344</v>
+        <v>130</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>345</v>
+        <v>192</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>346</v>
+        <v>193</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>347</v>
-      </c>
-      <c r="O50" t="s" s="2">
-        <v>348</v>
-      </c>
+        <v>167</v>
+      </c>
+      <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
         <v>77</v>
       </c>
@@ -8045,10 +8192,10 @@
         <v>77</v>
       </c>
       <c r="AB50" t="s" s="2">
-        <v>175</v>
+        <v>133</v>
       </c>
       <c r="AC50" t="s" s="2">
-        <v>349</v>
+        <v>194</v>
       </c>
       <c r="AD50" t="s" s="2">
         <v>77</v>
@@ -8057,7 +8204,7 @@
         <v>134</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>342</v>
+        <v>195</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>75</v>
@@ -8069,19 +8216,19 @@
         <v>77</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>96</v>
+        <v>136</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>350</v>
+        <v>189</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>351</v>
+        <v>77</v>
       </c>
       <c r="AM50" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>352</v>
+        <v>77</v>
       </c>
       <c r="AO50" t="s" s="2">
         <v>77</v>
@@ -8089,14 +8236,12 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>353</v>
+        <v>344</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>342</v>
-      </c>
-      <c r="C51" t="s" s="2">
-        <v>354</v>
-      </c>
+        <v>286</v>
+      </c>
+      <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
         <v>77</v>
       </c>
@@ -8111,13 +8256,13 @@
         <v>85</v>
       </c>
       <c r="I51" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="J51" t="s" s="2">
         <v>85</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>344</v>
+        <v>104</v>
       </c>
       <c r="L51" t="s" s="2">
         <v>345</v>
@@ -8126,10 +8271,10 @@
         <v>346</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>347</v>
+        <v>289</v>
       </c>
       <c r="O51" t="s" s="2">
-        <v>348</v>
+        <v>290</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>77</v>
@@ -8139,7 +8284,7 @@
         <v>77</v>
       </c>
       <c r="S51" t="s" s="2">
-        <v>77</v>
+        <v>291</v>
       </c>
       <c r="T51" t="s" s="2">
         <v>77</v>
@@ -8154,13 +8299,13 @@
         <v>77</v>
       </c>
       <c r="X51" t="s" s="2">
-        <v>77</v>
+        <v>202</v>
       </c>
       <c r="Y51" t="s" s="2">
-        <v>77</v>
+        <v>292</v>
       </c>
       <c r="Z51" t="s" s="2">
-        <v>77</v>
+        <v>293</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>77</v>
@@ -8178,13 +8323,13 @@
         <v>77</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>342</v>
+        <v>294</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH51" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="AI51" t="s" s="2">
         <v>77</v>
@@ -8193,16 +8338,16 @@
         <v>96</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>350</v>
+        <v>295</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>351</v>
+        <v>77</v>
       </c>
       <c r="AM51" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>352</v>
+        <v>296</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>77</v>
@@ -8210,10 +8355,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>355</v>
+        <v>347</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>356</v>
+        <v>297</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8233,19 +8378,23 @@
         <v>77</v>
       </c>
       <c r="J52" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="K52" t="s" s="2">
         <v>185</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>186</v>
+        <v>298</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>187</v>
-      </c>
-      <c r="N52" s="2"/>
-      <c r="O52" s="2"/>
+        <v>299</v>
+      </c>
+      <c r="N52" t="s" s="2">
+        <v>300</v>
+      </c>
+      <c r="O52" t="s" s="2">
+        <v>301</v>
+      </c>
       <c r="P52" t="s" s="2">
         <v>77</v>
       </c>
@@ -8293,7 +8442,7 @@
         <v>77</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>188</v>
+        <v>302</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>75</v>
@@ -8305,10 +8454,10 @@
         <v>77</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>77</v>
+        <v>96</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>189</v>
+        <v>303</v>
       </c>
       <c r="AL52" t="s" s="2">
         <v>77</v>
@@ -8317,7 +8466,7 @@
         <v>77</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>77</v>
+        <v>304</v>
       </c>
       <c r="AO52" t="s" s="2">
         <v>77</v>
@@ -8325,42 +8474,42 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>357</v>
+        <v>348</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>358</v>
+        <v>305</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
-        <v>164</v>
+        <v>306</v>
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="G53" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="H53" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="I53" t="s" s="2">
         <v>77</v>
       </c>
       <c r="J53" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>130</v>
+        <v>185</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>192</v>
+        <v>349</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>193</v>
+        <v>350</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>167</v>
+        <v>309</v>
       </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
@@ -8398,34 +8547,34 @@
         <v>77</v>
       </c>
       <c r="AB53" t="s" s="2">
-        <v>133</v>
+        <v>77</v>
       </c>
       <c r="AC53" t="s" s="2">
-        <v>194</v>
+        <v>77</v>
       </c>
       <c r="AD53" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE53" t="s" s="2">
-        <v>134</v>
+        <v>77</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>195</v>
+        <v>310</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH53" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="AI53" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>136</v>
+        <v>96</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>189</v>
+        <v>311</v>
       </c>
       <c r="AL53" t="s" s="2">
         <v>77</v>
@@ -8434,7 +8583,7 @@
         <v>77</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>77</v>
+        <v>312</v>
       </c>
       <c r="AO53" t="s" s="2">
         <v>77</v>
@@ -8442,10 +8591,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>359</v>
+        <v>351</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>360</v>
+        <v>352</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8465,16 +8614,16 @@
         <v>77</v>
       </c>
       <c r="J54" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>104</v>
+        <v>185</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>361</v>
+        <v>353</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>362</v>
+        <v>354</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" s="2"/>
@@ -8486,7 +8635,7 @@
         <v>77</v>
       </c>
       <c r="S54" t="s" s="2">
-        <v>363</v>
+        <v>77</v>
       </c>
       <c r="T54" t="s" s="2">
         <v>77</v>
@@ -8501,13 +8650,13 @@
         <v>77</v>
       </c>
       <c r="X54" t="s" s="2">
-        <v>202</v>
+        <v>77</v>
       </c>
       <c r="Y54" t="s" s="2">
-        <v>364</v>
+        <v>77</v>
       </c>
       <c r="Z54" t="s" s="2">
-        <v>365</v>
+        <v>77</v>
       </c>
       <c r="AA54" t="s" s="2">
         <v>77</v>
@@ -8525,7 +8674,7 @@
         <v>77</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>366</v>
+        <v>188</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>75</v>
@@ -8534,13 +8683,13 @@
         <v>84</v>
       </c>
       <c r="AI54" t="s" s="2">
-        <v>367</v>
+        <v>77</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>96</v>
+        <v>77</v>
       </c>
       <c r="AK54" t="s" s="2">
-        <v>368</v>
+        <v>77</v>
       </c>
       <c r="AL54" t="s" s="2">
         <v>77</v>
@@ -8549,7 +8698,7 @@
         <v>77</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>369</v>
+        <v>77</v>
       </c>
       <c r="AO54" t="s" s="2">
         <v>77</v>
@@ -8557,10 +8706,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>370</v>
+        <v>355</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>371</v>
+        <v>356</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8571,7 +8720,7 @@
         <v>75</v>
       </c>
       <c r="G55" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="H55" t="s" s="2">
         <v>77</v>
@@ -8580,23 +8729,19 @@
         <v>77</v>
       </c>
       <c r="J55" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>185</v>
+        <v>130</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>372</v>
+        <v>357</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>373</v>
-      </c>
-      <c r="N55" t="s" s="2">
-        <v>374</v>
-      </c>
-      <c r="O55" t="s" s="2">
-        <v>375</v>
-      </c>
+        <v>132</v>
+      </c>
+      <c r="N55" s="2"/>
+      <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
         <v>77</v>
       </c>
@@ -8632,34 +8777,32 @@
         <v>77</v>
       </c>
       <c r="AB55" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC55" t="s" s="2">
-        <v>77</v>
-      </c>
+        <v>133</v>
+      </c>
+      <c r="AC55" s="2"/>
       <c r="AD55" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE55" t="s" s="2">
-        <v>77</v>
+        <v>134</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>376</v>
+        <v>195</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH55" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="AI55" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>96</v>
+        <v>136</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>377</v>
+        <v>77</v>
       </c>
       <c r="AL55" t="s" s="2">
         <v>77</v>
@@ -8668,7 +8811,7 @@
         <v>77</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>378</v>
+        <v>77</v>
       </c>
       <c r="AO55" t="s" s="2">
         <v>77</v>
@@ -8676,12 +8819,14 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>379</v>
+        <v>358</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>380</v>
-      </c>
-      <c r="C56" s="2"/>
+        <v>356</v>
+      </c>
+      <c r="C56" t="s" s="2">
+        <v>359</v>
+      </c>
       <c r="D56" t="s" s="2">
         <v>77</v>
       </c>
@@ -8693,29 +8838,25 @@
         <v>84</v>
       </c>
       <c r="H56" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="I56" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="J56" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>104</v>
+        <v>360</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>381</v>
+        <v>361</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>382</v>
-      </c>
-      <c r="N56" t="s" s="2">
-        <v>383</v>
-      </c>
-      <c r="O56" t="s" s="2">
-        <v>384</v>
-      </c>
+        <v>362</v>
+      </c>
+      <c r="N56" s="2"/>
+      <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
         <v>77</v>
       </c>
@@ -8739,13 +8880,13 @@
         <v>77</v>
       </c>
       <c r="X56" t="s" s="2">
-        <v>202</v>
+        <v>77</v>
       </c>
       <c r="Y56" t="s" s="2">
-        <v>385</v>
+        <v>77</v>
       </c>
       <c r="Z56" t="s" s="2">
-        <v>386</v>
+        <v>77</v>
       </c>
       <c r="AA56" t="s" s="2">
         <v>77</v>
@@ -8763,22 +8904,22 @@
         <v>77</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>387</v>
+        <v>195</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH56" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="AI56" t="s" s="2">
-        <v>77</v>
+        <v>142</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>96</v>
+        <v>136</v>
       </c>
       <c r="AK56" t="s" s="2">
-        <v>295</v>
+        <v>127</v>
       </c>
       <c r="AL56" t="s" s="2">
         <v>77</v>
@@ -8787,7 +8928,7 @@
         <v>77</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>388</v>
+        <v>127</v>
       </c>
       <c r="AO56" t="s" s="2">
         <v>77</v>
@@ -8795,12 +8936,14 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>389</v>
+        <v>363</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>390</v>
-      </c>
-      <c r="C57" s="2"/>
+        <v>356</v>
+      </c>
+      <c r="C57" t="s" s="2">
+        <v>364</v>
+      </c>
       <c r="D57" t="s" s="2">
         <v>77</v>
       </c>
@@ -8812,26 +8955,24 @@
         <v>84</v>
       </c>
       <c r="H57" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="I57" t="s" s="2">
         <v>77</v>
       </c>
       <c r="J57" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>391</v>
+        <v>365</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>392</v>
+        <v>366</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>393</v>
-      </c>
-      <c r="N57" t="s" s="2">
-        <v>394</v>
-      </c>
+        <v>367</v>
+      </c>
+      <c r="N57" s="2"/>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
         <v>77</v>
@@ -8841,7 +8982,7 @@
         <v>77</v>
       </c>
       <c r="S57" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="T57" t="s" s="2">
         <v>77</v>
@@ -8880,22 +9021,22 @@
         <v>77</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>395</v>
+        <v>195</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH57" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="AI57" t="s" s="2">
-        <v>77</v>
+        <v>142</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>96</v>
+        <v>136</v>
       </c>
       <c r="AK57" t="s" s="2">
-        <v>189</v>
+        <v>127</v>
       </c>
       <c r="AL57" t="s" s="2">
         <v>77</v>
@@ -8904,7 +9045,7 @@
         <v>77</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>189</v>
+        <v>127</v>
       </c>
       <c r="AO57" t="s" s="2">
         <v>77</v>
@@ -8912,10 +9053,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>396</v>
+        <v>368</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>397</v>
+        <v>369</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8935,16 +9076,16 @@
         <v>77</v>
       </c>
       <c r="J58" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>240</v>
+        <v>185</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>398</v>
+        <v>370</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>399</v>
+        <v>371</v>
       </c>
       <c r="N58" s="2"/>
       <c r="O58" s="2"/>
@@ -8968,7 +9109,7 @@
         <v>77</v>
       </c>
       <c r="W58" t="s" s="2">
-        <v>77</v>
+        <v>372</v>
       </c>
       <c r="X58" t="s" s="2">
         <v>77</v>
@@ -8995,7 +9136,7 @@
         <v>77</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>400</v>
+        <v>373</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>75</v>
@@ -9007,10 +9148,10 @@
         <v>77</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>96</v>
+        <v>77</v>
       </c>
       <c r="AK58" t="s" s="2">
-        <v>338</v>
+        <v>77</v>
       </c>
       <c r="AL58" t="s" s="2">
         <v>77</v>
@@ -9019,7 +9160,7 @@
         <v>77</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>127</v>
+        <v>77</v>
       </c>
       <c r="AO58" t="s" s="2">
         <v>77</v>
@@ -9027,23 +9168,21 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>401</v>
+        <v>374</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>342</v>
-      </c>
-      <c r="C59" t="s" s="2">
-        <v>402</v>
-      </c>
+        <v>313</v>
+      </c>
+      <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
-        <v>77</v>
+        <v>314</v>
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
         <v>84</v>
       </c>
       <c r="G59" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="H59" t="s" s="2">
         <v>85</v>
@@ -9055,20 +9194,18 @@
         <v>85</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>344</v>
+        <v>185</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>345</v>
+        <v>315</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>346</v>
+        <v>316</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>347</v>
-      </c>
-      <c r="O59" t="s" s="2">
-        <v>348</v>
-      </c>
+        <v>317</v>
+      </c>
+      <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
         <v>77</v>
       </c>
@@ -9116,7 +9253,7 @@
         <v>77</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>342</v>
+        <v>318</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>75</v>
@@ -9131,16 +9268,16 @@
         <v>96</v>
       </c>
       <c r="AK59" t="s" s="2">
-        <v>350</v>
+        <v>319</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>351</v>
+        <v>77</v>
       </c>
       <c r="AM59" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>352</v>
+        <v>320</v>
       </c>
       <c r="AO59" t="s" s="2">
         <v>77</v>
@@ -9148,10 +9285,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>403</v>
+        <v>375</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>356</v>
+        <v>321</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9162,7 +9299,7 @@
         <v>75</v>
       </c>
       <c r="G60" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="H60" t="s" s="2">
         <v>77</v>
@@ -9171,16 +9308,16 @@
         <v>77</v>
       </c>
       <c r="J60" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="K60" t="s" s="2">
         <v>185</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>186</v>
+        <v>322</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>187</v>
+        <v>323</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" s="2"/>
@@ -9231,22 +9368,22 @@
         <v>77</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>188</v>
+        <v>324</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH60" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="AI60" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ60" t="s" s="2">
-        <v>77</v>
+        <v>96</v>
       </c>
       <c r="AK60" t="s" s="2">
-        <v>189</v>
+        <v>325</v>
       </c>
       <c r="AL60" t="s" s="2">
         <v>77</v>
@@ -9255,7 +9392,7 @@
         <v>77</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>77</v>
+        <v>326</v>
       </c>
       <c r="AO60" t="s" s="2">
         <v>77</v>
@@ -9263,14 +9400,14 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>404</v>
+        <v>376</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>358</v>
+        <v>327</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
-        <v>164</v>
+        <v>77</v>
       </c>
       <c r="E61" s="2"/>
       <c r="F61" t="s" s="2">
@@ -9286,20 +9423,18 @@
         <v>77</v>
       </c>
       <c r="J61" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>130</v>
+        <v>185</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>192</v>
+        <v>328</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>193</v>
-      </c>
-      <c r="N61" t="s" s="2">
-        <v>167</v>
-      </c>
+        <v>329</v>
+      </c>
+      <c r="N61" s="2"/>
       <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
         <v>77</v>
@@ -9336,19 +9471,19 @@
         <v>77</v>
       </c>
       <c r="AB61" t="s" s="2">
-        <v>133</v>
+        <v>77</v>
       </c>
       <c r="AC61" t="s" s="2">
-        <v>194</v>
+        <v>77</v>
       </c>
       <c r="AD61" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE61" t="s" s="2">
-        <v>134</v>
+        <v>77</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>195</v>
+        <v>330</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>75</v>
@@ -9360,10 +9495,10 @@
         <v>77</v>
       </c>
       <c r="AJ61" t="s" s="2">
-        <v>136</v>
+        <v>96</v>
       </c>
       <c r="AK61" t="s" s="2">
-        <v>189</v>
+        <v>331</v>
       </c>
       <c r="AL61" t="s" s="2">
         <v>77</v>
@@ -9372,7 +9507,7 @@
         <v>77</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>77</v>
+        <v>332</v>
       </c>
       <c r="AO61" t="s" s="2">
         <v>77</v>
@@ -9380,10 +9515,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>405</v>
+        <v>377</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>360</v>
+        <v>333</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9406,16 +9541,18 @@
         <v>85</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>104</v>
+        <v>240</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>361</v>
+        <v>334</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>362</v>
+        <v>335</v>
       </c>
       <c r="N62" s="2"/>
-      <c r="O62" s="2"/>
+      <c r="O62" t="s" s="2">
+        <v>336</v>
+      </c>
       <c r="P62" t="s" s="2">
         <v>77</v>
       </c>
@@ -9439,13 +9576,13 @@
         <v>77</v>
       </c>
       <c r="X62" t="s" s="2">
-        <v>202</v>
+        <v>77</v>
       </c>
       <c r="Y62" t="s" s="2">
-        <v>364</v>
+        <v>77</v>
       </c>
       <c r="Z62" t="s" s="2">
-        <v>365</v>
+        <v>77</v>
       </c>
       <c r="AA62" t="s" s="2">
         <v>77</v>
@@ -9463,7 +9600,7 @@
         <v>77</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>366</v>
+        <v>337</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>75</v>
@@ -9472,13 +9609,13 @@
         <v>84</v>
       </c>
       <c r="AI62" t="s" s="2">
-        <v>367</v>
+        <v>77</v>
       </c>
       <c r="AJ62" t="s" s="2">
         <v>96</v>
       </c>
       <c r="AK62" t="s" s="2">
-        <v>368</v>
+        <v>338</v>
       </c>
       <c r="AL62" t="s" s="2">
         <v>77</v>
@@ -9487,7 +9624,7 @@
         <v>77</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>369</v>
+        <v>339</v>
       </c>
       <c r="AO62" t="s" s="2">
         <v>77</v>
@@ -9495,12 +9632,14 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>406</v>
+        <v>378</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>371</v>
-      </c>
-      <c r="C63" s="2"/>
+        <v>274</v>
+      </c>
+      <c r="C63" t="s" s="2">
+        <v>379</v>
+      </c>
       <c r="D63" t="s" s="2">
         <v>77</v>
       </c>
@@ -9512,7 +9651,7 @@
         <v>84</v>
       </c>
       <c r="H63" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="I63" t="s" s="2">
         <v>77</v>
@@ -9521,19 +9660,19 @@
         <v>85</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>185</v>
+        <v>275</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>372</v>
+        <v>276</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>373</v>
+        <v>277</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>374</v>
+        <v>278</v>
       </c>
       <c r="O63" t="s" s="2">
-        <v>375</v>
+        <v>279</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>77</v>
@@ -9582,13 +9721,13 @@
         <v>77</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>376</v>
+        <v>274</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH63" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="AI63" t="s" s="2">
         <v>77</v>
@@ -9597,16 +9736,16 @@
         <v>96</v>
       </c>
       <c r="AK63" t="s" s="2">
-        <v>377</v>
+        <v>281</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>77</v>
+        <v>282</v>
       </c>
       <c r="AM63" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>378</v>
+        <v>283</v>
       </c>
       <c r="AO63" t="s" s="2">
         <v>77</v>
@@ -9614,10 +9753,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>407</v>
+        <v>380</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>380</v>
+        <v>284</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9634,26 +9773,22 @@
         <v>77</v>
       </c>
       <c r="I64" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="J64" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>104</v>
+        <v>185</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>381</v>
+        <v>186</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>382</v>
-      </c>
-      <c r="N64" t="s" s="2">
-        <v>383</v>
-      </c>
-      <c r="O64" t="s" s="2">
-        <v>384</v>
-      </c>
+        <v>187</v>
+      </c>
+      <c r="N64" s="2"/>
+      <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
         <v>77</v>
       </c>
@@ -9677,13 +9812,13 @@
         <v>77</v>
       </c>
       <c r="X64" t="s" s="2">
-        <v>202</v>
+        <v>77</v>
       </c>
       <c r="Y64" t="s" s="2">
-        <v>385</v>
+        <v>77</v>
       </c>
       <c r="Z64" t="s" s="2">
-        <v>386</v>
+        <v>77</v>
       </c>
       <c r="AA64" t="s" s="2">
         <v>77</v>
@@ -9701,7 +9836,7 @@
         <v>77</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>387</v>
+        <v>188</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>75</v>
@@ -9713,10 +9848,10 @@
         <v>77</v>
       </c>
       <c r="AJ64" t="s" s="2">
-        <v>96</v>
+        <v>77</v>
       </c>
       <c r="AK64" t="s" s="2">
-        <v>295</v>
+        <v>189</v>
       </c>
       <c r="AL64" t="s" s="2">
         <v>77</v>
@@ -9725,7 +9860,7 @@
         <v>77</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>388</v>
+        <v>77</v>
       </c>
       <c r="AO64" t="s" s="2">
         <v>77</v>
@@ -9733,21 +9868,21 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>408</v>
+        <v>381</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>390</v>
+        <v>285</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
-        <v>77</v>
+        <v>164</v>
       </c>
       <c r="E65" s="2"/>
       <c r="F65" t="s" s="2">
         <v>75</v>
       </c>
       <c r="G65" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="H65" t="s" s="2">
         <v>77</v>
@@ -9756,19 +9891,19 @@
         <v>77</v>
       </c>
       <c r="J65" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>391</v>
+        <v>130</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>392</v>
+        <v>192</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>393</v>
+        <v>193</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>394</v>
+        <v>167</v>
       </c>
       <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
@@ -9779,7 +9914,7 @@
         <v>77</v>
       </c>
       <c r="S65" t="s" s="2">
-        <v>409</v>
+        <v>77</v>
       </c>
       <c r="T65" t="s" s="2">
         <v>77</v>
@@ -9806,31 +9941,31 @@
         <v>77</v>
       </c>
       <c r="AB65" t="s" s="2">
-        <v>77</v>
+        <v>133</v>
       </c>
       <c r="AC65" t="s" s="2">
-        <v>77</v>
+        <v>194</v>
       </c>
       <c r="AD65" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE65" t="s" s="2">
-        <v>77</v>
+        <v>134</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>395</v>
+        <v>195</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH65" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="AI65" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ65" t="s" s="2">
-        <v>96</v>
+        <v>136</v>
       </c>
       <c r="AK65" t="s" s="2">
         <v>189</v>
@@ -9842,7 +9977,7 @@
         <v>77</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>189</v>
+        <v>77</v>
       </c>
       <c r="AO65" t="s" s="2">
         <v>77</v>
@@ -9850,10 +9985,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>410</v>
+        <v>382</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>397</v>
+        <v>286</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9861,7 +9996,7 @@
       </c>
       <c r="E66" s="2"/>
       <c r="F66" t="s" s="2">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="G66" t="s" s="2">
         <v>84</v>
@@ -9870,22 +10005,26 @@
         <v>77</v>
       </c>
       <c r="I66" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="J66" t="s" s="2">
         <v>85</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>240</v>
+        <v>104</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>398</v>
+        <v>287</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>399</v>
-      </c>
-      <c r="N66" s="2"/>
-      <c r="O66" s="2"/>
+        <v>288</v>
+      </c>
+      <c r="N66" t="s" s="2">
+        <v>289</v>
+      </c>
+      <c r="O66" t="s" s="2">
+        <v>290</v>
+      </c>
       <c r="P66" t="s" s="2">
         <v>77</v>
       </c>
@@ -9894,7 +10033,7 @@
         <v>77</v>
       </c>
       <c r="S66" t="s" s="2">
-        <v>77</v>
+        <v>383</v>
       </c>
       <c r="T66" t="s" s="2">
         <v>77</v>
@@ -9909,13 +10048,13 @@
         <v>77</v>
       </c>
       <c r="X66" t="s" s="2">
-        <v>77</v>
+        <v>202</v>
       </c>
       <c r="Y66" t="s" s="2">
-        <v>77</v>
+        <v>292</v>
       </c>
       <c r="Z66" t="s" s="2">
-        <v>77</v>
+        <v>293</v>
       </c>
       <c r="AA66" t="s" s="2">
         <v>77</v>
@@ -9933,7 +10072,7 @@
         <v>77</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>400</v>
+        <v>294</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>75</v>
@@ -9948,7 +10087,7 @@
         <v>96</v>
       </c>
       <c r="AK66" t="s" s="2">
-        <v>338</v>
+        <v>295</v>
       </c>
       <c r="AL66" t="s" s="2">
         <v>77</v>
@@ -9957,7 +10096,7 @@
         <v>77</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>127</v>
+        <v>296</v>
       </c>
       <c r="AO66" t="s" s="2">
         <v>77</v>
@@ -9965,20 +10104,18 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>411</v>
+        <v>384</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>342</v>
-      </c>
-      <c r="C67" t="s" s="2">
-        <v>412</v>
-      </c>
+        <v>297</v>
+      </c>
+      <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
         <v>77</v>
       </c>
       <c r="E67" s="2"/>
       <c r="F67" t="s" s="2">
-        <v>84</v>
+        <v>75</v>
       </c>
       <c r="G67" t="s" s="2">
         <v>84</v>
@@ -9993,19 +10130,19 @@
         <v>85</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>344</v>
+        <v>185</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>345</v>
+        <v>298</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>346</v>
+        <v>299</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>347</v>
+        <v>300</v>
       </c>
       <c r="O67" t="s" s="2">
-        <v>348</v>
+        <v>301</v>
       </c>
       <c r="P67" t="s" s="2">
         <v>77</v>
@@ -10054,13 +10191,13 @@
         <v>77</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>342</v>
+        <v>302</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH67" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="AI67" t="s" s="2">
         <v>77</v>
@@ -10069,16 +10206,16 @@
         <v>96</v>
       </c>
       <c r="AK67" t="s" s="2">
-        <v>350</v>
+        <v>303</v>
       </c>
       <c r="AL67" t="s" s="2">
-        <v>351</v>
+        <v>77</v>
       </c>
       <c r="AM67" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN67" t="s" s="2">
-        <v>352</v>
+        <v>304</v>
       </c>
       <c r="AO67" t="s" s="2">
         <v>77</v>
@@ -10086,21 +10223,21 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>413</v>
+        <v>385</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>356</v>
+        <v>305</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
-        <v>77</v>
+        <v>306</v>
       </c>
       <c r="E68" s="2"/>
       <c r="F68" t="s" s="2">
         <v>75</v>
       </c>
       <c r="G68" t="s" s="2">
-        <v>84</v>
+        <v>75</v>
       </c>
       <c r="H68" t="s" s="2">
         <v>77</v>
@@ -10109,18 +10246,20 @@
         <v>77</v>
       </c>
       <c r="J68" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="K68" t="s" s="2">
         <v>185</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>186</v>
+        <v>307</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>187</v>
-      </c>
-      <c r="N68" s="2"/>
+        <v>308</v>
+      </c>
+      <c r="N68" t="s" s="2">
+        <v>309</v>
+      </c>
       <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
         <v>77</v>
@@ -10169,7 +10308,7 @@
         <v>77</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>188</v>
+        <v>310</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>75</v>
@@ -10181,10 +10320,10 @@
         <v>77</v>
       </c>
       <c r="AJ68" t="s" s="2">
-        <v>77</v>
+        <v>96</v>
       </c>
       <c r="AK68" t="s" s="2">
-        <v>189</v>
+        <v>311</v>
       </c>
       <c r="AL68" t="s" s="2">
         <v>77</v>
@@ -10193,7 +10332,7 @@
         <v>77</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>77</v>
+        <v>312</v>
       </c>
       <c r="AO68" t="s" s="2">
         <v>77</v>
@@ -10201,42 +10340,42 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>414</v>
+        <v>386</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>358</v>
+        <v>313</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
-        <v>164</v>
+        <v>314</v>
       </c>
       <c r="E69" s="2"/>
       <c r="F69" t="s" s="2">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="G69" t="s" s="2">
         <v>76</v>
       </c>
       <c r="H69" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="I69" t="s" s="2">
         <v>77</v>
       </c>
       <c r="J69" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>130</v>
+        <v>185</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>192</v>
+        <v>387</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>193</v>
+        <v>388</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>167</v>
+        <v>317</v>
       </c>
       <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
@@ -10274,19 +10413,19 @@
         <v>77</v>
       </c>
       <c r="AB69" t="s" s="2">
-        <v>133</v>
+        <v>77</v>
       </c>
       <c r="AC69" t="s" s="2">
-        <v>194</v>
+        <v>77</v>
       </c>
       <c r="AD69" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE69" t="s" s="2">
-        <v>134</v>
+        <v>77</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>195</v>
+        <v>318</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>75</v>
@@ -10298,10 +10437,10 @@
         <v>77</v>
       </c>
       <c r="AJ69" t="s" s="2">
-        <v>136</v>
+        <v>96</v>
       </c>
       <c r="AK69" t="s" s="2">
-        <v>189</v>
+        <v>319</v>
       </c>
       <c r="AL69" t="s" s="2">
         <v>77</v>
@@ -10310,7 +10449,7 @@
         <v>77</v>
       </c>
       <c r="AN69" t="s" s="2">
-        <v>77</v>
+        <v>320</v>
       </c>
       <c r="AO69" t="s" s="2">
         <v>77</v>
@@ -10318,10 +10457,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>415</v>
+        <v>389</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>360</v>
+        <v>321</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10332,7 +10471,7 @@
         <v>75</v>
       </c>
       <c r="G70" t="s" s="2">
-        <v>84</v>
+        <v>75</v>
       </c>
       <c r="H70" t="s" s="2">
         <v>77</v>
@@ -10344,13 +10483,13 @@
         <v>85</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>104</v>
+        <v>185</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>361</v>
+        <v>322</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>362</v>
+        <v>323</v>
       </c>
       <c r="N70" s="2"/>
       <c r="O70" s="2"/>
@@ -10377,13 +10516,13 @@
         <v>77</v>
       </c>
       <c r="X70" t="s" s="2">
-        <v>202</v>
+        <v>77</v>
       </c>
       <c r="Y70" t="s" s="2">
-        <v>364</v>
+        <v>77</v>
       </c>
       <c r="Z70" t="s" s="2">
-        <v>365</v>
+        <v>77</v>
       </c>
       <c r="AA70" t="s" s="2">
         <v>77</v>
@@ -10401,22 +10540,22 @@
         <v>77</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>366</v>
+        <v>324</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH70" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="AI70" t="s" s="2">
-        <v>367</v>
+        <v>77</v>
       </c>
       <c r="AJ70" t="s" s="2">
         <v>96</v>
       </c>
       <c r="AK70" t="s" s="2">
-        <v>368</v>
+        <v>325</v>
       </c>
       <c r="AL70" t="s" s="2">
         <v>77</v>
@@ -10425,7 +10564,7 @@
         <v>77</v>
       </c>
       <c r="AN70" t="s" s="2">
-        <v>369</v>
+        <v>326</v>
       </c>
       <c r="AO70" t="s" s="2">
         <v>77</v>
@@ -10433,10 +10572,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>416</v>
+        <v>390</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>371</v>
+        <v>327</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10447,7 +10586,7 @@
         <v>75</v>
       </c>
       <c r="G71" t="s" s="2">
-        <v>84</v>
+        <v>75</v>
       </c>
       <c r="H71" t="s" s="2">
         <v>77</v>
@@ -10462,17 +10601,13 @@
         <v>185</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>372</v>
+        <v>328</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>373</v>
-      </c>
-      <c r="N71" t="s" s="2">
-        <v>374</v>
-      </c>
-      <c r="O71" t="s" s="2">
-        <v>375</v>
-      </c>
+        <v>329</v>
+      </c>
+      <c r="N71" s="2"/>
+      <c r="O71" s="2"/>
       <c r="P71" t="s" s="2">
         <v>77</v>
       </c>
@@ -10520,13 +10655,13 @@
         <v>77</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>376</v>
+        <v>330</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH71" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="AI71" t="s" s="2">
         <v>77</v>
@@ -10535,7 +10670,7 @@
         <v>96</v>
       </c>
       <c r="AK71" t="s" s="2">
-        <v>377</v>
+        <v>331</v>
       </c>
       <c r="AL71" t="s" s="2">
         <v>77</v>
@@ -10544,7 +10679,7 @@
         <v>77</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>378</v>
+        <v>332</v>
       </c>
       <c r="AO71" t="s" s="2">
         <v>77</v>
@@ -10552,10 +10687,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>417</v>
+        <v>391</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>380</v>
+        <v>333</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10566,31 +10701,29 @@
         <v>75</v>
       </c>
       <c r="G72" t="s" s="2">
-        <v>84</v>
+        <v>75</v>
       </c>
       <c r="H72" t="s" s="2">
         <v>77</v>
       </c>
       <c r="I72" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="J72" t="s" s="2">
         <v>85</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>104</v>
+        <v>240</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>381</v>
+        <v>334</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>382</v>
-      </c>
-      <c r="N72" t="s" s="2">
-        <v>383</v>
-      </c>
+        <v>335</v>
+      </c>
+      <c r="N72" s="2"/>
       <c r="O72" t="s" s="2">
-        <v>384</v>
+        <v>336</v>
       </c>
       <c r="P72" t="s" s="2">
         <v>77</v>
@@ -10615,13 +10748,13 @@
         <v>77</v>
       </c>
       <c r="X72" t="s" s="2">
-        <v>202</v>
+        <v>77</v>
       </c>
       <c r="Y72" t="s" s="2">
-        <v>385</v>
+        <v>77</v>
       </c>
       <c r="Z72" t="s" s="2">
-        <v>386</v>
+        <v>77</v>
       </c>
       <c r="AA72" t="s" s="2">
         <v>77</v>
@@ -10639,7 +10772,7 @@
         <v>77</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>387</v>
+        <v>337</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>75</v>
@@ -10654,7 +10787,7 @@
         <v>96</v>
       </c>
       <c r="AK72" t="s" s="2">
-        <v>295</v>
+        <v>338</v>
       </c>
       <c r="AL72" t="s" s="2">
         <v>77</v>
@@ -10663,7 +10796,7 @@
         <v>77</v>
       </c>
       <c r="AN72" t="s" s="2">
-        <v>388</v>
+        <v>339</v>
       </c>
       <c r="AO72" t="s" s="2">
         <v>77</v>
@@ -10671,10 +10804,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>418</v>
+        <v>392</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10682,10 +10815,10 @@
       </c>
       <c r="E73" s="2"/>
       <c r="F73" t="s" s="2">
-        <v>75</v>
+        <v>393</v>
       </c>
       <c r="G73" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="H73" t="s" s="2">
         <v>77</v>
@@ -10697,18 +10830,20 @@
         <v>85</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>394</v>
-      </c>
-      <c r="O73" s="2"/>
+        <v>397</v>
+      </c>
+      <c r="O73" t="s" s="2">
+        <v>398</v>
+      </c>
       <c r="P73" t="s" s="2">
         <v>77</v>
       </c>
@@ -10717,7 +10852,7 @@
         <v>77</v>
       </c>
       <c r="S73" t="s" s="2">
-        <v>343</v>
+        <v>77</v>
       </c>
       <c r="T73" t="s" s="2">
         <v>77</v>
@@ -10744,25 +10879,25 @@
         <v>77</v>
       </c>
       <c r="AB73" t="s" s="2">
-        <v>77</v>
+        <v>175</v>
       </c>
       <c r="AC73" t="s" s="2">
-        <v>77</v>
+        <v>399</v>
       </c>
       <c r="AD73" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE73" t="s" s="2">
-        <v>77</v>
+        <v>134</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>395</v>
+        <v>392</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH73" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="AI73" t="s" s="2">
         <v>77</v>
@@ -10771,16 +10906,16 @@
         <v>96</v>
       </c>
       <c r="AK73" t="s" s="2">
-        <v>189</v>
+        <v>400</v>
       </c>
       <c r="AL73" t="s" s="2">
-        <v>77</v>
+        <v>401</v>
       </c>
       <c r="AM73" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN73" t="s" s="2">
-        <v>189</v>
+        <v>402</v>
       </c>
       <c r="AO73" t="s" s="2">
         <v>77</v>
@@ -10788,24 +10923,26 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>419</v>
+        <v>403</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>397</v>
-      </c>
-      <c r="C74" s="2"/>
+        <v>392</v>
+      </c>
+      <c r="C74" t="s" s="2">
+        <v>404</v>
+      </c>
       <c r="D74" t="s" s="2">
         <v>77</v>
       </c>
       <c r="E74" s="2"/>
       <c r="F74" t="s" s="2">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="G74" t="s" s="2">
         <v>84</v>
       </c>
       <c r="H74" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="I74" t="s" s="2">
         <v>77</v>
@@ -10814,16 +10951,20 @@
         <v>85</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>240</v>
+        <v>394</v>
       </c>
       <c r="L74" t="s" s="2">
+        <v>395</v>
+      </c>
+      <c r="M74" t="s" s="2">
+        <v>396</v>
+      </c>
+      <c r="N74" t="s" s="2">
+        <v>397</v>
+      </c>
+      <c r="O74" t="s" s="2">
         <v>398</v>
       </c>
-      <c r="M74" t="s" s="2">
-        <v>399</v>
-      </c>
-      <c r="N74" s="2"/>
-      <c r="O74" s="2"/>
       <c r="P74" t="s" s="2">
         <v>77</v>
       </c>
@@ -10871,13 +11012,13 @@
         <v>77</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>400</v>
+        <v>392</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH74" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="AI74" t="s" s="2">
         <v>77</v>
@@ -10886,16 +11027,16 @@
         <v>96</v>
       </c>
       <c r="AK74" t="s" s="2">
-        <v>338</v>
+        <v>400</v>
       </c>
       <c r="AL74" t="s" s="2">
-        <v>77</v>
+        <v>401</v>
       </c>
       <c r="AM74" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN74" t="s" s="2">
-        <v>127</v>
+        <v>402</v>
       </c>
       <c r="AO74" t="s" s="2">
         <v>77</v>
@@ -10903,10 +11044,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>420</v>
+        <v>405</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>420</v>
+        <v>406</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -10926,23 +11067,19 @@
         <v>77</v>
       </c>
       <c r="J75" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>104</v>
+        <v>185</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>421</v>
+        <v>186</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>422</v>
-      </c>
-      <c r="N75" t="s" s="2">
-        <v>423</v>
-      </c>
-      <c r="O75" t="s" s="2">
-        <v>424</v>
-      </c>
+        <v>187</v>
+      </c>
+      <c r="N75" s="2"/>
+      <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
         <v>77</v>
       </c>
@@ -10966,13 +11103,13 @@
         <v>77</v>
       </c>
       <c r="X75" t="s" s="2">
-        <v>202</v>
+        <v>77</v>
       </c>
       <c r="Y75" t="s" s="2">
-        <v>425</v>
+        <v>77</v>
       </c>
       <c r="Z75" t="s" s="2">
-        <v>426</v>
+        <v>77</v>
       </c>
       <c r="AA75" t="s" s="2">
         <v>77</v>
@@ -10990,7 +11127,7 @@
         <v>77</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>420</v>
+        <v>188</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>75</v>
@@ -11002,19 +11139,19 @@
         <v>77</v>
       </c>
       <c r="AJ75" t="s" s="2">
-        <v>96</v>
+        <v>77</v>
       </c>
       <c r="AK75" t="s" s="2">
-        <v>427</v>
+        <v>189</v>
       </c>
       <c r="AL75" t="s" s="2">
-        <v>428</v>
+        <v>77</v>
       </c>
       <c r="AM75" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN75" t="s" s="2">
-        <v>429</v>
+        <v>77</v>
       </c>
       <c r="AO75" t="s" s="2">
         <v>77</v>
@@ -11022,46 +11159,44 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>430</v>
+        <v>407</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>430</v>
+        <v>408</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
-        <v>77</v>
+        <v>164</v>
       </c>
       <c r="E76" s="2"/>
       <c r="F76" t="s" s="2">
-        <v>84</v>
+        <v>75</v>
       </c>
       <c r="G76" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="H76" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="I76" t="s" s="2">
         <v>77</v>
       </c>
       <c r="J76" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>431</v>
+        <v>130</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>432</v>
+        <v>192</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>433</v>
+        <v>193</v>
       </c>
       <c r="N76" t="s" s="2">
-        <v>434</v>
-      </c>
-      <c r="O76" t="s" s="2">
-        <v>435</v>
-      </c>
+        <v>167</v>
+      </c>
+      <c r="O76" s="2"/>
       <c r="P76" t="s" s="2">
         <v>77</v>
       </c>
@@ -11097,54 +11232,54 @@
         <v>77</v>
       </c>
       <c r="AB76" t="s" s="2">
-        <v>77</v>
+        <v>133</v>
       </c>
       <c r="AC76" t="s" s="2">
-        <v>77</v>
+        <v>194</v>
       </c>
       <c r="AD76" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE76" t="s" s="2">
-        <v>77</v>
+        <v>134</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>430</v>
+        <v>195</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH76" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="AI76" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ76" t="s" s="2">
-        <v>96</v>
+        <v>136</v>
       </c>
       <c r="AK76" t="s" s="2">
-        <v>436</v>
+        <v>189</v>
       </c>
       <c r="AL76" t="s" s="2">
-        <v>437</v>
+        <v>77</v>
       </c>
       <c r="AM76" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN76" t="s" s="2">
-        <v>438</v>
+        <v>77</v>
       </c>
       <c r="AO76" t="s" s="2">
-        <v>439</v>
+        <v>77</v>
       </c>
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>440</v>
+        <v>409</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>440</v>
+        <v>410</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -11161,26 +11296,22 @@
         <v>77</v>
       </c>
       <c r="I77" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="J77" t="s" s="2">
         <v>85</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>441</v>
+        <v>104</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>442</v>
+        <v>411</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>443</v>
-      </c>
-      <c r="N77" t="s" s="2">
-        <v>444</v>
-      </c>
-      <c r="O77" t="s" s="2">
-        <v>445</v>
-      </c>
+        <v>412</v>
+      </c>
+      <c r="N77" s="2"/>
+      <c r="O77" s="2"/>
       <c r="P77" t="s" s="2">
         <v>77</v>
       </c>
@@ -11189,7 +11320,7 @@
         <v>77</v>
       </c>
       <c r="S77" t="s" s="2">
-        <v>77</v>
+        <v>413</v>
       </c>
       <c r="T77" t="s" s="2">
         <v>77</v>
@@ -11204,13 +11335,13 @@
         <v>77</v>
       </c>
       <c r="X77" t="s" s="2">
-        <v>77</v>
+        <v>202</v>
       </c>
       <c r="Y77" t="s" s="2">
-        <v>77</v>
+        <v>414</v>
       </c>
       <c r="Z77" t="s" s="2">
-        <v>77</v>
+        <v>415</v>
       </c>
       <c r="AA77" t="s" s="2">
         <v>77</v>
@@ -11228,7 +11359,7 @@
         <v>77</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>440</v>
+        <v>416</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>75</v>
@@ -11237,22 +11368,22 @@
         <v>84</v>
       </c>
       <c r="AI77" t="s" s="2">
-        <v>77</v>
+        <v>417</v>
       </c>
       <c r="AJ77" t="s" s="2">
         <v>96</v>
       </c>
       <c r="AK77" t="s" s="2">
-        <v>446</v>
+        <v>418</v>
       </c>
       <c r="AL77" t="s" s="2">
-        <v>189</v>
+        <v>77</v>
       </c>
       <c r="AM77" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN77" t="s" s="2">
-        <v>447</v>
+        <v>419</v>
       </c>
       <c r="AO77" t="s" s="2">
         <v>77</v>
@@ -11260,10 +11391,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>448</v>
+        <v>420</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>448</v>
+        <v>421</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11274,7 +11405,7 @@
         <v>75</v>
       </c>
       <c r="G78" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="H78" t="s" s="2">
         <v>77</v>
@@ -11286,19 +11417,19 @@
         <v>85</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>449</v>
+        <v>185</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>450</v>
+        <v>422</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>451</v>
+        <v>423</v>
       </c>
       <c r="N78" t="s" s="2">
-        <v>452</v>
+        <v>424</v>
       </c>
       <c r="O78" t="s" s="2">
-        <v>453</v>
+        <v>425</v>
       </c>
       <c r="P78" t="s" s="2">
         <v>77</v>
@@ -11347,13 +11478,13 @@
         <v>77</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>448</v>
+        <v>426</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH78" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="AI78" t="s" s="2">
         <v>77</v>
@@ -11362,16 +11493,16 @@
         <v>96</v>
       </c>
       <c r="AK78" t="s" s="2">
-        <v>454</v>
+        <v>427</v>
       </c>
       <c r="AL78" t="s" s="2">
-        <v>455</v>
+        <v>77</v>
       </c>
       <c r="AM78" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN78" t="s" s="2">
-        <v>456</v>
+        <v>428</v>
       </c>
       <c r="AO78" t="s" s="2">
         <v>77</v>
@@ -11379,10 +11510,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>457</v>
+        <v>429</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>457</v>
+        <v>430</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11390,7 +11521,7 @@
       </c>
       <c r="E79" s="2"/>
       <c r="F79" t="s" s="2">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="G79" t="s" s="2">
         <v>84</v>
@@ -11399,23 +11530,25 @@
         <v>77</v>
       </c>
       <c r="I79" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="J79" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>209</v>
+        <v>104</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>458</v>
+        <v>431</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>459</v>
-      </c>
-      <c r="N79" s="2"/>
+        <v>432</v>
+      </c>
+      <c r="N79" t="s" s="2">
+        <v>433</v>
+      </c>
       <c r="O79" t="s" s="2">
-        <v>460</v>
+        <v>434</v>
       </c>
       <c r="P79" t="s" s="2">
         <v>77</v>
@@ -11425,7 +11558,7 @@
         <v>77</v>
       </c>
       <c r="S79" t="s" s="2">
-        <v>77</v>
+        <v>435</v>
       </c>
       <c r="T79" t="s" s="2">
         <v>77</v>
@@ -11440,13 +11573,13 @@
         <v>77</v>
       </c>
       <c r="X79" t="s" s="2">
-        <v>214</v>
+        <v>202</v>
       </c>
       <c r="Y79" t="s" s="2">
-        <v>461</v>
+        <v>436</v>
       </c>
       <c r="Z79" t="s" s="2">
-        <v>462</v>
+        <v>437</v>
       </c>
       <c r="AA79" t="s" s="2">
         <v>77</v>
@@ -11464,7 +11597,7 @@
         <v>77</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>457</v>
+        <v>438</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>75</v>
@@ -11479,16 +11612,16 @@
         <v>96</v>
       </c>
       <c r="AK79" t="s" s="2">
-        <v>463</v>
+        <v>295</v>
       </c>
       <c r="AL79" t="s" s="2">
-        <v>464</v>
+        <v>77</v>
       </c>
       <c r="AM79" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN79" t="s" s="2">
-        <v>465</v>
+        <v>439</v>
       </c>
       <c r="AO79" t="s" s="2">
         <v>77</v>
@@ -11496,10 +11629,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>466</v>
+        <v>440</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>466</v>
+        <v>441</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -11519,23 +11652,21 @@
         <v>77</v>
       </c>
       <c r="J80" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>467</v>
+        <v>442</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>468</v>
+        <v>443</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>469</v>
+        <v>444</v>
       </c>
       <c r="N80" t="s" s="2">
-        <v>470</v>
-      </c>
-      <c r="O80" t="s" s="2">
-        <v>471</v>
-      </c>
+        <v>445</v>
+      </c>
+      <c r="O80" s="2"/>
       <c r="P80" t="s" s="2">
         <v>77</v>
       </c>
@@ -11544,7 +11675,7 @@
         <v>77</v>
       </c>
       <c r="S80" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="T80" t="s" s="2">
         <v>77</v>
@@ -11583,7 +11714,7 @@
         <v>77</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>466</v>
+        <v>446</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>75</v>
@@ -11598,16 +11729,16 @@
         <v>96</v>
       </c>
       <c r="AK80" t="s" s="2">
-        <v>472</v>
+        <v>189</v>
       </c>
       <c r="AL80" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM80" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN80" t="s" s="2">
         <v>189</v>
-      </c>
-      <c r="AM80" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN80" t="s" s="2">
-        <v>473</v>
       </c>
       <c r="AO80" t="s" s="2">
         <v>77</v>
@@ -11615,10 +11746,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>474</v>
+        <v>447</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>474</v>
+        <v>448</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -11629,7 +11760,7 @@
         <v>75</v>
       </c>
       <c r="G81" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="H81" t="s" s="2">
         <v>77</v>
@@ -11638,23 +11769,19 @@
         <v>77</v>
       </c>
       <c r="J81" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>475</v>
+        <v>240</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>476</v>
+        <v>449</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>477</v>
-      </c>
-      <c r="N81" t="s" s="2">
-        <v>478</v>
-      </c>
-      <c r="O81" t="s" s="2">
-        <v>479</v>
-      </c>
+        <v>450</v>
+      </c>
+      <c r="N81" s="2"/>
+      <c r="O81" s="2"/>
       <c r="P81" t="s" s="2">
         <v>77</v>
       </c>
@@ -11702,13 +11829,13 @@
         <v>77</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>474</v>
+        <v>451</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH81" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="AI81" t="s" s="2">
         <v>77</v>
@@ -11717,16 +11844,16 @@
         <v>96</v>
       </c>
       <c r="AK81" t="s" s="2">
-        <v>480</v>
+        <v>338</v>
       </c>
       <c r="AL81" t="s" s="2">
-        <v>189</v>
+        <v>77</v>
       </c>
       <c r="AM81" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN81" t="s" s="2">
-        <v>481</v>
+        <v>127</v>
       </c>
       <c r="AO81" t="s" s="2">
         <v>77</v>
@@ -11734,45 +11861,47 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>482</v>
+        <v>452</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>482</v>
-      </c>
-      <c r="C82" s="2"/>
+        <v>392</v>
+      </c>
+      <c r="C82" t="s" s="2">
+        <v>453</v>
+      </c>
       <c r="D82" t="s" s="2">
         <v>77</v>
       </c>
       <c r="E82" s="2"/>
       <c r="F82" t="s" s="2">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="G82" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="H82" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="I82" t="s" s="2">
         <v>77</v>
       </c>
       <c r="J82" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>483</v>
+        <v>394</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>484</v>
+        <v>395</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>485</v>
+        <v>396</v>
       </c>
       <c r="N82" t="s" s="2">
-        <v>486</v>
+        <v>397</v>
       </c>
       <c r="O82" t="s" s="2">
-        <v>487</v>
+        <v>398</v>
       </c>
       <c r="P82" t="s" s="2">
         <v>77</v>
@@ -11821,7 +11950,7 @@
         <v>77</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>482</v>
+        <v>392</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>75</v>
@@ -11833,19 +11962,19 @@
         <v>77</v>
       </c>
       <c r="AJ82" t="s" s="2">
-        <v>488</v>
+        <v>96</v>
       </c>
       <c r="AK82" t="s" s="2">
-        <v>489</v>
+        <v>400</v>
       </c>
       <c r="AL82" t="s" s="2">
-        <v>189</v>
+        <v>401</v>
       </c>
       <c r="AM82" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN82" t="s" s="2">
-        <v>77</v>
+        <v>402</v>
       </c>
       <c r="AO82" t="s" s="2">
         <v>77</v>
@@ -11853,10 +11982,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>490</v>
+        <v>454</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>490</v>
+        <v>406</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -11968,10 +12097,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>491</v>
+        <v>455</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>491</v>
+        <v>408</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -12041,16 +12170,16 @@
         <v>77</v>
       </c>
       <c r="AB84" t="s" s="2">
-        <v>77</v>
+        <v>133</v>
       </c>
       <c r="AC84" t="s" s="2">
-        <v>77</v>
+        <v>194</v>
       </c>
       <c r="AD84" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE84" t="s" s="2">
-        <v>77</v>
+        <v>134</v>
       </c>
       <c r="AF84" t="s" s="2">
         <v>195</v>
@@ -12085,46 +12214,42 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>492</v>
+        <v>456</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>492</v>
+        <v>410</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
-        <v>493</v>
+        <v>77</v>
       </c>
       <c r="E85" s="2"/>
       <c r="F85" t="s" s="2">
         <v>75</v>
       </c>
       <c r="G85" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="H85" t="s" s="2">
         <v>77</v>
       </c>
       <c r="I85" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="J85" t="s" s="2">
         <v>85</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>130</v>
+        <v>104</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>494</v>
+        <v>411</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>495</v>
-      </c>
-      <c r="N85" t="s" s="2">
-        <v>167</v>
-      </c>
-      <c r="O85" t="s" s="2">
-        <v>168</v>
-      </c>
+        <v>412</v>
+      </c>
+      <c r="N85" s="2"/>
+      <c r="O85" s="2"/>
       <c r="P85" t="s" s="2">
         <v>77</v>
       </c>
@@ -12133,7 +12258,7 @@
         <v>77</v>
       </c>
       <c r="S85" t="s" s="2">
-        <v>77</v>
+        <v>413</v>
       </c>
       <c r="T85" t="s" s="2">
         <v>77</v>
@@ -12148,13 +12273,13 @@
         <v>77</v>
       </c>
       <c r="X85" t="s" s="2">
-        <v>77</v>
+        <v>202</v>
       </c>
       <c r="Y85" t="s" s="2">
-        <v>77</v>
+        <v>414</v>
       </c>
       <c r="Z85" t="s" s="2">
-        <v>77</v>
+        <v>415</v>
       </c>
       <c r="AA85" t="s" s="2">
         <v>77</v>
@@ -12172,22 +12297,22 @@
         <v>77</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>496</v>
+        <v>416</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH85" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="AI85" t="s" s="2">
-        <v>77</v>
+        <v>417</v>
       </c>
       <c r="AJ85" t="s" s="2">
-        <v>136</v>
+        <v>96</v>
       </c>
       <c r="AK85" t="s" s="2">
-        <v>127</v>
+        <v>418</v>
       </c>
       <c r="AL85" t="s" s="2">
         <v>77</v>
@@ -12196,7 +12321,7 @@
         <v>77</v>
       </c>
       <c r="AN85" t="s" s="2">
-        <v>77</v>
+        <v>419</v>
       </c>
       <c r="AO85" t="s" s="2">
         <v>77</v>
@@ -12204,10 +12329,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>497</v>
+        <v>457</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>497</v>
+        <v>421</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -12218,7 +12343,7 @@
         <v>75</v>
       </c>
       <c r="G86" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="H86" t="s" s="2">
         <v>77</v>
@@ -12227,20 +12352,22 @@
         <v>77</v>
       </c>
       <c r="J86" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>209</v>
+        <v>185</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>498</v>
+        <v>422</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>499</v>
-      </c>
-      <c r="N86" s="2"/>
+        <v>423</v>
+      </c>
+      <c r="N86" t="s" s="2">
+        <v>424</v>
+      </c>
       <c r="O86" t="s" s="2">
-        <v>500</v>
+        <v>425</v>
       </c>
       <c r="P86" t="s" s="2">
         <v>77</v>
@@ -12265,13 +12392,13 @@
         <v>77</v>
       </c>
       <c r="X86" t="s" s="2">
-        <v>214</v>
+        <v>77</v>
       </c>
       <c r="Y86" t="s" s="2">
-        <v>501</v>
+        <v>77</v>
       </c>
       <c r="Z86" t="s" s="2">
-        <v>502</v>
+        <v>77</v>
       </c>
       <c r="AA86" t="s" s="2">
         <v>77</v>
@@ -12289,13 +12416,13 @@
         <v>77</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>497</v>
+        <v>426</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH86" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="AI86" t="s" s="2">
         <v>77</v>
@@ -12304,16 +12431,16 @@
         <v>96</v>
       </c>
       <c r="AK86" t="s" s="2">
-        <v>503</v>
+        <v>427</v>
       </c>
       <c r="AL86" t="s" s="2">
-        <v>189</v>
+        <v>77</v>
       </c>
       <c r="AM86" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN86" t="s" s="2">
-        <v>504</v>
+        <v>428</v>
       </c>
       <c r="AO86" t="s" s="2">
         <v>77</v>
@@ -12321,10 +12448,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>505</v>
+        <v>458</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>505</v>
+        <v>430</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -12332,7 +12459,7 @@
       </c>
       <c r="E87" s="2"/>
       <c r="F87" t="s" s="2">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="G87" t="s" s="2">
         <v>84</v>
@@ -12341,23 +12468,25 @@
         <v>77</v>
       </c>
       <c r="I87" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="J87" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>275</v>
+        <v>104</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>506</v>
+        <v>431</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>507</v>
-      </c>
-      <c r="N87" s="2"/>
+        <v>432</v>
+      </c>
+      <c r="N87" t="s" s="2">
+        <v>433</v>
+      </c>
       <c r="O87" t="s" s="2">
-        <v>508</v>
+        <v>434</v>
       </c>
       <c r="P87" t="s" s="2">
         <v>77</v>
@@ -12367,7 +12496,7 @@
         <v>77</v>
       </c>
       <c r="S87" t="s" s="2">
-        <v>77</v>
+        <v>435</v>
       </c>
       <c r="T87" t="s" s="2">
         <v>77</v>
@@ -12382,13 +12511,13 @@
         <v>77</v>
       </c>
       <c r="X87" t="s" s="2">
-        <v>77</v>
+        <v>202</v>
       </c>
       <c r="Y87" t="s" s="2">
-        <v>77</v>
+        <v>436</v>
       </c>
       <c r="Z87" t="s" s="2">
-        <v>77</v>
+        <v>437</v>
       </c>
       <c r="AA87" t="s" s="2">
         <v>77</v>
@@ -12406,7 +12535,7 @@
         <v>77</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>505</v>
+        <v>438</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>75</v>
@@ -12421,16 +12550,16 @@
         <v>96</v>
       </c>
       <c r="AK87" t="s" s="2">
-        <v>281</v>
+        <v>295</v>
       </c>
       <c r="AL87" t="s" s="2">
-        <v>189</v>
+        <v>77</v>
       </c>
       <c r="AM87" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN87" t="s" s="2">
-        <v>509</v>
+        <v>439</v>
       </c>
       <c r="AO87" t="s" s="2">
         <v>77</v>
@@ -12438,10 +12567,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>510</v>
+        <v>459</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>510</v>
+        <v>441</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -12452,7 +12581,7 @@
         <v>75</v>
       </c>
       <c r="G88" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="H88" t="s" s="2">
         <v>77</v>
@@ -12461,23 +12590,21 @@
         <v>77</v>
       </c>
       <c r="J88" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>344</v>
+        <v>442</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>511</v>
+        <v>443</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>512</v>
+        <v>444</v>
       </c>
       <c r="N88" t="s" s="2">
-        <v>513</v>
-      </c>
-      <c r="O88" t="s" s="2">
-        <v>348</v>
-      </c>
+        <v>445</v>
+      </c>
+      <c r="O88" s="2"/>
       <c r="P88" t="s" s="2">
         <v>77</v>
       </c>
@@ -12486,7 +12613,7 @@
         <v>77</v>
       </c>
       <c r="S88" t="s" s="2">
-        <v>77</v>
+        <v>460</v>
       </c>
       <c r="T88" t="s" s="2">
         <v>77</v>
@@ -12525,13 +12652,13 @@
         <v>77</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>510</v>
+        <v>446</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH88" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="AI88" t="s" s="2">
         <v>77</v>
@@ -12540,16 +12667,16 @@
         <v>96</v>
       </c>
       <c r="AK88" t="s" s="2">
-        <v>350</v>
+        <v>189</v>
       </c>
       <c r="AL88" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM88" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN88" t="s" s="2">
         <v>189</v>
-      </c>
-      <c r="AM88" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN88" t="s" s="2">
-        <v>514</v>
       </c>
       <c r="AO88" t="s" s="2">
         <v>77</v>
@@ -12557,10 +12684,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>515</v>
+        <v>461</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>515</v>
+        <v>448</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -12580,21 +12707,19 @@
         <v>77</v>
       </c>
       <c r="J89" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="K89" t="s" s="2">
+        <v>240</v>
+      </c>
+      <c r="L89" t="s" s="2">
         <v>449</v>
       </c>
-      <c r="L89" t="s" s="2">
-        <v>516</v>
-      </c>
       <c r="M89" t="s" s="2">
-        <v>517</v>
+        <v>450</v>
       </c>
       <c r="N89" s="2"/>
-      <c r="O89" t="s" s="2">
-        <v>518</v>
-      </c>
+      <c r="O89" s="2"/>
       <c r="P89" t="s" s="2">
         <v>77</v>
       </c>
@@ -12642,7 +12767,7 @@
         <v>77</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>515</v>
+        <v>451</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>75</v>
@@ -12657,16 +12782,16 @@
         <v>96</v>
       </c>
       <c r="AK89" t="s" s="2">
-        <v>454</v>
+        <v>338</v>
       </c>
       <c r="AL89" t="s" s="2">
-        <v>189</v>
+        <v>77</v>
       </c>
       <c r="AM89" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN89" t="s" s="2">
-        <v>519</v>
+        <v>127</v>
       </c>
       <c r="AO89" t="s" s="2">
         <v>77</v>
@@ -12674,43 +12799,47 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>520</v>
+        <v>462</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>520</v>
-      </c>
-      <c r="C90" s="2"/>
+        <v>392</v>
+      </c>
+      <c r="C90" t="s" s="2">
+        <v>463</v>
+      </c>
       <c r="D90" t="s" s="2">
         <v>77</v>
       </c>
       <c r="E90" s="2"/>
       <c r="F90" t="s" s="2">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="G90" t="s" s="2">
         <v>84</v>
       </c>
       <c r="H90" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="I90" t="s" s="2">
         <v>77</v>
       </c>
       <c r="J90" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>104</v>
+        <v>394</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>421</v>
+        <v>395</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>521</v>
-      </c>
-      <c r="N90" s="2"/>
+        <v>396</v>
+      </c>
+      <c r="N90" t="s" s="2">
+        <v>397</v>
+      </c>
       <c r="O90" t="s" s="2">
-        <v>522</v>
+        <v>398</v>
       </c>
       <c r="P90" t="s" s="2">
         <v>77</v>
@@ -12735,13 +12864,13 @@
         <v>77</v>
       </c>
       <c r="X90" t="s" s="2">
-        <v>202</v>
+        <v>77</v>
       </c>
       <c r="Y90" t="s" s="2">
-        <v>425</v>
+        <v>77</v>
       </c>
       <c r="Z90" t="s" s="2">
-        <v>426</v>
+        <v>77</v>
       </c>
       <c r="AA90" t="s" s="2">
         <v>77</v>
@@ -12759,13 +12888,13 @@
         <v>77</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>520</v>
+        <v>392</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH90" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="AI90" t="s" s="2">
         <v>77</v>
@@ -12774,16 +12903,16 @@
         <v>96</v>
       </c>
       <c r="AK90" t="s" s="2">
-        <v>427</v>
+        <v>400</v>
       </c>
       <c r="AL90" t="s" s="2">
-        <v>189</v>
+        <v>401</v>
       </c>
       <c r="AM90" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN90" t="s" s="2">
-        <v>523</v>
+        <v>402</v>
       </c>
       <c r="AO90" t="s" s="2">
         <v>77</v>
@@ -12791,10 +12920,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>524</v>
+        <v>464</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>524</v>
+        <v>406</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -12817,18 +12946,16 @@
         <v>77</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>248</v>
+        <v>185</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>525</v>
+        <v>186</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>526</v>
+        <v>187</v>
       </c>
       <c r="N91" s="2"/>
-      <c r="O91" t="s" s="2">
-        <v>527</v>
-      </c>
+      <c r="O91" s="2"/>
       <c r="P91" t="s" s="2">
         <v>77</v>
       </c>
@@ -12876,7 +13003,7 @@
         <v>77</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>524</v>
+        <v>188</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>75</v>
@@ -12885,22 +13012,22 @@
         <v>84</v>
       </c>
       <c r="AI91" t="s" s="2">
-        <v>528</v>
+        <v>77</v>
       </c>
       <c r="AJ91" t="s" s="2">
-        <v>96</v>
+        <v>77</v>
       </c>
       <c r="AK91" t="s" s="2">
-        <v>529</v>
+        <v>189</v>
       </c>
       <c r="AL91" t="s" s="2">
-        <v>189</v>
+        <v>77</v>
       </c>
       <c r="AM91" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN91" t="s" s="2">
-        <v>530</v>
+        <v>77</v>
       </c>
       <c r="AO91" t="s" s="2">
         <v>77</v>
@@ -12908,21 +13035,21 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>531</v>
+        <v>465</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>531</v>
+        <v>408</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
-        <v>77</v>
+        <v>164</v>
       </c>
       <c r="E92" s="2"/>
       <c r="F92" t="s" s="2">
         <v>75</v>
       </c>
       <c r="G92" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="H92" t="s" s="2">
         <v>77</v>
@@ -12934,15 +13061,17 @@
         <v>77</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>240</v>
+        <v>130</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>532</v>
+        <v>192</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>533</v>
-      </c>
-      <c r="N92" s="2"/>
+        <v>193</v>
+      </c>
+      <c r="N92" t="s" s="2">
+        <v>167</v>
+      </c>
       <c r="O92" s="2"/>
       <c r="P92" t="s" s="2">
         <v>77</v>
@@ -12979,37 +13108,37 @@
         <v>77</v>
       </c>
       <c r="AB92" t="s" s="2">
-        <v>77</v>
+        <v>133</v>
       </c>
       <c r="AC92" t="s" s="2">
-        <v>77</v>
+        <v>194</v>
       </c>
       <c r="AD92" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE92" t="s" s="2">
-        <v>77</v>
+        <v>134</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>531</v>
+        <v>195</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH92" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="AI92" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ92" t="s" s="2">
-        <v>96</v>
+        <v>136</v>
       </c>
       <c r="AK92" t="s" s="2">
-        <v>534</v>
+        <v>189</v>
       </c>
       <c r="AL92" t="s" s="2">
-        <v>189</v>
+        <v>77</v>
       </c>
       <c r="AM92" t="s" s="2">
         <v>77</v>
@@ -13023,10 +13152,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>535</v>
+        <v>466</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>535</v>
+        <v>410</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -13037,7 +13166,7 @@
         <v>75</v>
       </c>
       <c r="G93" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="H93" t="s" s="2">
         <v>77</v>
@@ -13046,23 +13175,19 @@
         <v>77</v>
       </c>
       <c r="J93" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>483</v>
+        <v>104</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>536</v>
+        <v>411</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>537</v>
-      </c>
-      <c r="N93" t="s" s="2">
-        <v>538</v>
-      </c>
-      <c r="O93" t="s" s="2">
-        <v>539</v>
-      </c>
+        <v>412</v>
+      </c>
+      <c r="N93" s="2"/>
+      <c r="O93" s="2"/>
       <c r="P93" t="s" s="2">
         <v>77</v>
       </c>
@@ -13071,7 +13196,7 @@
         <v>77</v>
       </c>
       <c r="S93" t="s" s="2">
-        <v>77</v>
+        <v>413</v>
       </c>
       <c r="T93" t="s" s="2">
         <v>77</v>
@@ -13086,13 +13211,13 @@
         <v>77</v>
       </c>
       <c r="X93" t="s" s="2">
-        <v>77</v>
+        <v>202</v>
       </c>
       <c r="Y93" t="s" s="2">
-        <v>77</v>
+        <v>414</v>
       </c>
       <c r="Z93" t="s" s="2">
-        <v>77</v>
+        <v>415</v>
       </c>
       <c r="AA93" t="s" s="2">
         <v>77</v>
@@ -13110,31 +13235,31 @@
         <v>77</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>535</v>
+        <v>416</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH93" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="AI93" t="s" s="2">
-        <v>77</v>
+        <v>417</v>
       </c>
       <c r="AJ93" t="s" s="2">
         <v>96</v>
       </c>
       <c r="AK93" t="s" s="2">
-        <v>540</v>
+        <v>418</v>
       </c>
       <c r="AL93" t="s" s="2">
-        <v>541</v>
+        <v>77</v>
       </c>
       <c r="AM93" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN93" t="s" s="2">
-        <v>77</v>
+        <v>419</v>
       </c>
       <c r="AO93" t="s" s="2">
         <v>77</v>
@@ -13142,10 +13267,10 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>542</v>
+        <v>467</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>542</v>
+        <v>421</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -13165,19 +13290,23 @@
         <v>77</v>
       </c>
       <c r="J94" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="K94" t="s" s="2">
         <v>185</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>186</v>
+        <v>422</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>187</v>
-      </c>
-      <c r="N94" s="2"/>
-      <c r="O94" s="2"/>
+        <v>423</v>
+      </c>
+      <c r="N94" t="s" s="2">
+        <v>424</v>
+      </c>
+      <c r="O94" t="s" s="2">
+        <v>425</v>
+      </c>
       <c r="P94" t="s" s="2">
         <v>77</v>
       </c>
@@ -13225,7 +13354,7 @@
         <v>77</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>188</v>
+        <v>426</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>75</v>
@@ -13237,10 +13366,10 @@
         <v>77</v>
       </c>
       <c r="AJ94" t="s" s="2">
-        <v>77</v>
+        <v>96</v>
       </c>
       <c r="AK94" t="s" s="2">
-        <v>189</v>
+        <v>427</v>
       </c>
       <c r="AL94" t="s" s="2">
         <v>77</v>
@@ -13249,7 +13378,7 @@
         <v>77</v>
       </c>
       <c r="AN94" t="s" s="2">
-        <v>77</v>
+        <v>428</v>
       </c>
       <c r="AO94" t="s" s="2">
         <v>77</v>
@@ -13257,44 +13386,46 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>543</v>
+        <v>468</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>543</v>
+        <v>430</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
-        <v>164</v>
+        <v>77</v>
       </c>
       <c r="E95" s="2"/>
       <c r="F95" t="s" s="2">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="G95" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="H95" t="s" s="2">
         <v>77</v>
       </c>
       <c r="I95" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="J95" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>130</v>
+        <v>104</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>192</v>
+        <v>431</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>193</v>
+        <v>432</v>
       </c>
       <c r="N95" t="s" s="2">
-        <v>167</v>
-      </c>
-      <c r="O95" s="2"/>
+        <v>433</v>
+      </c>
+      <c r="O95" t="s" s="2">
+        <v>434</v>
+      </c>
       <c r="P95" t="s" s="2">
         <v>77</v>
       </c>
@@ -13303,7 +13434,7 @@
         <v>77</v>
       </c>
       <c r="S95" t="s" s="2">
-        <v>77</v>
+        <v>435</v>
       </c>
       <c r="T95" t="s" s="2">
         <v>77</v>
@@ -13318,13 +13449,13 @@
         <v>77</v>
       </c>
       <c r="X95" t="s" s="2">
-        <v>77</v>
+        <v>202</v>
       </c>
       <c r="Y95" t="s" s="2">
-        <v>77</v>
+        <v>436</v>
       </c>
       <c r="Z95" t="s" s="2">
-        <v>77</v>
+        <v>437</v>
       </c>
       <c r="AA95" t="s" s="2">
         <v>77</v>
@@ -13342,22 +13473,22 @@
         <v>77</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>195</v>
+        <v>438</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH95" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="AI95" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ95" t="s" s="2">
-        <v>136</v>
+        <v>96</v>
       </c>
       <c r="AK95" t="s" s="2">
-        <v>189</v>
+        <v>295</v>
       </c>
       <c r="AL95" t="s" s="2">
         <v>77</v>
@@ -13366,7 +13497,7 @@
         <v>77</v>
       </c>
       <c r="AN95" t="s" s="2">
-        <v>77</v>
+        <v>439</v>
       </c>
       <c r="AO95" t="s" s="2">
         <v>77</v>
@@ -13374,46 +13505,44 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>544</v>
+        <v>469</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>544</v>
+        <v>441</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
-        <v>493</v>
+        <v>77</v>
       </c>
       <c r="E96" s="2"/>
       <c r="F96" t="s" s="2">
         <v>75</v>
       </c>
       <c r="G96" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="H96" t="s" s="2">
         <v>77</v>
       </c>
       <c r="I96" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="J96" t="s" s="2">
         <v>85</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>130</v>
+        <v>442</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>494</v>
+        <v>443</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>495</v>
+        <v>444</v>
       </c>
       <c r="N96" t="s" s="2">
-        <v>167</v>
-      </c>
-      <c r="O96" t="s" s="2">
-        <v>168</v>
-      </c>
+        <v>445</v>
+      </c>
+      <c r="O96" s="2"/>
       <c r="P96" t="s" s="2">
         <v>77</v>
       </c>
@@ -13422,7 +13551,7 @@
         <v>77</v>
       </c>
       <c r="S96" t="s" s="2">
-        <v>77</v>
+        <v>393</v>
       </c>
       <c r="T96" t="s" s="2">
         <v>77</v>
@@ -13461,22 +13590,22 @@
         <v>77</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>496</v>
+        <v>446</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH96" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="AI96" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ96" t="s" s="2">
-        <v>136</v>
+        <v>96</v>
       </c>
       <c r="AK96" t="s" s="2">
-        <v>127</v>
+        <v>189</v>
       </c>
       <c r="AL96" t="s" s="2">
         <v>77</v>
@@ -13485,7 +13614,7 @@
         <v>77</v>
       </c>
       <c r="AN96" t="s" s="2">
-        <v>77</v>
+        <v>189</v>
       </c>
       <c r="AO96" t="s" s="2">
         <v>77</v>
@@ -13493,10 +13622,10 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>545</v>
+        <v>470</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>545</v>
+        <v>448</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -13504,7 +13633,7 @@
       </c>
       <c r="E97" s="2"/>
       <c r="F97" t="s" s="2">
-        <v>84</v>
+        <v>75</v>
       </c>
       <c r="G97" t="s" s="2">
         <v>84</v>
@@ -13516,23 +13645,19 @@
         <v>77</v>
       </c>
       <c r="J97" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>209</v>
+        <v>240</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>546</v>
+        <v>449</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>547</v>
-      </c>
-      <c r="N97" t="s" s="2">
-        <v>548</v>
-      </c>
-      <c r="O97" t="s" s="2">
-        <v>549</v>
-      </c>
+        <v>450</v>
+      </c>
+      <c r="N97" s="2"/>
+      <c r="O97" s="2"/>
       <c r="P97" t="s" s="2">
         <v>77</v>
       </c>
@@ -13556,13 +13681,13 @@
         <v>77</v>
       </c>
       <c r="X97" t="s" s="2">
-        <v>108</v>
+        <v>77</v>
       </c>
       <c r="Y97" t="s" s="2">
-        <v>109</v>
+        <v>77</v>
       </c>
       <c r="Z97" t="s" s="2">
-        <v>110</v>
+        <v>77</v>
       </c>
       <c r="AA97" t="s" s="2">
         <v>77</v>
@@ -13580,10 +13705,10 @@
         <v>77</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>545</v>
+        <v>451</v>
       </c>
       <c r="AG97" t="s" s="2">
-        <v>84</v>
+        <v>75</v>
       </c>
       <c r="AH97" t="s" s="2">
         <v>84</v>
@@ -13595,16 +13720,16 @@
         <v>96</v>
       </c>
       <c r="AK97" t="s" s="2">
-        <v>550</v>
+        <v>338</v>
       </c>
       <c r="AL97" t="s" s="2">
-        <v>551</v>
+        <v>77</v>
       </c>
       <c r="AM97" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN97" t="s" s="2">
-        <v>552</v>
+        <v>127</v>
       </c>
       <c r="AO97" t="s" s="2">
         <v>77</v>
@@ -13612,10 +13737,10 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>553</v>
+        <v>471</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>553</v>
+        <v>471</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -13635,22 +13760,22 @@
         <v>77</v>
       </c>
       <c r="J98" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="K98" t="s" s="2">
-        <v>266</v>
+        <v>104</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>554</v>
+        <v>472</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>555</v>
+        <v>473</v>
       </c>
       <c r="N98" t="s" s="2">
-        <v>556</v>
+        <v>474</v>
       </c>
       <c r="O98" t="s" s="2">
-        <v>557</v>
+        <v>475</v>
       </c>
       <c r="P98" t="s" s="2">
         <v>77</v>
@@ -13675,13 +13800,13 @@
         <v>77</v>
       </c>
       <c r="X98" t="s" s="2">
-        <v>77</v>
+        <v>202</v>
       </c>
       <c r="Y98" t="s" s="2">
-        <v>77</v>
+        <v>476</v>
       </c>
       <c r="Z98" t="s" s="2">
-        <v>77</v>
+        <v>477</v>
       </c>
       <c r="AA98" t="s" s="2">
         <v>77</v>
@@ -13699,7 +13824,7 @@
         <v>77</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>553</v>
+        <v>471</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>75</v>
@@ -13714,16 +13839,16 @@
         <v>96</v>
       </c>
       <c r="AK98" t="s" s="2">
-        <v>558</v>
+        <v>478</v>
       </c>
       <c r="AL98" t="s" s="2">
-        <v>559</v>
+        <v>479</v>
       </c>
       <c r="AM98" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN98" t="s" s="2">
-        <v>560</v>
+        <v>480</v>
       </c>
       <c r="AO98" t="s" s="2">
         <v>77</v>
@@ -13731,44 +13856,46 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>561</v>
+        <v>481</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>561</v>
+        <v>481</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
-        <v>562</v>
+        <v>77</v>
       </c>
       <c r="E99" s="2"/>
       <c r="F99" t="s" s="2">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="G99" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="H99" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="I99" t="s" s="2">
         <v>77</v>
       </c>
       <c r="J99" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="K99" t="s" s="2">
-        <v>563</v>
+        <v>482</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>564</v>
+        <v>483</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>565</v>
+        <v>484</v>
       </c>
       <c r="N99" t="s" s="2">
-        <v>566</v>
-      </c>
-      <c r="O99" s="2"/>
+        <v>485</v>
+      </c>
+      <c r="O99" t="s" s="2">
+        <v>486</v>
+      </c>
       <c r="P99" t="s" s="2">
         <v>77</v>
       </c>
@@ -13816,13 +13943,13 @@
         <v>77</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>561</v>
+        <v>481</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH99" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="AI99" t="s" s="2">
         <v>77</v>
@@ -13831,27 +13958,27 @@
         <v>96</v>
       </c>
       <c r="AK99" t="s" s="2">
-        <v>567</v>
+        <v>487</v>
       </c>
       <c r="AL99" t="s" s="2">
-        <v>189</v>
+        <v>488</v>
       </c>
       <c r="AM99" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN99" t="s" s="2">
-        <v>568</v>
+        <v>489</v>
       </c>
       <c r="AO99" t="s" s="2">
-        <v>77</v>
+        <v>490</v>
       </c>
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>569</v>
+        <v>491</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>569</v>
+        <v>491</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -13868,25 +13995,25 @@
         <v>77</v>
       </c>
       <c r="I100" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="J100" t="s" s="2">
         <v>85</v>
       </c>
       <c r="K100" t="s" s="2">
-        <v>248</v>
+        <v>492</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>570</v>
+        <v>493</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>571</v>
+        <v>494</v>
       </c>
       <c r="N100" t="s" s="2">
-        <v>572</v>
+        <v>495</v>
       </c>
       <c r="O100" t="s" s="2">
-        <v>573</v>
+        <v>496</v>
       </c>
       <c r="P100" t="s" s="2">
         <v>77</v>
@@ -13935,7 +14062,7 @@
         <v>77</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>569</v>
+        <v>491</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>75</v>
@@ -13950,16 +14077,16 @@
         <v>96</v>
       </c>
       <c r="AK100" t="s" s="2">
-        <v>529</v>
+        <v>497</v>
       </c>
       <c r="AL100" t="s" s="2">
-        <v>574</v>
+        <v>189</v>
       </c>
       <c r="AM100" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN100" t="s" s="2">
-        <v>77</v>
+        <v>498</v>
       </c>
       <c r="AO100" t="s" s="2">
         <v>77</v>
@@ -13967,10 +14094,10 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>575</v>
+        <v>499</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>575</v>
+        <v>499</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -13987,25 +14114,25 @@
         <v>77</v>
       </c>
       <c r="I101" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="J101" t="s" s="2">
         <v>85</v>
       </c>
       <c r="K101" t="s" s="2">
-        <v>483</v>
+        <v>500</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>576</v>
+        <v>501</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>577</v>
+        <v>502</v>
       </c>
       <c r="N101" t="s" s="2">
-        <v>578</v>
+        <v>503</v>
       </c>
       <c r="O101" t="s" s="2">
-        <v>579</v>
+        <v>504</v>
       </c>
       <c r="P101" t="s" s="2">
         <v>77</v>
@@ -14054,7 +14181,7 @@
         <v>77</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>575</v>
+        <v>499</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>75</v>
@@ -14069,16 +14196,16 @@
         <v>96</v>
       </c>
       <c r="AK101" t="s" s="2">
-        <v>580</v>
+        <v>505</v>
       </c>
       <c r="AL101" t="s" s="2">
-        <v>189</v>
+        <v>506</v>
       </c>
       <c r="AM101" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN101" t="s" s="2">
-        <v>77</v>
+        <v>507</v>
       </c>
       <c r="AO101" t="s" s="2">
         <v>77</v>
@@ -14086,10 +14213,10 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>581</v>
+        <v>508</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>581</v>
+        <v>508</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -14112,16 +14239,18 @@
         <v>77</v>
       </c>
       <c r="K102" t="s" s="2">
-        <v>185</v>
+        <v>209</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>186</v>
+        <v>509</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>187</v>
+        <v>510</v>
       </c>
       <c r="N102" s="2"/>
-      <c r="O102" s="2"/>
+      <c r="O102" t="s" s="2">
+        <v>511</v>
+      </c>
       <c r="P102" t="s" s="2">
         <v>77</v>
       </c>
@@ -14145,13 +14274,13 @@
         <v>77</v>
       </c>
       <c r="X102" t="s" s="2">
-        <v>77</v>
+        <v>214</v>
       </c>
       <c r="Y102" t="s" s="2">
-        <v>77</v>
+        <v>512</v>
       </c>
       <c r="Z102" t="s" s="2">
-        <v>77</v>
+        <v>513</v>
       </c>
       <c r="AA102" t="s" s="2">
         <v>77</v>
@@ -14169,7 +14298,7 @@
         <v>77</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>188</v>
+        <v>508</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>75</v>
@@ -14181,19 +14310,19 @@
         <v>77</v>
       </c>
       <c r="AJ102" t="s" s="2">
-        <v>77</v>
+        <v>96</v>
       </c>
       <c r="AK102" t="s" s="2">
-        <v>189</v>
+        <v>514</v>
       </c>
       <c r="AL102" t="s" s="2">
-        <v>77</v>
+        <v>515</v>
       </c>
       <c r="AM102" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN102" t="s" s="2">
-        <v>77</v>
+        <v>516</v>
       </c>
       <c r="AO102" t="s" s="2">
         <v>77</v>
@@ -14201,21 +14330,21 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>582</v>
+        <v>517</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>582</v>
+        <v>517</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
-        <v>164</v>
+        <v>77</v>
       </c>
       <c r="E103" s="2"/>
       <c r="F103" t="s" s="2">
         <v>75</v>
       </c>
       <c r="G103" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="H103" t="s" s="2">
         <v>77</v>
@@ -14227,18 +14356,20 @@
         <v>77</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>130</v>
+        <v>518</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>192</v>
+        <v>519</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>193</v>
+        <v>520</v>
       </c>
       <c r="N103" t="s" s="2">
-        <v>167</v>
-      </c>
-      <c r="O103" s="2"/>
+        <v>521</v>
+      </c>
+      <c r="O103" t="s" s="2">
+        <v>522</v>
+      </c>
       <c r="P103" t="s" s="2">
         <v>77</v>
       </c>
@@ -14286,31 +14417,31 @@
         <v>77</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>195</v>
+        <v>517</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH103" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="AI103" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ103" t="s" s="2">
-        <v>136</v>
+        <v>96</v>
       </c>
       <c r="AK103" t="s" s="2">
+        <v>523</v>
+      </c>
+      <c r="AL103" t="s" s="2">
         <v>189</v>
       </c>
-      <c r="AL103" t="s" s="2">
-        <v>77</v>
-      </c>
       <c r="AM103" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN103" t="s" s="2">
-        <v>77</v>
+        <v>524</v>
       </c>
       <c r="AO103" t="s" s="2">
         <v>77</v>
@@ -14318,14 +14449,14 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>583</v>
+        <v>525</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>583</v>
+        <v>525</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
-        <v>493</v>
+        <v>77</v>
       </c>
       <c r="E104" s="2"/>
       <c r="F104" t="s" s="2">
@@ -14338,25 +14469,25 @@
         <v>77</v>
       </c>
       <c r="I104" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="J104" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="K104" t="s" s="2">
-        <v>130</v>
+        <v>526</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>494</v>
+        <v>527</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>495</v>
+        <v>528</v>
       </c>
       <c r="N104" t="s" s="2">
-        <v>167</v>
+        <v>529</v>
       </c>
       <c r="O104" t="s" s="2">
-        <v>168</v>
+        <v>530</v>
       </c>
       <c r="P104" t="s" s="2">
         <v>77</v>
@@ -14405,7 +14536,7 @@
         <v>77</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>496</v>
+        <v>525</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>75</v>
@@ -14417,19 +14548,19 @@
         <v>77</v>
       </c>
       <c r="AJ104" t="s" s="2">
-        <v>136</v>
+        <v>96</v>
       </c>
       <c r="AK104" t="s" s="2">
-        <v>127</v>
+        <v>531</v>
       </c>
       <c r="AL104" t="s" s="2">
-        <v>77</v>
+        <v>189</v>
       </c>
       <c r="AM104" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN104" t="s" s="2">
-        <v>77</v>
+        <v>532</v>
       </c>
       <c r="AO104" t="s" s="2">
         <v>77</v>
@@ -14437,10 +14568,10 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>584</v>
+        <v>533</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>584</v>
+        <v>533</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -14448,10 +14579,10 @@
       </c>
       <c r="E105" s="2"/>
       <c r="F105" t="s" s="2">
-        <v>84</v>
+        <v>75</v>
       </c>
       <c r="G105" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="H105" t="s" s="2">
         <v>77</v>
@@ -14460,21 +14591,23 @@
         <v>77</v>
       </c>
       <c r="J105" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="K105" t="s" s="2">
-        <v>585</v>
+        <v>534</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>586</v>
+        <v>535</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>587</v>
+        <v>536</v>
       </c>
       <c r="N105" t="s" s="2">
-        <v>588</v>
-      </c>
-      <c r="O105" s="2"/>
+        <v>537</v>
+      </c>
+      <c r="O105" t="s" s="2">
+        <v>538</v>
+      </c>
       <c r="P105" t="s" s="2">
         <v>77</v>
       </c>
@@ -14522,22 +14655,22 @@
         <v>77</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>584</v>
+        <v>533</v>
       </c>
       <c r="AG105" t="s" s="2">
-        <v>84</v>
+        <v>75</v>
       </c>
       <c r="AH105" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="AI105" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ105" t="s" s="2">
-        <v>96</v>
+        <v>539</v>
       </c>
       <c r="AK105" t="s" s="2">
-        <v>177</v>
+        <v>540</v>
       </c>
       <c r="AL105" t="s" s="2">
         <v>189</v>
@@ -14546,7 +14679,7 @@
         <v>77</v>
       </c>
       <c r="AN105" t="s" s="2">
-        <v>589</v>
+        <v>77</v>
       </c>
       <c r="AO105" t="s" s="2">
         <v>77</v>
@@ -14554,10 +14687,10 @@
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>590</v>
+        <v>541</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>590</v>
+        <v>541</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -14565,7 +14698,7 @@
       </c>
       <c r="E106" s="2"/>
       <c r="F106" t="s" s="2">
-        <v>84</v>
+        <v>75</v>
       </c>
       <c r="G106" t="s" s="2">
         <v>84</v>
@@ -14577,16 +14710,16 @@
         <v>77</v>
       </c>
       <c r="J106" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="K106" t="s" s="2">
-        <v>104</v>
+        <v>185</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>591</v>
+        <v>186</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>592</v>
+        <v>187</v>
       </c>
       <c r="N106" s="2"/>
       <c r="O106" s="2"/>
@@ -14613,62 +14746,2763 @@
         <v>77</v>
       </c>
       <c r="X106" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y106" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z106" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA106" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB106" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC106" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD106" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE106" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF106" t="s" s="2">
+        <v>188</v>
+      </c>
+      <c r="AG106" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH106" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI106" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ106" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AK106" t="s" s="2">
+        <v>189</v>
+      </c>
+      <c r="AL106" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM106" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN106" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AO106" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="107" hidden="true">
+      <c r="A107" t="s" s="2">
+        <v>542</v>
+      </c>
+      <c r="B107" t="s" s="2">
+        <v>542</v>
+      </c>
+      <c r="C107" s="2"/>
+      <c r="D107" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="E107" s="2"/>
+      <c r="F107" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G107" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H107" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I107" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J107" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K107" t="s" s="2">
+        <v>130</v>
+      </c>
+      <c r="L107" t="s" s="2">
+        <v>192</v>
+      </c>
+      <c r="M107" t="s" s="2">
+        <v>193</v>
+      </c>
+      <c r="N107" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="O107" s="2"/>
+      <c r="P107" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q107" s="2"/>
+      <c r="R107" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S107" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T107" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U107" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V107" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W107" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X107" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y107" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z107" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA107" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB107" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC107" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD107" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE107" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF107" t="s" s="2">
+        <v>195</v>
+      </c>
+      <c r="AG107" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH107" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI107" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ107" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="AK107" t="s" s="2">
+        <v>189</v>
+      </c>
+      <c r="AL107" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM107" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN107" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AO107" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="108" hidden="true">
+      <c r="A108" t="s" s="2">
+        <v>543</v>
+      </c>
+      <c r="B108" t="s" s="2">
+        <v>543</v>
+      </c>
+      <c r="C108" s="2"/>
+      <c r="D108" t="s" s="2">
+        <v>544</v>
+      </c>
+      <c r="E108" s="2"/>
+      <c r="F108" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G108" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H108" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I108" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="J108" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="K108" t="s" s="2">
+        <v>130</v>
+      </c>
+      <c r="L108" t="s" s="2">
+        <v>545</v>
+      </c>
+      <c r="M108" t="s" s="2">
+        <v>546</v>
+      </c>
+      <c r="N108" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="O108" t="s" s="2">
+        <v>168</v>
+      </c>
+      <c r="P108" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q108" s="2"/>
+      <c r="R108" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S108" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T108" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U108" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V108" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W108" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X108" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y108" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z108" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA108" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB108" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC108" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD108" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE108" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF108" t="s" s="2">
+        <v>547</v>
+      </c>
+      <c r="AG108" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH108" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI108" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ108" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="AK108" t="s" s="2">
+        <v>127</v>
+      </c>
+      <c r="AL108" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM108" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN108" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AO108" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="109" hidden="true">
+      <c r="A109" t="s" s="2">
+        <v>548</v>
+      </c>
+      <c r="B109" t="s" s="2">
+        <v>548</v>
+      </c>
+      <c r="C109" s="2"/>
+      <c r="D109" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E109" s="2"/>
+      <c r="F109" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G109" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H109" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I109" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J109" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K109" t="s" s="2">
+        <v>209</v>
+      </c>
+      <c r="L109" t="s" s="2">
+        <v>549</v>
+      </c>
+      <c r="M109" t="s" s="2">
+        <v>550</v>
+      </c>
+      <c r="N109" s="2"/>
+      <c r="O109" t="s" s="2">
+        <v>551</v>
+      </c>
+      <c r="P109" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q109" s="2"/>
+      <c r="R109" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S109" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T109" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U109" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V109" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W109" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X109" t="s" s="2">
+        <v>214</v>
+      </c>
+      <c r="Y109" t="s" s="2">
+        <v>552</v>
+      </c>
+      <c r="Z109" t="s" s="2">
+        <v>553</v>
+      </c>
+      <c r="AA109" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB109" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC109" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD109" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE109" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF109" t="s" s="2">
+        <v>548</v>
+      </c>
+      <c r="AG109" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH109" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI109" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ109" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="AK109" t="s" s="2">
+        <v>554</v>
+      </c>
+      <c r="AL109" t="s" s="2">
+        <v>189</v>
+      </c>
+      <c r="AM109" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN109" t="s" s="2">
+        <v>555</v>
+      </c>
+      <c r="AO109" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="110" hidden="true">
+      <c r="A110" t="s" s="2">
+        <v>556</v>
+      </c>
+      <c r="B110" t="s" s="2">
+        <v>556</v>
+      </c>
+      <c r="C110" s="2"/>
+      <c r="D110" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E110" s="2"/>
+      <c r="F110" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G110" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="H110" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I110" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J110" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K110" t="s" s="2">
+        <v>275</v>
+      </c>
+      <c r="L110" t="s" s="2">
+        <v>557</v>
+      </c>
+      <c r="M110" t="s" s="2">
+        <v>558</v>
+      </c>
+      <c r="N110" s="2"/>
+      <c r="O110" t="s" s="2">
+        <v>559</v>
+      </c>
+      <c r="P110" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q110" s="2"/>
+      <c r="R110" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S110" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T110" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U110" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V110" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W110" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X110" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y110" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z110" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA110" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB110" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC110" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD110" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE110" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF110" t="s" s="2">
+        <v>556</v>
+      </c>
+      <c r="AG110" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH110" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI110" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ110" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="AK110" t="s" s="2">
+        <v>281</v>
+      </c>
+      <c r="AL110" t="s" s="2">
+        <v>189</v>
+      </c>
+      <c r="AM110" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN110" t="s" s="2">
+        <v>560</v>
+      </c>
+      <c r="AO110" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="111" hidden="true">
+      <c r="A111" t="s" s="2">
+        <v>561</v>
+      </c>
+      <c r="B111" t="s" s="2">
+        <v>561</v>
+      </c>
+      <c r="C111" s="2"/>
+      <c r="D111" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E111" s="2"/>
+      <c r="F111" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G111" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H111" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I111" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J111" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K111" t="s" s="2">
+        <v>394</v>
+      </c>
+      <c r="L111" t="s" s="2">
+        <v>562</v>
+      </c>
+      <c r="M111" t="s" s="2">
+        <v>563</v>
+      </c>
+      <c r="N111" t="s" s="2">
+        <v>564</v>
+      </c>
+      <c r="O111" t="s" s="2">
+        <v>398</v>
+      </c>
+      <c r="P111" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q111" s="2"/>
+      <c r="R111" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S111" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T111" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U111" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V111" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W111" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X111" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y111" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z111" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA111" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB111" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC111" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD111" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE111" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF111" t="s" s="2">
+        <v>561</v>
+      </c>
+      <c r="AG111" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH111" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI111" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ111" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="AK111" t="s" s="2">
+        <v>400</v>
+      </c>
+      <c r="AL111" t="s" s="2">
+        <v>189</v>
+      </c>
+      <c r="AM111" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN111" t="s" s="2">
+        <v>565</v>
+      </c>
+      <c r="AO111" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="112" hidden="true">
+      <c r="A112" t="s" s="2">
+        <v>566</v>
+      </c>
+      <c r="B112" t="s" s="2">
+        <v>566</v>
+      </c>
+      <c r="C112" s="2"/>
+      <c r="D112" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E112" s="2"/>
+      <c r="F112" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G112" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="H112" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I112" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J112" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K112" t="s" s="2">
+        <v>500</v>
+      </c>
+      <c r="L112" t="s" s="2">
+        <v>567</v>
+      </c>
+      <c r="M112" t="s" s="2">
+        <v>568</v>
+      </c>
+      <c r="N112" s="2"/>
+      <c r="O112" t="s" s="2">
+        <v>569</v>
+      </c>
+      <c r="P112" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q112" s="2"/>
+      <c r="R112" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S112" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T112" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U112" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V112" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W112" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X112" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y112" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z112" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA112" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB112" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC112" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD112" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE112" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF112" t="s" s="2">
+        <v>566</v>
+      </c>
+      <c r="AG112" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH112" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI112" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ112" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="AK112" t="s" s="2">
+        <v>505</v>
+      </c>
+      <c r="AL112" t="s" s="2">
+        <v>189</v>
+      </c>
+      <c r="AM112" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN112" t="s" s="2">
+        <v>570</v>
+      </c>
+      <c r="AO112" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="113" hidden="true">
+      <c r="A113" t="s" s="2">
+        <v>571</v>
+      </c>
+      <c r="B113" t="s" s="2">
+        <v>571</v>
+      </c>
+      <c r="C113" s="2"/>
+      <c r="D113" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E113" s="2"/>
+      <c r="F113" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G113" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="H113" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I113" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J113" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K113" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="L113" t="s" s="2">
+        <v>472</v>
+      </c>
+      <c r="M113" t="s" s="2">
+        <v>572</v>
+      </c>
+      <c r="N113" s="2"/>
+      <c r="O113" t="s" s="2">
+        <v>573</v>
+      </c>
+      <c r="P113" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q113" s="2"/>
+      <c r="R113" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S113" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T113" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U113" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V113" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W113" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X113" t="s" s="2">
         <v>202</v>
       </c>
-      <c r="Y106" t="s" s="2">
+      <c r="Y113" t="s" s="2">
+        <v>476</v>
+      </c>
+      <c r="Z113" t="s" s="2">
+        <v>477</v>
+      </c>
+      <c r="AA113" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB113" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC113" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD113" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE113" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF113" t="s" s="2">
+        <v>571</v>
+      </c>
+      <c r="AG113" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH113" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI113" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ113" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="AK113" t="s" s="2">
+        <v>478</v>
+      </c>
+      <c r="AL113" t="s" s="2">
+        <v>189</v>
+      </c>
+      <c r="AM113" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN113" t="s" s="2">
+        <v>574</v>
+      </c>
+      <c r="AO113" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="114" hidden="true">
+      <c r="A114" t="s" s="2">
+        <v>575</v>
+      </c>
+      <c r="B114" t="s" s="2">
+        <v>575</v>
+      </c>
+      <c r="C114" s="2"/>
+      <c r="D114" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E114" s="2"/>
+      <c r="F114" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G114" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="H114" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I114" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J114" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K114" t="s" s="2">
+        <v>248</v>
+      </c>
+      <c r="L114" t="s" s="2">
+        <v>576</v>
+      </c>
+      <c r="M114" t="s" s="2">
+        <v>577</v>
+      </c>
+      <c r="N114" s="2"/>
+      <c r="O114" t="s" s="2">
+        <v>578</v>
+      </c>
+      <c r="P114" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q114" s="2"/>
+      <c r="R114" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S114" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T114" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U114" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V114" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W114" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X114" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y114" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z114" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA114" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB114" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC114" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD114" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE114" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF114" t="s" s="2">
+        <v>575</v>
+      </c>
+      <c r="AG114" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH114" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI114" t="s" s="2">
+        <v>579</v>
+      </c>
+      <c r="AJ114" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="AK114" t="s" s="2">
+        <v>580</v>
+      </c>
+      <c r="AL114" t="s" s="2">
+        <v>189</v>
+      </c>
+      <c r="AM114" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN114" t="s" s="2">
+        <v>581</v>
+      </c>
+      <c r="AO114" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="115" hidden="true">
+      <c r="A115" t="s" s="2">
+        <v>582</v>
+      </c>
+      <c r="B115" t="s" s="2">
+        <v>582</v>
+      </c>
+      <c r="C115" s="2"/>
+      <c r="D115" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E115" s="2"/>
+      <c r="F115" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G115" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="H115" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I115" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J115" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K115" t="s" s="2">
+        <v>240</v>
+      </c>
+      <c r="L115" t="s" s="2">
+        <v>583</v>
+      </c>
+      <c r="M115" t="s" s="2">
+        <v>584</v>
+      </c>
+      <c r="N115" s="2"/>
+      <c r="O115" s="2"/>
+      <c r="P115" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q115" s="2"/>
+      <c r="R115" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S115" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T115" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U115" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V115" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W115" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X115" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y115" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z115" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA115" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB115" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC115" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD115" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE115" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF115" t="s" s="2">
+        <v>582</v>
+      </c>
+      <c r="AG115" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH115" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI115" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ115" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="AK115" t="s" s="2">
+        <v>585</v>
+      </c>
+      <c r="AL115" t="s" s="2">
+        <v>189</v>
+      </c>
+      <c r="AM115" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN115" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AO115" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="116" hidden="true">
+      <c r="A116" t="s" s="2">
+        <v>586</v>
+      </c>
+      <c r="B116" t="s" s="2">
+        <v>586</v>
+      </c>
+      <c r="C116" s="2"/>
+      <c r="D116" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E116" s="2"/>
+      <c r="F116" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G116" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H116" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I116" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J116" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K116" t="s" s="2">
+        <v>534</v>
+      </c>
+      <c r="L116" t="s" s="2">
+        <v>587</v>
+      </c>
+      <c r="M116" t="s" s="2">
+        <v>588</v>
+      </c>
+      <c r="N116" t="s" s="2">
+        <v>589</v>
+      </c>
+      <c r="O116" t="s" s="2">
+        <v>590</v>
+      </c>
+      <c r="P116" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q116" s="2"/>
+      <c r="R116" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S116" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T116" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U116" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V116" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W116" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X116" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y116" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z116" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA116" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB116" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC116" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD116" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE116" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF116" t="s" s="2">
+        <v>586</v>
+      </c>
+      <c r="AG116" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH116" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI116" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ116" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="AK116" t="s" s="2">
+        <v>591</v>
+      </c>
+      <c r="AL116" t="s" s="2">
         <v>592</v>
       </c>
-      <c r="Z106" t="s" s="2">
+      <c r="AM116" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN116" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AO116" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="117" hidden="true">
+      <c r="A117" t="s" s="2">
         <v>593</v>
       </c>
-      <c r="AA106" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB106" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC106" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD106" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE106" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF106" t="s" s="2">
-        <v>590</v>
-      </c>
-      <c r="AG106" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AH106" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AI106" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ106" t="s" s="2">
+      <c r="B117" t="s" s="2">
+        <v>593</v>
+      </c>
+      <c r="C117" s="2"/>
+      <c r="D117" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E117" s="2"/>
+      <c r="F117" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G117" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="H117" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I117" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J117" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K117" t="s" s="2">
+        <v>185</v>
+      </c>
+      <c r="L117" t="s" s="2">
+        <v>186</v>
+      </c>
+      <c r="M117" t="s" s="2">
+        <v>187</v>
+      </c>
+      <c r="N117" s="2"/>
+      <c r="O117" s="2"/>
+      <c r="P117" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q117" s="2"/>
+      <c r="R117" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S117" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T117" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U117" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V117" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W117" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X117" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y117" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z117" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA117" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB117" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC117" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD117" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE117" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF117" t="s" s="2">
+        <v>188</v>
+      </c>
+      <c r="AG117" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH117" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI117" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ117" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AK117" t="s" s="2">
+        <v>189</v>
+      </c>
+      <c r="AL117" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM117" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN117" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AO117" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="118" hidden="true">
+      <c r="A118" t="s" s="2">
+        <v>594</v>
+      </c>
+      <c r="B118" t="s" s="2">
+        <v>594</v>
+      </c>
+      <c r="C118" s="2"/>
+      <c r="D118" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="E118" s="2"/>
+      <c r="F118" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G118" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H118" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I118" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J118" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K118" t="s" s="2">
+        <v>130</v>
+      </c>
+      <c r="L118" t="s" s="2">
+        <v>192</v>
+      </c>
+      <c r="M118" t="s" s="2">
+        <v>193</v>
+      </c>
+      <c r="N118" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="O118" s="2"/>
+      <c r="P118" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q118" s="2"/>
+      <c r="R118" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S118" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T118" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U118" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V118" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W118" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X118" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y118" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z118" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA118" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB118" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC118" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD118" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE118" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF118" t="s" s="2">
+        <v>195</v>
+      </c>
+      <c r="AG118" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH118" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI118" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ118" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="AK118" t="s" s="2">
+        <v>189</v>
+      </c>
+      <c r="AL118" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM118" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN118" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AO118" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="119" hidden="true">
+      <c r="A119" t="s" s="2">
+        <v>595</v>
+      </c>
+      <c r="B119" t="s" s="2">
+        <v>595</v>
+      </c>
+      <c r="C119" s="2"/>
+      <c r="D119" t="s" s="2">
+        <v>544</v>
+      </c>
+      <c r="E119" s="2"/>
+      <c r="F119" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G119" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H119" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I119" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="J119" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="K119" t="s" s="2">
+        <v>130</v>
+      </c>
+      <c r="L119" t="s" s="2">
+        <v>545</v>
+      </c>
+      <c r="M119" t="s" s="2">
+        <v>546</v>
+      </c>
+      <c r="N119" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="O119" t="s" s="2">
+        <v>168</v>
+      </c>
+      <c r="P119" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q119" s="2"/>
+      <c r="R119" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S119" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T119" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U119" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V119" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W119" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X119" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y119" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z119" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA119" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB119" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC119" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD119" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE119" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF119" t="s" s="2">
+        <v>547</v>
+      </c>
+      <c r="AG119" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH119" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI119" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ119" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="AK119" t="s" s="2">
+        <v>127</v>
+      </c>
+      <c r="AL119" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM119" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN119" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AO119" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="120" hidden="true">
+      <c r="A120" t="s" s="2">
+        <v>596</v>
+      </c>
+      <c r="B120" t="s" s="2">
+        <v>596</v>
+      </c>
+      <c r="C120" s="2"/>
+      <c r="D120" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E120" s="2"/>
+      <c r="F120" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="G120" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="H120" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I120" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J120" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K120" t="s" s="2">
+        <v>209</v>
+      </c>
+      <c r="L120" t="s" s="2">
+        <v>597</v>
+      </c>
+      <c r="M120" t="s" s="2">
+        <v>598</v>
+      </c>
+      <c r="N120" t="s" s="2">
+        <v>599</v>
+      </c>
+      <c r="O120" t="s" s="2">
+        <v>600</v>
+      </c>
+      <c r="P120" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q120" s="2"/>
+      <c r="R120" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S120" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T120" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U120" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V120" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W120" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X120" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="Y120" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="Z120" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="AA120" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB120" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC120" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD120" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE120" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF120" t="s" s="2">
+        <v>596</v>
+      </c>
+      <c r="AG120" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AH120" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI120" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ120" t="s" s="2">
         <v>96</v>
       </c>
-      <c r="AK106" t="s" s="2">
-        <v>594</v>
-      </c>
-      <c r="AL106" t="s" s="2">
+      <c r="AK120" t="s" s="2">
+        <v>601</v>
+      </c>
+      <c r="AL120" t="s" s="2">
+        <v>602</v>
+      </c>
+      <c r="AM120" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN120" t="s" s="2">
+        <v>603</v>
+      </c>
+      <c r="AO120" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="121" hidden="true">
+      <c r="A121" t="s" s="2">
+        <v>604</v>
+      </c>
+      <c r="B121" t="s" s="2">
+        <v>604</v>
+      </c>
+      <c r="C121" s="2"/>
+      <c r="D121" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E121" s="2"/>
+      <c r="F121" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G121" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="H121" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I121" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J121" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K121" t="s" s="2">
+        <v>266</v>
+      </c>
+      <c r="L121" t="s" s="2">
+        <v>605</v>
+      </c>
+      <c r="M121" t="s" s="2">
+        <v>606</v>
+      </c>
+      <c r="N121" t="s" s="2">
+        <v>607</v>
+      </c>
+      <c r="O121" t="s" s="2">
+        <v>608</v>
+      </c>
+      <c r="P121" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q121" s="2"/>
+      <c r="R121" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S121" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T121" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U121" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V121" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W121" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X121" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y121" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z121" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA121" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB121" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC121" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD121" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE121" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF121" t="s" s="2">
+        <v>604</v>
+      </c>
+      <c r="AG121" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH121" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI121" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ121" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="AK121" t="s" s="2">
+        <v>609</v>
+      </c>
+      <c r="AL121" t="s" s="2">
+        <v>610</v>
+      </c>
+      <c r="AM121" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN121" t="s" s="2">
+        <v>611</v>
+      </c>
+      <c r="AO121" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="122" hidden="true">
+      <c r="A122" t="s" s="2">
+        <v>612</v>
+      </c>
+      <c r="B122" t="s" s="2">
+        <v>612</v>
+      </c>
+      <c r="C122" s="2"/>
+      <c r="D122" t="s" s="2">
+        <v>613</v>
+      </c>
+      <c r="E122" s="2"/>
+      <c r="F122" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G122" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H122" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I122" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J122" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K122" t="s" s="2">
+        <v>614</v>
+      </c>
+      <c r="L122" t="s" s="2">
+        <v>615</v>
+      </c>
+      <c r="M122" t="s" s="2">
+        <v>616</v>
+      </c>
+      <c r="N122" t="s" s="2">
+        <v>617</v>
+      </c>
+      <c r="O122" s="2"/>
+      <c r="P122" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q122" s="2"/>
+      <c r="R122" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S122" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T122" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U122" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V122" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W122" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X122" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y122" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z122" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA122" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB122" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC122" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD122" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE122" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF122" t="s" s="2">
+        <v>612</v>
+      </c>
+      <c r="AG122" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH122" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI122" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ122" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="AK122" t="s" s="2">
+        <v>618</v>
+      </c>
+      <c r="AL122" t="s" s="2">
         <v>189</v>
       </c>
-      <c r="AM106" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN106" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AO106" t="s" s="2">
+      <c r="AM122" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN122" t="s" s="2">
+        <v>619</v>
+      </c>
+      <c r="AO122" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="123" hidden="true">
+      <c r="A123" t="s" s="2">
+        <v>620</v>
+      </c>
+      <c r="B123" t="s" s="2">
+        <v>620</v>
+      </c>
+      <c r="C123" s="2"/>
+      <c r="D123" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E123" s="2"/>
+      <c r="F123" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G123" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="H123" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I123" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J123" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="K123" t="s" s="2">
+        <v>248</v>
+      </c>
+      <c r="L123" t="s" s="2">
+        <v>621</v>
+      </c>
+      <c r="M123" t="s" s="2">
+        <v>622</v>
+      </c>
+      <c r="N123" t="s" s="2">
+        <v>623</v>
+      </c>
+      <c r="O123" t="s" s="2">
+        <v>624</v>
+      </c>
+      <c r="P123" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q123" s="2"/>
+      <c r="R123" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S123" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T123" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U123" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V123" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W123" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X123" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y123" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z123" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA123" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB123" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC123" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD123" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE123" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF123" t="s" s="2">
+        <v>620</v>
+      </c>
+      <c r="AG123" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH123" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI123" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ123" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="AK123" t="s" s="2">
+        <v>580</v>
+      </c>
+      <c r="AL123" t="s" s="2">
+        <v>625</v>
+      </c>
+      <c r="AM123" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN123" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AO123" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="124" hidden="true">
+      <c r="A124" t="s" s="2">
+        <v>626</v>
+      </c>
+      <c r="B124" t="s" s="2">
+        <v>626</v>
+      </c>
+      <c r="C124" s="2"/>
+      <c r="D124" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E124" s="2"/>
+      <c r="F124" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G124" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H124" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I124" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="J124" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="K124" t="s" s="2">
+        <v>534</v>
+      </c>
+      <c r="L124" t="s" s="2">
+        <v>627</v>
+      </c>
+      <c r="M124" t="s" s="2">
+        <v>628</v>
+      </c>
+      <c r="N124" t="s" s="2">
+        <v>629</v>
+      </c>
+      <c r="O124" t="s" s="2">
+        <v>630</v>
+      </c>
+      <c r="P124" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q124" s="2"/>
+      <c r="R124" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S124" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T124" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U124" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V124" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W124" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X124" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y124" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z124" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA124" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB124" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC124" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD124" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE124" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF124" t="s" s="2">
+        <v>626</v>
+      </c>
+      <c r="AG124" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH124" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI124" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ124" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="AK124" t="s" s="2">
+        <v>631</v>
+      </c>
+      <c r="AL124" t="s" s="2">
+        <v>189</v>
+      </c>
+      <c r="AM124" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN124" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AO124" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="125" hidden="true">
+      <c r="A125" t="s" s="2">
+        <v>632</v>
+      </c>
+      <c r="B125" t="s" s="2">
+        <v>632</v>
+      </c>
+      <c r="C125" s="2"/>
+      <c r="D125" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E125" s="2"/>
+      <c r="F125" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G125" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="H125" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I125" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J125" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K125" t="s" s="2">
+        <v>185</v>
+      </c>
+      <c r="L125" t="s" s="2">
+        <v>186</v>
+      </c>
+      <c r="M125" t="s" s="2">
+        <v>187</v>
+      </c>
+      <c r="N125" s="2"/>
+      <c r="O125" s="2"/>
+      <c r="P125" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q125" s="2"/>
+      <c r="R125" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S125" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T125" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U125" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V125" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W125" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X125" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y125" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z125" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA125" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB125" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC125" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD125" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE125" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF125" t="s" s="2">
+        <v>188</v>
+      </c>
+      <c r="AG125" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH125" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI125" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ125" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AK125" t="s" s="2">
+        <v>189</v>
+      </c>
+      <c r="AL125" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM125" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN125" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AO125" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="126" hidden="true">
+      <c r="A126" t="s" s="2">
+        <v>633</v>
+      </c>
+      <c r="B126" t="s" s="2">
+        <v>633</v>
+      </c>
+      <c r="C126" s="2"/>
+      <c r="D126" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="E126" s="2"/>
+      <c r="F126" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G126" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H126" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I126" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J126" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K126" t="s" s="2">
+        <v>130</v>
+      </c>
+      <c r="L126" t="s" s="2">
+        <v>192</v>
+      </c>
+      <c r="M126" t="s" s="2">
+        <v>193</v>
+      </c>
+      <c r="N126" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="O126" s="2"/>
+      <c r="P126" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q126" s="2"/>
+      <c r="R126" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S126" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T126" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U126" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V126" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W126" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X126" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y126" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z126" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA126" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB126" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC126" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD126" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE126" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF126" t="s" s="2">
+        <v>195</v>
+      </c>
+      <c r="AG126" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH126" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI126" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ126" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="AK126" t="s" s="2">
+        <v>189</v>
+      </c>
+      <c r="AL126" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM126" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN126" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AO126" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="127" hidden="true">
+      <c r="A127" t="s" s="2">
+        <v>634</v>
+      </c>
+      <c r="B127" t="s" s="2">
+        <v>634</v>
+      </c>
+      <c r="C127" s="2"/>
+      <c r="D127" t="s" s="2">
+        <v>544</v>
+      </c>
+      <c r="E127" s="2"/>
+      <c r="F127" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G127" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H127" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I127" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="J127" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="K127" t="s" s="2">
+        <v>130</v>
+      </c>
+      <c r="L127" t="s" s="2">
+        <v>545</v>
+      </c>
+      <c r="M127" t="s" s="2">
+        <v>546</v>
+      </c>
+      <c r="N127" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="O127" t="s" s="2">
+        <v>168</v>
+      </c>
+      <c r="P127" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q127" s="2"/>
+      <c r="R127" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S127" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T127" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U127" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V127" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W127" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X127" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y127" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z127" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA127" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB127" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC127" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD127" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE127" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF127" t="s" s="2">
+        <v>547</v>
+      </c>
+      <c r="AG127" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH127" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI127" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ127" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="AK127" t="s" s="2">
+        <v>127</v>
+      </c>
+      <c r="AL127" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM127" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN127" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AO127" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="128" hidden="true">
+      <c r="A128" t="s" s="2">
+        <v>635</v>
+      </c>
+      <c r="B128" t="s" s="2">
+        <v>635</v>
+      </c>
+      <c r="C128" s="2"/>
+      <c r="D128" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E128" s="2"/>
+      <c r="F128" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="G128" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="H128" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I128" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J128" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="K128" t="s" s="2">
+        <v>636</v>
+      </c>
+      <c r="L128" t="s" s="2">
+        <v>637</v>
+      </c>
+      <c r="M128" t="s" s="2">
+        <v>638</v>
+      </c>
+      <c r="N128" t="s" s="2">
+        <v>639</v>
+      </c>
+      <c r="O128" s="2"/>
+      <c r="P128" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q128" s="2"/>
+      <c r="R128" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S128" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T128" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U128" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V128" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W128" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X128" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y128" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z128" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA128" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB128" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC128" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD128" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE128" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF128" t="s" s="2">
+        <v>635</v>
+      </c>
+      <c r="AG128" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AH128" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI128" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ128" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="AK128" t="s" s="2">
+        <v>177</v>
+      </c>
+      <c r="AL128" t="s" s="2">
+        <v>189</v>
+      </c>
+      <c r="AM128" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN128" t="s" s="2">
+        <v>640</v>
+      </c>
+      <c r="AO128" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="129" hidden="true">
+      <c r="A129" t="s" s="2">
+        <v>641</v>
+      </c>
+      <c r="B129" t="s" s="2">
+        <v>641</v>
+      </c>
+      <c r="C129" s="2"/>
+      <c r="D129" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E129" s="2"/>
+      <c r="F129" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="G129" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="H129" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I129" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J129" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="K129" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="L129" t="s" s="2">
+        <v>642</v>
+      </c>
+      <c r="M129" t="s" s="2">
+        <v>643</v>
+      </c>
+      <c r="N129" s="2"/>
+      <c r="O129" s="2"/>
+      <c r="P129" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q129" s="2"/>
+      <c r="R129" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S129" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T129" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U129" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V129" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W129" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X129" t="s" s="2">
+        <v>202</v>
+      </c>
+      <c r="Y129" t="s" s="2">
+        <v>643</v>
+      </c>
+      <c r="Z129" t="s" s="2">
+        <v>644</v>
+      </c>
+      <c r="AA129" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB129" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC129" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD129" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE129" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF129" t="s" s="2">
+        <v>641</v>
+      </c>
+      <c r="AG129" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AH129" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI129" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ129" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="AK129" t="s" s="2">
+        <v>645</v>
+      </c>
+      <c r="AL129" t="s" s="2">
+        <v>189</v>
+      </c>
+      <c r="AM129" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN129" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AO129" t="s" s="2">
         <v>77</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AO106">
+  <autoFilter ref="A1:AO129">
     <filterColumn colId="6">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -14678,7 +17512,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI105">
+  <conditionalFormatting sqref="A2:AI128">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>
